--- a/nigooda-web/nigooda-backend/products.xlsx
+++ b/nigooda-web/nigooda-backend/products.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S204"/>
+  <dimension ref="A1:S304"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11826,9 +11826,5609 @@
         <v>0</v>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>f204</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Diabexy</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Diabexy Sugar Control Diabetic Atta</v>
+      </c>
+      <c r="D205" t="str">
+        <v>https://intl.diabexy.com/cdn/shop/files/ATTA_FRONT.jpg?v=1753341286</v>
+      </c>
+      <c r="E205" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F205" t="str">
+        <v>Diabetic / Low Sugar Food</v>
+      </c>
+      <c r="G205">
+        <v>489</v>
+      </c>
+      <c r="H205" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="I205" t="str">
+        <v>Diabexy Sugar Control Diabetic Atta is a scientifically formulated flour designed specifically for individuals managing diabetes and those seeking a low-glycemic lifestyle. This sugar-free atta is an excellent alternative to regular wheat flour, as it significantly reduces the glycemic load of your daily meals. It is crafted with a high-quality blend of ingredients including almonds, flax seeds, sunflower seeds, pumpkin seeds, and isolated soy protein that provide a rich source of protein and healthy fats while keeping carbohydrate levels in check. The texture is smooth, allowing you to prepare soft and delicious rotis, parathas, or pooris that taste remarkably like traditional bread. Benefits include better post-meal blood sugar management, sustained energy levels without insulin spikes, and improved satiety due to high fiber content. This product is certified for its low glycemic index and is free from added sugars and artificial preservatives. Whether you are diabetic, pre-diabetic, or health-conscious, Diabexy Atta helps you enjoy your favorite Indian meals without compromising your health goals. It is easy to knead and cook, making it a seamless addition to any kitchen pantry for health-focused cooking and general wellness.</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://diabexy.com/</v>
+      </c>
+      <c r="K205" t="str">
+        <v>diabexy-sugar-control-diabetic-atta</v>
+      </c>
+      <c r="L205" t="str">
+        <v xml:space="preserve">1kg </v>
+      </c>
+      <c r="M205" t="str">
+        <v>Diabetic Atta, Low GI Flour, Sugar Free Flour, Diabexy Sugar Control, Diabetic Friendly Food, Low Glycemic Index, High Protein Atta, Healthy Flour, Blood Sugar Management, Keto Friendly Flour, Grain Free Flour, Low Carb Atta, Diabetes Management, Healthy Roti, Nutritional Flour, Fiber Rich Atta, Natural Ingredients, Weight Loss Flour, Diabexy Products, Sugar Free Diet, Healthy Grains, Nut Based Flour, Seed Based Flour, Non GMO, No Added Sugar, Diabetic Staples, Indian Diabetic Diet, Healthy Cooking, Wellness Food, Low Carb Diet, Heart Healthy, Digestive Health, Soft Roti for Diabetics, High Fiber Diet, Protein Rich Flour, Diabexy Atta 1kg, Diabetic Nutrition, Healthy Eating, Low Glycemic Load, Blood Glucose Control</v>
+      </c>
+      <c r="N205" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P205" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q205" t="b">
+        <v>0</v>
+      </c>
+      <c r="R205" t="b">
+        <v>0</v>
+      </c>
+      <c r="S205" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>f205</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Diabexy</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Diabexy Atta LITE</v>
+      </c>
+      <c r="D206" t="str">
+        <v>https://intl.diabexy.com/cdn/shop/files/atta_2.jpg?v=1753341642</v>
+      </c>
+      <c r="E206" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F206" t="str">
+        <v>Diabetic / Low Sugar Food</v>
+      </c>
+      <c r="G206">
+        <v>344</v>
+      </c>
+      <c r="H206" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="I206" t="str">
+        <v>Diabexy Atta LITE is a specially formulated multigrain flour designed specifically for individuals managing diabetes. This high-fiber blend is crafted using over five nutrient-dense grains to help slow down the absorption of sugar in the bloodstream, aiding in stable glucose levels. Unlike many other specialty flours, this LITE version is completely nut-free, making it an excellent choice for those with allergies or those seeking a lighter alternative. The flour is exceptionally rich in dietary fiber, which promotes digestive health and provides prolonged satiety. It is engineered to provide a texture and flavor profile very similar to traditional wheat flour, allowing users to make soft, delicious rotis and parathas without the typical blood sugar spikes. This vegetarian product is ideal for daily consumption and supports a low-carbohydrate lifestyle by focusing on a lower glycemic load. Incorporating this atta into a balanced diet can help improve metabolic health and energy levels throughout the day.</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://diabexy.com/</v>
+      </c>
+      <c r="K206" t="str">
+        <v>diabexy-sugar-control-diabetic-atta</v>
+      </c>
+      <c r="L206" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="M206" t="str">
+        <v>Diabexy, Atta LITE, Multigrain Atta, Diabetes Friendly, Low Glycemic Index, Sugar Control, High Fiber, Nut Free, Healthy Flour, Diabetic Food, Weight Management, Low Carb, Natural Ingredients, Blood Sugar Support, Vegetarian, Whole Grains, Nutritious, Daily Essentials, Fiber Rich, Protein Flour, Non GMO, Healthy Living, Glucose Management, Diet Food, Roti Mix, Indian Staples, Wellness, Nut Free Flour, Metabolism Boost, Digestive Health</v>
+      </c>
+      <c r="N206" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P206" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q206" t="b">
+        <v>0</v>
+      </c>
+      <c r="R206" t="b">
+        <v>0</v>
+      </c>
+      <c r="S206" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>f206</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Diabexy</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Diabexy Gluten Free Atta</v>
+      </c>
+      <c r="D207" t="str">
+        <v>https://intl.diabexy.com/cdn/shop/files/ATTA_1.jpg?v=1753341276</v>
+      </c>
+      <c r="E207" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F207" t="str">
+        <v>Diabetic / Low Sugar Food</v>
+      </c>
+      <c r="G207">
+        <v>448</v>
+      </c>
+      <c r="H207" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="I207" t="str">
+        <v>Diabexy Gluten Free Atta is a premium high-protein, sugar-free flour meticulously crafted for individuals managing diabetes. This nutrient-dense atta is enriched with essential dietary fibers, wholesome nuts, and seeds, providing a balanced nutritional profile that supports healthy blood sugar levels. Designed as a direct substitute for regular flour, it allows for the preparation of delicious, low-carbohydrate rotis and baked goods without compromising on taste or texture. The inclusion of high-quality plant proteins and healthy fats ensures sustained energy and satiety throughout the day. It is completely gluten-free, making it suitable for those with gluten sensitivities or celiac disease. This diabetic-friendly flour is an excellent addition to a health-conscious kitchen, offering both versatility in cooking and significant nutritional benefits for long-term wellness. Free from added sugars and artificial preservatives, Diabexy Gluten Free Atta helps you maintain a healthy lifestyle while still enjoying traditional meals. It is specifically formulated to have a low glycemic load, assisting in effective blood sugar management and weight control.</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://diabexy.com/</v>
+      </c>
+      <c r="K207" t="str">
+        <v>diabexy-sugar-control-diabetic-atta</v>
+      </c>
+      <c r="L207" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="M207" t="str">
+        <v>Diabexy, Gluten Free Atta, Diabetic Friendly Flour, Sugar Free Atta, High Protein Flour, Low Carb Flour, Diabetes Management, Healthy Cooking, Nut and Seed Flour, Dietary Fiber, Weight Management, Gluten Free Food, Healthy Roti, Low Glycemic Index, Nutritional Flour, Diabetic Diet, Heart Healthy, Plant Based Protein, Natural Ingredients, Sugar Free Diet, Healthy Lifestyle, Celiac Friendly, Low Sugar Food, Wholesome Grains, Superfood Flour, Wellness Product, Daily Nutrition, High Fiber Diet, Protein Enriched, Healthy Baking</v>
+      </c>
+      <c r="N207" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P207" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="b">
+        <v>0</v>
+      </c>
+      <c r="R207" t="b">
+        <v>0</v>
+      </c>
+      <c r="S207" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>f207</v>
+      </c>
+      <c r="B208" t="str">
+        <v>NutroActive</v>
+      </c>
+      <c r="C208" t="str">
+        <v>NutroActive Low Carb Keto Atta</v>
+      </c>
+      <c r="D208" t="str">
+        <v>https://intl.diabexy.com/cdn/shop/files/1_1_fcfe5fcb-18f9-421b-a8ad-59f646e41854.jpg?v=1767770782</v>
+      </c>
+      <c r="E208" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F208" t="str">
+        <v>Diabetic / Low Sugar Food</v>
+      </c>
+      <c r="G208">
+        <v>499</v>
+      </c>
+      <c r="H208" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="I208" t="str">
+        <v>NutroActive Low Carb Keto Atta is a premium quality flour meticulously crafted for those on a ketogenic or low-carb lifestyle. This high-protein, low-glycemic flour is an ideal choice for individuals managing diabetes or pursuing a weight loss journey. Formulated with nutrient-dense ingredients like almonds and flax seeds, it provides a rich source of healthy fats and dietary fiber while keeping net carbs to a minimum. The texture is specifically engineered to mimic traditional wheat atta, allowing you to prepare soft, delicious rotis and parathas without the typical blood sugar spikes. It is free from added sugars and artificial preservatives, ensuring a natural and wholesome addition to your daily meals. This versatile flour helps maintain satiety and effectively manages insulin levels, supporting a slimmer body and improved metabolic health. Whether you are baking or cooking traditional Indian staples, this keto-friendly atta provides the perfect balance of health, flavor, and functionality for your diet.</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://diabexy.com/</v>
+      </c>
+      <c r="K208" t="str">
+        <v>diabexy-sugar-control-diabetic-atta</v>
+      </c>
+      <c r="L208" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="M208" t="str">
+        <v>Low Carb Atta, Keto Flour, Weight Loss Food, High Protein Atta, Diabetic Friendly Flour, Sugar-Free Atta, NutroActive Keto, Healthy Rotis, Low Glycemic Index, Grain-Free Flour, Keto Diet Essentials, Protein Rich Flour, Blood Sugar Management, Healthy Baking, Almond Flour Blend, Flax Seed Flour, Keto Chapatis, Low Carb Recipes, NutroActive Products, Healthy Eating, Weight Management, Low Carb Lifestyle, Nutrient Dense, High Fiber Atta, Natural Ingredients, No Added Sugar, Healthy Fats, Heart Healthy, Satiety, Slimming Food, Keto Friendly, Meal Prep, Indian Low Carb, NutroActive Atta, Diabexy, Healthy Lifestyle, Keto Staples, Low Carb Staples</v>
+      </c>
+      <c r="N208" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P208" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="b">
+        <v>0</v>
+      </c>
+      <c r="R208" t="b">
+        <v>0</v>
+      </c>
+      <c r="S208" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>f208</v>
+      </c>
+      <c r="B209" t="str">
+        <v>NutroActive</v>
+      </c>
+      <c r="C209" t="str">
+        <v>NutroActive Keto Gluten Free Atta</v>
+      </c>
+      <c r="D209" t="str">
+        <v>https://intl.diabexy.com/cdn/shop/files/ATTA_08b1e099-098a-4a1e-a28f-525530a1d158.jpg?v=1753341474</v>
+      </c>
+      <c r="E209" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F209" t="str">
+        <v>Diabetic / Low Sugar Food</v>
+      </c>
+      <c r="G209">
+        <v>476</v>
+      </c>
+      <c r="H209" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="I209" t="str">
+        <v>NutroActive Keto Gluten Free Atta is a meticulously crafted low-carb flour designed for individuals following a ketogenic or weight-loss diet. This gluten-free alternative is made from a blend of high-protein and high-fiber ingredients, ensuring a low Glycemic Index (GI) that prevents rapid spikes in blood sugar levels after consumption. It is perfect for making soft, delicious rotis and parathas that fit seamlessly into a healthy lifestyle without the carb-heavy burden of traditional wheat flour. The flour is rich in healthy fats and essential nutrients, promoting long-lasting energy and satiety, which helps in curbing unwanted cravings. It features a fine, easy-to-knead texture that is superior to many other gluten-free flours, making it convenient for daily kitchen use. Benefits include improved metabolic health, weight management support, and better digestion. This product is free from hidden sugars, artificial preservatives, and additives, ensuring you get a pure, natural addition to your pantry. Ideal for diabetics and health-conscious consumers, this keto-friendly flour allows you to enjoy traditional Indian meals while staying on track with your fitness goals.</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://diabexy.com/</v>
+      </c>
+      <c r="K209" t="str">
+        <v>diabexy-sugar-control-diabetic-atta</v>
+      </c>
+      <c r="L209" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="M209" t="str">
+        <v>Keto Atta, Gluten Free Flour, Low Carb Flour, Weight Loss Flour, High Protein Atta, Diabetic Friendly Flour, Low GI Atta, NutroActive Keto, Healthy Flour, Grain Free Flour, Keto Diet India, Weight Management, Low Carb Roti, Gluten Free Roti, Healthy Grains, NutroActive Products, Protein Rich Flour, Ketogenic Food, Sugar Control Flour, NutroActive Atta, Keto Staples, Low Carb Lifestyle, Healthy Baking, Fiber Rich Flour, Non-GMO Flour, Natural Ingredients, Weight Loss Diet, Low Carb Chapati, NutroActive Flour, Healthy Eating, Keto Friendly, Flour Alternative, Paleo Friendly, Diabetic Diet, Healthy Lifestyle</v>
+      </c>
+      <c r="N209" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P209" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="b">
+        <v>0</v>
+      </c>
+      <c r="R209" t="b">
+        <v>0</v>
+      </c>
+      <c r="S209" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>f209</v>
+      </c>
+      <c r="B210" t="str">
+        <v>NutroActive</v>
+      </c>
+      <c r="C210" t="str">
+        <v>NutroActive Keto Atta Daily | Nuts Free Low Carb Atta</v>
+      </c>
+      <c r="D210" t="str">
+        <v>https://intl.diabexy.com/cdn/shop/files/Keto_atta_daily.jpg?v=1753341431</v>
+      </c>
+      <c r="E210" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F210" t="str">
+        <v>Diabetic / Low Sugar Food</v>
+      </c>
+      <c r="G210">
+        <v>349</v>
+      </c>
+      <c r="H210" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="I210" t="str">
+        <v>NutroActive Keto Atta Daily is a specialized nuts-free flour designed for those following a ketogenic lifestyle or managing blood sugar levels. This high-protein, low-carb atta is an excellent choice for individuals looking to lose weight or maintain a healthy diet without sacrificing the traditional texture of rotis. Formulated to be diabetes-friendly, it provides a stable source of energy without the carb-heavy impact of regular wheat flour. The flour is crafted from high-quality ingredients including seeds and vegetable proteins, ensuring it is rich in fiber and essential nutrients. It features a soft texture and a neutral flavor profile that blends seamlessly into daily meals. Whether you are preparing rotis, parathas, or other baked goods, this atta offers the perfect balance of health and taste. It is certified for quality and designed for daily consumption, helping you stay in ketosis while enjoying your favorite comfort foods. This product is ideal for those who have nut allergies but still want a low-carbohydrate alternative for their daily bread.</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://diabexy.com/</v>
+      </c>
+      <c r="K210" t="str">
+        <v>diabexy-sugar-control-diabetic-atta</v>
+      </c>
+      <c r="L210" t="str">
+        <v>1kg</v>
+      </c>
+      <c r="M210" t="str">
+        <v>NutroActive, Keto Atta, Low Carb Flour, High Protein Atta, Nuts Free Keto, Diabetes Friendly, Weight Loss Food, Keto Diet, Healthy Flour, NutroActive Daily, Sugar Free Flour, Diabetic Diet, Keto Rotis, Protein Rich, Low GI Flour, Healthy Grains, Grain Substitutes, Ketogenic Lifestyle, Seed Flour, Vegetable Protein, Fiber Rich, Low Carb Rotis, Indian Keto, NutroActive Products, Healthy Eating, Low Carb Meals, NutroActive Atta, Keto Friendly Flour, Daily Keto, Clean Eating, Keto Essentials</v>
+      </c>
+      <c r="N210" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P210" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="b">
+        <v>0</v>
+      </c>
+      <c r="R210" t="b">
+        <v>0</v>
+      </c>
+      <c r="S210" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>f210</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Diabexy</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Diabexy Breakfast Pancake Mix 350g | Sugar-Free &amp; Diabetic-Friendly</v>
+      </c>
+      <c r="D211" t="str">
+        <v>https://intl.diabexy.com/cdn/shop/files/Diabexy_Pancake_f1eef08e-747c-4bc4-abef-74458464f45a.jpg?v=1753341302</v>
+      </c>
+      <c r="E211" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F211" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G211">
+        <v>384</v>
+      </c>
+      <c r="H211" t="str">
+        <v>350g</v>
+      </c>
+      <c r="I211" t="str">
+        <v>Diabexy Pancake Mix is a specially formulated breakfast solution designed for individuals managing diabetes or looking for a sugar-free morning meal. This 350g pack offers an easy-to-make batter that can be prepared in just three simple steps, making it a convenient choice for busy mornings. Crafted with health in mind, it is enriched with essential vitamins including Vitamin A, C, and E, providing nutritional highlights alongside its low glycemic impact. The mix is ideal for creating soft, fluffy Indian-style pancakes that satisfy cravings without the sugar spike. It features a blend of high-quality ingredients tailored for diabetic dietary requirements, ensuring both safety and flavor. The texture is designed to be smooth and consistent once mixed, resulting in a delicious breakfast option that aligns with a healthy lifestyle. This product is certified to meet specific dietary standards, offering a reliable and tasty alternative to traditional high-carb pancake mixes. The formulation focuses on slow-release energy, helping to maintain stable blood glucose levels throughout the morning.</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://diabexy.com/</v>
+      </c>
+      <c r="K211" t="str">
+        <v>diabexy-sugar-free-drops1</v>
+      </c>
+      <c r="L211" t="str">
+        <v>350g</v>
+      </c>
+      <c r="M211" t="str">
+        <v>Diabexy, Pancake Mix, Sugar-Free, Diabetic-Friendly, Breakfast, Healthy Breakfast, Instant Mix, Low Sugar, Vitamin Enriched, Vitamin A, Vitamin C, Vitamin E, Diabetic Food, Low Glycemic, Easy Breakfast, 350g, Indian Pancake, Healthy Living, Nutrition, High Fiber, Low Carb, Snack, Dessert, Breakfast Batter, No Added Sugar, Fitness Food, Wellness, Meal Prep, Quick Breakfast, Diabetic Diet, Healthy Eating, Pancake Batter</v>
+      </c>
+      <c r="N211" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P211" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="b">
+        <v>0</v>
+      </c>
+      <c r="R211" t="b">
+        <v>0</v>
+      </c>
+      <c r="S211" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>f211</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Diabexy</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Diabexy Dosa Mix 350g</v>
+      </c>
+      <c r="D212" t="str">
+        <v>https://intl.diabexy.com/cdn/shop/files/Diabexy_Dosa.jpg?v=1753341357</v>
+      </c>
+      <c r="E212" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F212" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G212">
+        <v>384</v>
+      </c>
+      <c r="H212" t="str">
+        <v>350g</v>
+      </c>
+      <c r="I212" t="str">
+        <v>Diabexy Dosa Mix is a premium, ready-to-cook solution designed specifically for individuals managing blood sugar levels or following a ketogenic diet. This 100% natural, sugar-free batter mix offers the authentic taste of homemade South Indian dosas without the high carbohydrate content typically found in traditional rice-based batters. It is crafted from a proprietary blend of high-quality ingredients, including nuts, seeds, and plant-based proteins, ensuring a very low glycemic load. This nutrient-dense mix is rich in healthy fats and fiber, providing sustained energy and supporting metabolic health. Preparing a meal is incredibly easy: simply whisk the powder with water to achieve a smooth consistency, and it is ready to be poured onto a hot tawa. The resulting dosas are crisp, golden, and flavorful, offering a satisfying texture that pairs perfectly with coconut chutney or sambar. Free from artificial preservatives and additives, this mix is a certified healthy choice for those seeking to enjoy traditional flavors while maintaining a balanced, low-sugar lifestyle.</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://diabexy.com/</v>
+      </c>
+      <c r="K212" t="str">
+        <v>diabexy-sugar-free-drops1</v>
+      </c>
+      <c r="L212" t="str">
+        <v>350g</v>
+      </c>
+      <c r="M212" t="str">
+        <v>Diabexy, Dosa Mix, Sugar Free Dosa, Diabetic Friendly Food, Low Glycemic Load, Keto Dosa, Healthy Breakfast, Ready to Cook, Instant Dosa Batter, Gluten Free Dosa, Low Carb Breakfast, Diabetes Management, High Fiber Food, Natural Ingredients, Healthy Indian Breakfast, Low Sugar Diet, Nut Based Dosa, Protein Rich Dosa, Weight Loss Food, Metabolic Health, Blood Sugar Control, Homemade Taste, Traditional Dosa, Vegan Friendly, Preservative Free, No Added Sugar, Healthy Eating, South Indian Cuisine, Nutritious Batter, Easy to Cook, Diabetic Recipes, Low Carb Snacks, Wholesome Meal, Diet Friendly, Healthy Living, Premium Quality, Natural Dosa Mix</v>
+      </c>
+      <c r="N212" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P212" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="b">
+        <v>0</v>
+      </c>
+      <c r="R212" t="b">
+        <v>0</v>
+      </c>
+      <c r="S212" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>f212</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Diabexy</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Diabexy Sugar Free Drops - Sugarfree Sweetener</v>
+      </c>
+      <c r="D213" t="str">
+        <v>https://diabexy.com/cdn/shop/files/Sugar_Drop_1200x.jpg?v=1753341393</v>
+      </c>
+      <c r="E213" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F213" t="str">
+        <v>Diabetic / Low Sugar Food</v>
+      </c>
+      <c r="G213">
+        <v>159</v>
+      </c>
+      <c r="H213" t="str">
+        <v>30ml</v>
+      </c>
+      <c r="I213" t="str">
+        <v>Diabexy Sugar Free Drops offer a premium liquid sweetener solution specifically formulated for individuals managing diabetes or following a low-carb lifestyle. Composed primarily of purified water and high-quality sucralose, these drops provide a clean, sweet taste without the bitter aftertaste often associated with artificial sweeteners. Each drop is engineered to have a zero Glycemic Load, meaning it does not spike blood glucose levels, making it an ideal choice for sugar-free living. This product is exceptionally versatile and heat-stable, allowing it to be used in hot beverages like tea and coffee, as well as in cooking and baking applications for various desserts. One single drop provides the equivalent sweetness of one teaspoon of sugar, making it highly concentrated and cost-effective. Diabexy ensures that their formula is safe for long-term consumption by people of all ages, including children and pregnant women. The liquid form allows for instant dissolution in both hot and cold liquids, ensuring a smooth texture and consistent flavor throughout your meal or drink. Certified as a low GI product, it supports weight loss goals and helps maintain healthy insulin levels while satisfying your sweet tooth.</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://diabexy.com/</v>
+      </c>
+      <c r="K213" t="str">
+        <v>diabexy-sugar-free-drops</v>
+      </c>
+      <c r="L213" t="str">
+        <v>30ml - Pack of 1</v>
+      </c>
+      <c r="M213" t="str">
+        <v>Sugar Free, Diabetes Friendly, Zero Calorie Sweetener, Low Glycemic Index, Diabexy Drops, Sucralose Sweetener, Liquid Stevia Alternative, Keto Friendly, Weight Loss, Blood Sugar Control, Diabetic Snacks, Healthy Sweetener, No Aftertaste, Tea Sweetener, Coffee Drops, Baking Sweetener, Zero Carb, Insulin Support, Natural Taste, Sugar Substitute, Calorie Free, Non-GMO, Gluten Free, Vegan Sweetener, Diabexy Food, High Concentration, Easy To Use, Portable Sweetener, Heat Stable, Cooking Sweetener, Dessert Drops, Healthy Lifestyle, Fitness Diet, Paleo Friendly, Low GI Food, Blood Glucose Management, Safe For Diabetics, Purified Water Based, High Quality Sucralose, Diabexy India</v>
+      </c>
+      <c r="N213" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P213" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="b">
+        <v>0</v>
+      </c>
+      <c r="R213" t="b">
+        <v>0</v>
+      </c>
+      <c r="S213" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>f213</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Diabexy</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Diabexy Sugar Free Sweetener 250g | Low Glycemic Sugar Substitute</v>
+      </c>
+      <c r="D214" t="str">
+        <v>https://intl.diabexy.com/cdn/shop/files/3_2_74de2c34-3ef4-4c9a-9e36-0e6e3015258b.jpg?v=1753341400</v>
+      </c>
+      <c r="E214" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F214" t="str">
+        <v>Diabetic / Low Sugar Food</v>
+      </c>
+      <c r="G214">
+        <v>433</v>
+      </c>
+      <c r="H214" t="str">
+        <v>250g</v>
+      </c>
+      <c r="I214" t="str">
+        <v>Diabexy Sugar Free Sweetener is a premium low-glycemic sugar substitute specifically formulated for individuals managing diabetes, following a keto lifestyle, or focusing on weight loss. This 250g sugar-free powder provides the perfect alternative to traditional sugar without the spike in blood glucose levels, thanks to its meticulously balanced low glycemic load. It integrates seamlessly into daily routines, making it ideal for sweetening tea, coffee, and a wide variety of beverages. Beyond drinks, its heat-stable properties allow for versatile use in healthy cooking and baking, ensuring you can enjoy your favorite desserts and treats guilt-free. The texture is fine and easy to dissolve, offering a clean sweet flavor without a harsh aftertaste. By choosing Diabexy, you benefit from a product designed to support metabolic health while satisfying sweet cravings. This sweetener is a staple for anyone committed to a healthy, low-carb diet seeking a reliable and effective sugar replacement for better blood sugar management, providing a safe and effective way to reduce sugar intake without compromising on taste.</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://diabexy.com/</v>
+      </c>
+      <c r="K214" t="str">
+        <v>diabexy-sugar-free-drops</v>
+      </c>
+      <c r="L214" t="str">
+        <v>250g</v>
+      </c>
+      <c r="M214" t="str">
+        <v>Sugar Free Sweetener, Low Glycemic Index, Diabetes Friendly, Keto Sugar Substitute, Weight Loss Food, Sugar Free Powder, Healthy Cooking, Low Carb Sweetener, Blood Sugar Management, Diabexy, Diabetic Diet, Keto Friendly, Natural Sweetener, No Added Sugar, Healthy Baking, Calorie Free, Stevia Alternative, Erythritol Blend, Metabolic Health, Insulin Sensitivity, Sugar Replacement, Diabetic Snacks, Low GI Foods, Sugar Free Tea, Sugar Free Coffee, Healthy Desserts, Guilt Free Sweets, Non-GMO Sweetener, Gluten Free Sweetener, Vegan Sweetener, Zero Calorie, Fitness Diet, Bodybuilding Nutrition, Low Carb Lifestyle, Diabetic Care, Diabexy Products, Sugar Free India, Healthy Lifestyle, Nutrition Focused, Premium Sweetener, Easy Dissolve, Heat Stable Sweetener, Baking Essentials, Pantry Staples, Wellness Products</v>
+      </c>
+      <c r="N214" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P214" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="b">
+        <v>0</v>
+      </c>
+      <c r="R214" t="b">
+        <v>0</v>
+      </c>
+      <c r="S214" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>f214</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Millet Amma</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Millet Rava Idli Mix | 250 GMS Pack | 92% Millet Content | Easy &amp; Ready to Cook | Instant Millet Breakfast Mix | Rich in Protein &amp; High Fiber | 100% Vegan</v>
+      </c>
+      <c r="D215" t="str">
+        <v>https://milletamma.com/cdn/shop/products/MilletRavaIdliMilletAmma_cc7276db-f2e7-41f8-8355-e8671f5aa381_1200x1200.jpg?v=1738412583</v>
+      </c>
+      <c r="E215" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F215" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G215">
+        <v>220</v>
+      </c>
+      <c r="H215" t="str">
+        <v>250 GMS Pack</v>
+      </c>
+      <c r="I215" t="str">
+        <v>Millet Amma's Organic Millet Rava Idli Mix offers a nutritious and delicious start to your day with a significant 92% millet content. This gluten-free mix is specifically formulated using Little Millet, making it an excellent source of essential minerals like calcium and magnesium. Unlike traditional rice-based idlis, these millet idlis feature a relatively low glycemic index, promoting better blood sugar management. Each pack is meticulously crafted with organic ingredients including urad dal, chana dal, and a flavorful tempering of curry leaves, mustard seeds, and ginger. The addition of cashew nuts provides a delightful crunch and richness to every bite. Perfect for busy mornings, this instant breakfast solution is 100% vegan and high in fiber, aiding digestion and providing sustained energy. Simply follow the easy preparation steps to enjoy soft, fluffy, and healthy idlis that don't compromise on taste. It is an ideal choice for health-conscious individuals and those looking for wholesome, traditional flavors in a modern, convenient format.</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://milletamma.com/</v>
+      </c>
+      <c r="K215" t="str">
+        <v>millet-rava-idli-mix</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Millet Rava Idli Mix | 250 GMS Pack | 92% Millet Content | Easy &amp; Ready to Cook | Instant Millet Breakfast Mix | Rich in Protein &amp; High Fiber | 100% Vegan</v>
+      </c>
+      <c r="M215" t="str">
+        <v>Millet Rava Idli Mix, 250 GMS Pack, 92% Millet Content, Easy &amp; Ready to Cook, Instant Millet Breakfast Mix, Rich in Protein &amp; High Fiber, 100% Vegan, Millet Amma, Organic, Gluten-free, Healthy Breakfast, Calcium Rich, Magnesium Rich, Low Glycemic Index, Rice Idli Replacement, Little Millet, Healthy Food, Weight Loss, Nutritious, Natural Ingredients, Breakfast Mix, Ready to Cook, Indian Breakfast, Traditional Taste, Vegan Breakfast, Fiber Rich, No Preservatives, Organic Food India, Millet Based Food</v>
+      </c>
+      <c r="N215" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P215" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="b">
+        <v>0</v>
+      </c>
+      <c r="R215" t="b">
+        <v>0</v>
+      </c>
+      <c r="S215" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>f215</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Millet Amma</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Organic Millet Khichdi Mix | 250 GMS Pack | 65% Millet Content | Easy &amp; Ready to Cook | Instant Millet Breakfast Mix | Rich in Protein &amp; High Fiber | 100% Vegan</v>
+      </c>
+      <c r="D216" t="str">
+        <v>https://milletamma.com/cdn/shop/products/MilletKhichdiMix-MilletAmma-GlutenFree_1200x1200.jpg?v=1738413645</v>
+      </c>
+      <c r="E216" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F216" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G216">
+        <v>230</v>
+      </c>
+      <c r="H216" t="str">
+        <v>250 gms</v>
+      </c>
+      <c r="I216" t="str">
+        <v>Millet Amma’s Organic Millet Khichdi Mix offers a nutritious and healthy spin on the beloved classic comfort dish. Expertly crafted with a significant 65% Foxtail Millet content, this mix is exceptionally rich in dietary fiber, essential minerals, and vital vitamins. It serves as a delicious and wholesome substitute for traditional rice-based khichdi. The inclusion of Foxtail millets ensures a low glycemic index, providing a steady release of energy and keeping you satiated for extended periods. This 100% vegan and gluten-free mix is perfect for health-conscious individuals and those with specific dietary sensitivities. The blend consists of organic Foxtail millets, Moong dal, aromatic curry leaves, handpicked spices, and healthy pink salt. It is incredibly easy to prepare, allowing you to whip up a satisfying meal in just a few minutes. Ideal for breakfast or a light dinner, it offers a wonderful texture and authentic flavor. This product is made with love, ensuring your family receives the best choice for their health without compromising on taste and quality. Each pack contains 250 grams of organic goodness, carefully processed to retain its nutritional value and natural aroma for a shelf life of six months.</v>
+      </c>
+      <c r="J216" t="str">
+        <v>https://milletamma.com/</v>
+      </c>
+      <c r="K216" t="str">
+        <v>millet-rava-idli-mix</v>
+      </c>
+      <c r="L216" t="str">
+        <v>Organic Millet Khichdi Mix | 250 GMS Pack | 65% Millet Content | Easy &amp; Ready to Cook | Instant Millet Breakfast Mix | Rich in Protein &amp; High Fiber | 100% Vegan</v>
+      </c>
+      <c r="M216" t="str">
+        <v>millet khichdi mix, organic millet khichdi, foxtail millet, ready to cook, instant breakfast, gluten free, vegan, healthy breakfast, low GI food, high fiber, Millet Amma, organic food mix, moong dal khichdi, pink salt, easy meals, nutritious, weight loss, diabetic friendly, natural, no preservatives, indian breakfast, traditional khichdi, protein rich, whole grain, foxtail recipes, millet products, breakfast ideas, fiber rich, organic cereals, healthy grains, ready to eat, plant based, nutrient dense, comfort food</v>
+      </c>
+      <c r="N216" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P216" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="b">
+        <v>0</v>
+      </c>
+      <c r="R216" t="b">
+        <v>0</v>
+      </c>
+      <c r="S216" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>f216</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Millet Amma</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Millet Pongal Mix | 250 GMS Pack | 58% Millet Content | Easy &amp; Ready to Cook | Instant Millet Breakfast Mix | Rich in Protein &amp; High Fiber | 100% Vegan</v>
+      </c>
+      <c r="D217" t="str">
+        <v>https://milletamma.com/cdn/shop/products/MilletPongalMix-MilletAmma_1200x1200.jpg?v=1717387238</v>
+      </c>
+      <c r="E217" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F217" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G217">
+        <v>230</v>
+      </c>
+      <c r="H217" t="str">
+        <v>250 GMS</v>
+      </c>
+      <c r="I217" t="str">
+        <v>Millet Amma’s Organic Millet Pongal Mix offers a wholesome and nutritious start to your day with the comfort of a piping hot traditional breakfast. This ready-to-cook mix features a high millet content of over 58%, primarily utilizing Foxtail Millet blended perfectly with Moong Dal. It is naturally rich in essential dietary fiber, iron, and proteins, making it an ideal choice for health-conscious consumers and those seeking a balanced diet. The mix is incredibly easy to prepare, requiring only a few minutes to transform into a delicious meal, perfect for busy mornings. Crafted with 100% organic and vegan ingredients, it contains no artificial preservatives or additives. The texture is creamy and satisfying, while the flavor profile is authentic and savory. This product is certified organic and follows strict quality standards to ensure you receive the best of ancient grains. Simply follow the easy cooking instructions on the pack to enjoy a guilt-free, high-energy meal that supports digestion and overall wellness. It is 100% vegan and gluten-free.</v>
+      </c>
+      <c r="J217" t="str">
+        <v>https://milletamma.com/</v>
+      </c>
+      <c r="K217" t="str">
+        <v>millet-rava-idli-mix</v>
+      </c>
+      <c r="L217" t="str">
+        <v>Millet Pongal Mix | 250 GMS Pack | 58% Millet Content | Easy &amp; Ready to Cook | Instant Millet Breakfast Mix | Rich in Protein &amp; High Fiber | 100% Vegan</v>
+      </c>
+      <c r="M217" t="str">
+        <v>Millet Pongal Mix, Organic Breakfast, Foxtail Millet, Ready to Cook, Healthy Breakfast, Vegan Food, High Protein, High Fiber, Gluten Free Pongal, Millet Amma, Instant Meal, Indian Breakfast, Nutritious Food, Iron Rich, Low Glycemic, Ancient Grains, Weight Management, Easy Cooking, Organic Pongal, Moong Dal Mix, Traditional Taste, Chemical Free, Preservative Free, Smart Food, Healthy Lifestyle, Morning Energy, Digestive Health, Sustainable Food, Natural Ingredients, Superfood Mix, Quick Breakfast, Wholesome Meal, Diet Friendly, Fitness Food, South Indian Breakfast, Breakfast Porridge, Clean Eating, Plant Based, Non GMO, Gourmet Food, Millet Recipes, Healthy Grains, Nutritious Mix, Energy Boosting, Travel Food, Hostel Food, Single Serve Pack</v>
+      </c>
+      <c r="N217" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P217" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="b">
+        <v>0</v>
+      </c>
+      <c r="R217" t="b">
+        <v>0</v>
+      </c>
+      <c r="S217" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>f217</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Millet Amma</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Millet Rava Dosa Mix | 250 Gms Pack | 58% Millet Content | Easy &amp; Ready to Cook | Instant Millet Breakfast Mix | Rich in Protein &amp; High Fiber | 100% Vegan</v>
+      </c>
+      <c r="D218" t="str">
+        <v>https://milletamma.com/cdn/shop/products/MilletRavaDosaMilletAmma_1200x1200.jpg?v=1738413151</v>
+      </c>
+      <c r="E218" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F218" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G218">
+        <v>200</v>
+      </c>
+      <c r="H218" t="str">
+        <v>250 gms</v>
+      </c>
+      <c r="I218" t="str">
+        <v>Millet Amma’s Millet Rava Dosa Mix is a nutritious and convenient breakfast solution that brings the goodness of traditional grains to your table. Containing over 58% millet content, specifically Little Millet, this mix is blended with Red Rice and Jeera to create a high-energy meal that is rich in protein, fiber, and essential minerals. This 100% organic formulation is meticulously crafted without any artificial preservatives, ensuring a wholesome experience for individuals of all ages. Being both vegan and gluten-free, it caters perfectly to diverse dietary requirements and supports effective weight management. The mix features a flavorful profile with ingredients like pink salt, curry leaves, and mustard seeds, delivering the authentic, crispy texture of a classic Rava Dosa. It is exceptionally easy to prepare, making it a perfect ready-to-cook option for busy mornings. For an enhanced dining experience, pair these crispy dosas with organic Moringa chutney or peanut podi. Store this mix in a cool, dry place to maintain its 6-month shelf life. This product is a testament to healthy eating combined with traditional taste.</v>
+      </c>
+      <c r="J218" t="str">
+        <v>https://milletamma.com/</v>
+      </c>
+      <c r="K218" t="str">
+        <v>millet-rava-idli-mix</v>
+      </c>
+      <c r="L218" t="str">
+        <v>Millet Rava Dosa Mix | 250 Gms Pack | 58% Millet Content | Easy &amp; Ready to Cook | Instant Millet Breakfast Mix | Rich in Protein &amp; High Fiber | 100% Vegan</v>
+      </c>
+      <c r="M218" t="str">
+        <v>Millet Rava Dosa Mix, 250g Pack, 58 Percent Millet, Ready to Cook, Instant Breakfast, Healthy Breakfast Mix, Protein Rich, High Fiber, 100% Vegan, Millet Amma, Organic Food, Gluten Free Dosa, Little Millet, Red Rice, Jeera, No Preservatives, Weight Management, Crispy Rava Dosa, Nutritious Meal, Indian Breakfast, Natural Ingredients, High Energy, Fiber Rich Diet, Protein Breakfast, Diet Friendly, Morning Meals, Easy Cooking, Traditional Taste, Healthy Living, Wholesome Grains, Pink Salt, Curry Leaves, Mustard Seeds, Organic Breakfast, Low Glycemic, Gut Healthy, Clean Label, Plant Based, Indian Superfoods, Breakfast Staples, Fast Cooking, Healthy Snacks, Millet Recipes, Fitness Food, Nutrient Dense, Breakfast Ideas, Home Style Cooking</v>
+      </c>
+      <c r="N218" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P218" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="b">
+        <v>0</v>
+      </c>
+      <c r="R218" t="b">
+        <v>0</v>
+      </c>
+      <c r="S218" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>f218</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Millet Amma</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Little Millet Pasta - 180gm</v>
+      </c>
+      <c r="D219" t="str">
+        <v>http://milletamma.com/cdn/shop/products/10a_7ca9ae94-5246-4935-a950-c2502fb03a06_1200x1200.jpg?v=1738413267</v>
+      </c>
+      <c r="E219" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F219" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G219">
+        <v>140</v>
+      </c>
+      <c r="H219" t="str">
+        <v>180gm</v>
+      </c>
+      <c r="I219" t="str">
+        <v>Millet Amma’s Little Millet Pasta is a health-conscious alternative to traditional wheat pasta, specifically designed for those who refuse to compromise on taste or nutrition. Crafted with 50% Little Millet (Kutki) flour and whole wheat, this pasta is a powerhouse of dietary fiber and slow-digesting carbohydrates. Little Millet is recognized for its low glycemic index, which helps regulate blood sugar levels by slowing glucose entry into the bloodstream. Rich in magnesium for heart health and Vitamin B3 (niacin) for cholesterol management, it also provides essential phosphorus for energy production and muscle tissue repair. The product is entirely free from artificial additives or preservatives, using natural ingredients for a wholesome experience. Included is a flavorful tastemaker blend featuring cloves, coriander, ginger, cinnamon, cumin, and vegetable powders. Perfect for a quick, nutritious meal, it offers a firm texture and savory flavor profile. Store in an airtight container to maintain freshness for up to six months.</v>
+      </c>
+      <c r="J219" t="str">
+        <v>https://milletamma.com/</v>
+      </c>
+      <c r="K219" t="str">
+        <v>little-millet-pasta1</v>
+      </c>
+      <c r="L219" t="str">
+        <v>Little Millet Pasta - 180gm</v>
+      </c>
+      <c r="M219" t="str">
+        <v>Little Millet Pasta, Millet Amma, healthy pasta, organic millet, ready to cook, low GI food, dietary fiber, magnesium rich, vitamin B3, heart health, cholesterol control, weight loss food, kutki millet, whole wheat pasta, natural ingredients, no preservatives, vegan food, Indian millets, nutritious dinner, healthy snacks, diabetic friendly, slow carbs, energy production, phosphorus rich, aromatic spices, clove, coriander, ginger, cinnamon, cumin, onion powder, garlic powder, tomato powder, shelf stable, artisan pasta, ancient grains, millet benefits, high fiber pasta, fitness food, wholesome meal, meal prep, easy cooking, nutrient dense, sustainable grains, clean eating</v>
+      </c>
+      <c r="N219" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P219" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="b">
+        <v>0</v>
+      </c>
+      <c r="R219" t="b">
+        <v>0</v>
+      </c>
+      <c r="S219" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>f219</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Millet Amma</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Jowar Millet Pasta - 180gm</v>
+      </c>
+      <c r="D220" t="str">
+        <v>https://milletamma.com/cdn/shop/products/13b_1200x1200.jpg?v=1717387850</v>
+      </c>
+      <c r="E220" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F220" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G220">
+        <v>140</v>
+      </c>
+      <c r="H220" t="str">
+        <v>180 gms</v>
+      </c>
+      <c r="I220" t="str">
+        <v>Millet Amma’s Jowar Millet Pasta is a tasty and nutritious alternative to traditional pasta that doesn't compromise on flavor. Crafted from high-quality Jowar (Sorghum) and Whole Wheat Flour, this pasta offers a significantly higher concentration of dietary fiber compared to other cereal grains. This high fiber content ensures lasting satiety, effectively managing hunger pangs and assisting in weight loss goals. The product includes a specially formulated tastemaker featuring a blend of cloves, coriander, ginger, cinnamon, and cumin for a rich, aromatic flavor profile. Free from artificial additives and preservatives, it is designed for health-conscious consumers seeking wholesome meals. The texture is smooth and satisfying, making it a favorite for all ages. Enjoy the benefits of natural ingredients and essential nutrients in a ready-to-cook format that prepares in minutes. Store in a cool, dry place for a shelf life of up to 6 months.</v>
+      </c>
+      <c r="J220" t="str">
+        <v>https://milletamma.com/</v>
+      </c>
+      <c r="K220" t="str">
+        <v>little-millet-pasta1</v>
+      </c>
+      <c r="L220" t="str">
+        <v>Jowar Millet Pasta - 180gm</v>
+      </c>
+      <c r="M220" t="str">
+        <v>Jowar Millet Pasta, Sorghum Pasta, Healthy Pasta, High Fiber Food, Weight Loss Friendly, Millet Amma, Ready to Cook, Whole Wheat Pasta, Gluten Free Diet, Vegan Friendly, Natural Ingredients, No Preservatives, Millet Snacks, Indian Millets, Nutritious Meal, Easy Dinner, Breakfast Ideas, High Satiety Food, Organic Pasta, Gourmet Millet, Healthy Lifestyle, Fiber Rich, Low Calorie Pasta, Traditional Grains, Ancient Grains, Wholesome Food, Non-GMO, Plant Based, Indian Food Brands, Quick Meals</v>
+      </c>
+      <c r="N220" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P220" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="b">
+        <v>0</v>
+      </c>
+      <c r="R220" t="b">
+        <v>0</v>
+      </c>
+      <c r="S220" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>f220</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Millet Amma</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Jowar Millet Instant Noodles - 175gm</v>
+      </c>
+      <c r="D221" t="str">
+        <v>https://milletamma.com/cdn/shop/products/15a_1200x1200.jpg?v=1738921797</v>
+      </c>
+      <c r="E221" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F221" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G221">
+        <v>160</v>
+      </c>
+      <c r="H221" t="str">
+        <v>175gm</v>
+      </c>
+      <c r="I221" t="str">
+        <v>Millet Amma’s Jowar Millet Instant Noodles offer a healthy and delicious alternative to traditional wheat-based noodles. Crafted with care, these noodles are made from premium Jowar (Sorghum) millet, ensuring you enjoy the comfort of a quick meal without the guilt of maida or other harmful additives. Jowar is a nutrient-dense ancient grain known for being rich in dietary fiber, protein, and essential minerals like iron and phosphorus. These noodles are perfect for those seeking a gluten-free lifestyle or a low-glycemic index food option. The texture is smooth and satisfying, pairing perfectly with the included seasoning or your favorite homemade sauce. Easy to prepare in just a few minutes, they are an ideal choice for busy professionals, students, and health-conscious families looking for a wholesome meal. This product is 100% natural, vegan-friendly, and contains no preservatives, making it a nutritious addition to your pantry. Enjoy a bowl of savory goodness that promotes better digestion and provides sustained energy levels throughout the day with every bite.</v>
+      </c>
+      <c r="J221" t="str">
+        <v>https://milletamma.com/</v>
+      </c>
+      <c r="K221" t="str">
+        <v>little-millet-pasta2</v>
+      </c>
+      <c r="L221" t="str">
+        <v>Jowar Millet Instant Noodles - 175gm</v>
+      </c>
+      <c r="M221" t="str">
+        <v>Jowar Noodles, Millet Noodles, Instant Noodles, Healthy Snacks, Gluten Free, No Maida Noodles, Sorghum Noodles, Millet Amma, Ready to Cook, Healthy Breakfast, Diet Food, Low Glycemic, High Fiber, Protein Rich, Vegan Noodles, Natural Food, Guilt Free Snacks, Quick Meals, Indian Millets, Superfood, Weight Loss Food, Nutritious Noodles, Kids Lunchbox, Healthy Dinner, Organic Noodles, No Preservatives, Ancient Grains, Iron Rich, Digestive Health, Energy Boosting, Millet Recipes, Jowar Benefits, Sorghum Flour, Instant Food Mix, Wholesome Meal, Savory Noodles, Gourmet Millet, Healthy Lifestyle, Clean Eating, Plant Based, Non GMO, Artisan Noodles, Tasty Millet, Easy Cooking, Nutritious Diet, Fiber Rich Food</v>
+      </c>
+      <c r="N221" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P221" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="b">
+        <v>0</v>
+      </c>
+      <c r="R221" t="b">
+        <v>0</v>
+      </c>
+      <c r="S221" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>f221</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Millet Amma</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Little Millet Instant Noodles - 175gm</v>
+      </c>
+      <c r="D222" t="str">
+        <v>http://milletamma.com/cdn/shop/products/14a_1200x1200.jpg?v=1738411663</v>
+      </c>
+      <c r="E222" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F222" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G222">
+        <v>160</v>
+      </c>
+      <c r="H222" t="str">
+        <v>175gm</v>
+      </c>
+      <c r="I222" t="str">
+        <v>Millet Amma’s Little Millet Instant Noodles offer a comforting and delicious meal option for those seeking a healthier alternative to traditional maida-based noodles. Crafted with 50% Little Millet flour and whole wheat flour, these noodles are a low glycemic index food, providing slow-digesting carbohydrates and high dietary fiber to help control blood sugar levels. Nutritionally dense, they are rich in magnesium for heart health, Vitamin B3 (niacin) to help lower cholesterol, and phosphorus to support weight loss and body tissue repair. The included tastemaker is a natural blend of cloves, coriander, ginger, cinnamon, cumin, and onion, garlic, and tomato powders, ensuring a flavorful experience without any artificial additives or preservatives. Perfect for a quick, wholesome meal, these noodles have a satisfying texture and can be prepared in minutes. For optimal freshness, store in a cool, dry place and move to an airtight container once opened. These noodles have a six-month shelf life, making them a convenient pantry staple for health-conscious families looking for nourishing, ready-to-cook options.</v>
+      </c>
+      <c r="J222" t="str">
+        <v>https://milletamma.com/</v>
+      </c>
+      <c r="K222" t="str">
+        <v>little-millet-pasta2</v>
+      </c>
+      <c r="L222" t="str">
+        <v>Little Millet Instant Noodles - 175gm</v>
+      </c>
+      <c r="M222" t="str">
+        <v>Little Millet Instant Noodles, Millet Amma, buy millets online, organic millet products, millet noodles, instant noodles, healthy noodles, gluten-free alternative, no maida, low glycemic index, dietary fiber, magnesium rich, heart health, vitamin B3, niacin, cholesterol management, phosphorus, weight loss, body tissue repair, energy production, natural ingredients, no artificial additives, no preservatives, ready to cook, kutki millet, slow digesting carbs, blood sugar control, wholesome pasta, nourishing meal, quick dinner, nutritious snack, healthy breakfast, millet recipes, indian millets, unpolished millets, fiber rich food, plant based protein, vegan noodles, easy to cook, 6 months shelf life</v>
+      </c>
+      <c r="N222" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P222" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="b">
+        <v>0</v>
+      </c>
+      <c r="R222" t="b">
+        <v>0</v>
+      </c>
+      <c r="S222" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>f222</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Millet Amma</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Little Millet Hakka Noodles 180gm</v>
+      </c>
+      <c r="D223" t="str">
+        <v>https://milletamma.com/cdn/shop/products/16a_1200x1200.jpg?v=1738921946</v>
+      </c>
+      <c r="E223" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F223" t="str">
+        <v>Instant Food Mix</v>
+      </c>
+      <c r="G223">
+        <v>170</v>
+      </c>
+      <c r="H223" t="str">
+        <v>180gm</v>
+      </c>
+      <c r="I223" t="str">
+        <v>Millet Amma’s Little Millet Hakka Noodles offer a delicious and nutritious alternative to traditional maida-based noodles. Crafted with the goodness of Little Millet, one of the ancient small millets known for its high nutritional value, these noodles are designed for those who seek comfort food without compromising on health. They are naturally rich in dietary fiber, minerals, and vitamins, making them an excellent choice for maintaining a healthy lifestyle. Unlike conventional instant noodles, this variant is free from harmful additives and refined flour, ensuring a low glycemic index and better digestion. The texture is smooth and satisfying, pairing perfectly with sautéed vegetables and savory sauces for a complete meal. Ideal for busy individuals or health-conscious families, these noodles are easy to prepare and cook in minutes. They provide sustained energy and are suitable for weight management and diabetic-friendly diets. Whether you are whipping up a quick snack or a wholesome dinner, Millet Amma ensures you enjoy the authentic taste of hakka noodles with the wholesome benefits of millets. This product is a testament to the brand's commitment to clean eating and traditional grains.</v>
+      </c>
+      <c r="J223" t="str">
+        <v>https://milletamma.com/</v>
+      </c>
+      <c r="K223" t="str">
+        <v>little-millet-pasta2</v>
+      </c>
+      <c r="L223" t="str">
+        <v>Jowar Millet Instant Noodles - 175gm</v>
+      </c>
+      <c r="M223" t="str">
+        <v>Little Millet, Hakka Noodles, Millet Amma, Healthy Noodles, No Maida, Gluten Free, High Fiber, Low GI Food, Instant Noodles, Ready To Cook, Millet Pasta, Nutritious Snacks, Whole Grain Noodles, Diabetic Friendly, Weight Loss Food, Natural Ingredients, Organic Food, Indian Millets, Healthy Lunch, Quick Meal, Guilt Free Eating, Small Millets, Fiber Rich, Vegan Noodles, Traditional Grains, Clean Label, No Preservatives, Healthy Alternative, Easy Cooking, Breakfast Ideas, Wholesome Food, Gourmet Noodles, Plant Based, Energy Booster, Kids Healthy Food, Diet Friendly, Smart Carbs, Ancient Grains, Superfood, Millet Recipes</v>
+      </c>
+      <c r="N223" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P223" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="b">
+        <v>0</v>
+      </c>
+      <c r="R223" t="b">
+        <v>0</v>
+      </c>
+      <c r="S223" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>f223</v>
+      </c>
+      <c r="B224" t="str">
+        <v>First Bud Organics</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Raw Comb Honey - Pure Organic Forest Honeycomb</v>
+      </c>
+      <c r="D224" t="str">
+        <v>http://firstbud.in/cdn/shop/files/combhoneyfront.png?v=1711548758</v>
+      </c>
+      <c r="E224" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F224" t="str">
+        <v>Whole Foods</v>
+      </c>
+      <c r="G224">
+        <v>999</v>
+      </c>
+      <c r="H224" t="str">
+        <v>500 gm</v>
+      </c>
+      <c r="I224" t="str">
+        <v>First Bud Organics Raw Comb Honey is a premium, 100% pure organic forest honeycomb sourced directly from the pristine Himalayan region. This natural raw honey features a thick, authentic layer of honeycomb preserved right inside the jar, offering a unique texture and flavor profile that mass-produced honey lacks. Rich in essential antioxidants and minerals, this comb honey supports overall wellness and provides a natural energy boost. It is highly effective in improving cholesterol levels and aiding in better digestion. The honey is unprocessed, ensuring that all the natural enzymes and pollen remain intact for maximum nutritional benefit. Perfect for spreading on toast, adding to cheese platters, or enjoying straight from the spoon, it delivers a rich, floral sweetness and a satisfying chewy texture from the wax. This product is a testament to purity, being free from additives or artificial preservatives. Experience the unadulterated taste of the forest with this exquisite, nutrient-dense superfood that brings the health benefits of the hive directly to your table.</v>
+      </c>
+      <c r="J224" t="str">
+        <v>https://firstbud.in/</v>
+      </c>
+      <c r="K224" t="str">
+        <v>first-bud-raw-comb-honey</v>
+      </c>
+      <c r="L224" t="str">
+        <v>Raw Comb Honey - Pure Organic Forest Honeycomb</v>
+      </c>
+      <c r="M224" t="str">
+        <v>Raw Comb Honey, Organic Honeycomb, Himalayan Honey, Pure Raw Honey, Forest Honey, Natural Sweetener, Antioxidant Rich, Digestive Health, Cholesterol Support, First Bud Organics, Unprocessed Honey, Healthy Superfood, Gourmet Honey, Honey with Wax, Nutrient Dense, Floral Honey, Sustainable Sourcing, Premium Honey, Organic Pantry, Himalayan Superfood, Natural Energy, Wellness Product, Honey Jar, Authentic Honey, No Added Sugar, Chemical Free, Healthy Snacks, Breakfast Toppings, Artisan Honey, Immunity Booster</v>
+      </c>
+      <c r="N224" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P224" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="b">
+        <v>0</v>
+      </c>
+      <c r="R224" t="b">
+        <v>0</v>
+      </c>
+      <c r="S224" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>f224</v>
+      </c>
+      <c r="B225" t="str">
+        <v>First Bud Organics</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Organic Tulsi Honey - 100% Natural Unprocessed Tulsi Honey</v>
+      </c>
+      <c r="D225" t="str">
+        <v>http://firstbud.in/cdn/shop/files/B0CQQZF1QP.MAINIMAGE.jpg?v=1709535364</v>
+      </c>
+      <c r="E225" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F225" t="str">
+        <v>Whole Foods</v>
+      </c>
+      <c r="G225">
+        <v>545</v>
+      </c>
+      <c r="H225" t="str">
+        <v>500g</v>
+      </c>
+      <c r="I225" t="str">
+        <v>First Bud Organics presents its premium Organic Tulsi Honey, a 100% natural and unprocessed treasure collected directly from the nectar of Tulsi (Holy Basil) flowers. This honey is prized for its unique soothing and rejuvenating qualities, making it a staple in Ayurvedic wellness practices. Unlike commercial honey, it remains raw and unfiltered, preserving all the vital enzymes, antioxidants, and minerals provided by nature. The flavor profile is distinct, with subtle herbal notes of Tulsi that complement its natural sweetness, providing a smooth and rich texture that melts on the tongue. This superfood acts as a potent immunity booster and a natural remedy for respiratory health, often used to soothe coughs and sore throats. It is free from added sugars, preservatives, or artificial flavors, ensuring you receive only the purest form of honey. Perfect for drizzling over cereals, mixing into warm teas, or enjoying straight from the spoon, First Bud Organics Tulsi Honey is a healthy alternative to refined sugar. Certified organic and sustainably sourced, this honey supports both your health and the environment.</v>
+      </c>
+      <c r="J225" t="str">
+        <v>https://firstbud.in/</v>
+      </c>
+      <c r="K225" t="str">
+        <v>first-bud-raw-comb-honey</v>
+      </c>
+      <c r="L225" t="str">
+        <v>Organic Tulsi Honey - 100% Natural Unprocessed Tulsi Honey</v>
+      </c>
+      <c r="M225" t="str">
+        <v>Organic, Tulsi Honey, Natural Honey, Raw Honey, Unprocessed Honey, Healthy Sweetener, Immunity Booster, First Bud Organics, Pure Honey, Ayurvedic Honey, Medicinal Honey, Antioxidant Rich, Sugar Substitute, Eco-friendly Packaging, Sustainably Sourced, Tulsi Infused, Herbal Honey, Cold Pressed Honey, Non-GMO, No Added Sugar, Healthy Living, Wellness, Superfood, Natural Healing, Detox, Morning Ritual, Tea Sweetener, Forest Honey, Wild Honey, Bee Honey, Organic Certified, Indian Honey, Traditional Honey, Health Supplement, Nutritious, Energy Booster, Cough Relief, Throat Soother, Rejuvenating Honey, Nutrient Dense, Floral Nectar, Glass Jar Honey, Gourmet Honey, Pesticide Free, Chemical Free, Farm Fresh</v>
+      </c>
+      <c r="N225" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P225" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="b">
+        <v>0</v>
+      </c>
+      <c r="R225" t="b">
+        <v>0</v>
+      </c>
+      <c r="S225" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>f225</v>
+      </c>
+      <c r="B226" t="str">
+        <v>First Bud Organics</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Jamun Honey</v>
+      </c>
+      <c r="D226" t="str">
+        <v>https://firstbud.in/cdn/shop/files/Artboard0.jpg?v=1711526050</v>
+      </c>
+      <c r="E226" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F226" t="str">
+        <v>Whole Foods</v>
+      </c>
+      <c r="G226">
+        <v>499</v>
+      </c>
+      <c r="H226" t="str">
+        <v>500 gm</v>
+      </c>
+      <c r="I226" t="str">
+        <v>Indulge in the delightful sweetness of nature with our Jamun Honey, a 100% organic and raw product sourced from pristine orchards where Indian Black Plum (Jamun) trees flourish. Crafted by bees gathering nectar from Jamun blossoms, this honey captures a rich, fruity flavor and exceptional taste. Meticulously harvested and unprocessed, it retains all its natural nutrients, enzymes, and antioxidants. Known for helping improve liver function and gut health, this honey is a natural alternative to refined sugar with a unique woody and fruity profile. Our Jamun Honey is ideal for those seeking a healthy lifestyle and can be consumed directly, mixed with warm water, or used as a natural sweetener in desserts and beverages. Experience the pure goodness of nature's nectar, certified for its organic quality and harvested with care to ensure the highest standards of purity.</v>
+      </c>
+      <c r="J226" t="str">
+        <v>https://firstbud.in/</v>
+      </c>
+      <c r="K226" t="str">
+        <v>first-bud-raw-comb-honey</v>
+      </c>
+      <c r="L226" t="str">
+        <v>Jamun Honey</v>
+      </c>
+      <c r="M226" t="str">
+        <v>Jamun Honey, Organic Honey, Raw Honey, Pure Jamun Honey, First Bud Organics, Natural Sweetener, Liver Health, Gut Health, Indian Black Plum Honey, Fruity Honey, Healthy Food, Antioxidant Rich Honey, Unprocessed Honey, Wild Honey, Ayurvedic Honey, Immunity Booster, Jamun Fruit Nectar, Buy Honey Online India, Healthy Sugar Substitute, Premium Honey, Sustainable Harvesting, Nutritious Food, Low GI Sweetener, Diabetic Friendly Food, Whole Foods, Natural Healing, Wellness Products, Organic Certified, First Bud Honey, Artisanal Honey</v>
+      </c>
+      <c r="N226" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P226" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="b">
+        <v>0</v>
+      </c>
+      <c r="R226" t="b">
+        <v>0</v>
+      </c>
+      <c r="S226" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>f226</v>
+      </c>
+      <c r="B227" t="str">
+        <v>First Bud Organics</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Pahadi Honey - 100% Organic Raw Honey (250g) Unprocessed</v>
+      </c>
+      <c r="D227" t="str">
+        <v>https://firstbud.in/cdn/shop/files/pahaadihoney250.webp?v=1713195851</v>
+      </c>
+      <c r="E227" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F227" t="str">
+        <v>Whole Foods</v>
+      </c>
+      <c r="G227">
+        <v>299</v>
+      </c>
+      <c r="H227" t="str">
+        <v>250 gm</v>
+      </c>
+      <c r="I227" t="str">
+        <v>First Bud Organics Pahadi Honey is a 100% natural, organic raw honey meticulously sourced from the pristine, wild forests of the Himalayan mountains. This high-quality product is NMR tested to ensure absolute authenticity and purity, providing consumers with a trustworthy and premium honey experience. Being completely unprocessed, it retains all its natural enzymes, antioxidants, and nutritional benefits that are often lost in industrial heat treatment. It contains no added preservatives, artificial colors, or flavors, making it a healthy alternative to refined sugar. The texture is smooth and rich, with a flavor profile that captures the diverse floral essence of the Himalayan landscape. Ideal for boosting immunity and providing a quick energy source, this honey can be used in teas, breakfasts, or as a natural sweetener in various recipes. Its medicinal properties are well-regarded in traditional wellness practices. This honey is not just a sweetener but a superfood that supports a healthy lifestyle. Each jar represents a commitment to purity and sustainable sourcing practices directly from nature.</v>
+      </c>
+      <c r="J227" t="str">
+        <v>https://firstbud.in/</v>
+      </c>
+      <c r="K227" t="str">
+        <v>first-bud-raw-comb-honey</v>
+      </c>
+      <c r="L227" t="str">
+        <v>Pahadi Honey - 100% Organic Raw Honey (250g) Unprocessed</v>
+      </c>
+      <c r="M227" t="str">
+        <v>Honey, Organic Honey, Raw Honey, Pahadi Honey, First Bud Organics, Himalayan Honey, NMR Tested Honey, Unprocessed Honey, Natural Sweetener, Healthy Food, Pure Honey, No Added Sugar, Preservative Free, Immune Booster, Energy Source, Traditional Honey, Forest Honey, Wild Honey, Ayurvedic, Wellness, Organic Food India, High Quality Honey, Best Honey Brand, Breakfast Essential, Natural Medicine, Antioxidant Rich, Sustainable Sourcing, Farm to Table, Superfood, Nutritious, Sweetener, Baking Ingredient, Tea Sweetener, Healthy Lifestyle, First Bud, Authentic Honey, Non-GMO, Eco Friendly, Local Produce</v>
+      </c>
+      <c r="N227" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P227" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="b">
+        <v>0</v>
+      </c>
+      <c r="R227" t="b">
+        <v>0</v>
+      </c>
+      <c r="S227" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>f227</v>
+      </c>
+      <c r="B228" t="str">
+        <v>First Bud Organics</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Pahadi Honey - 100% Unprocessed Organic Raw Honey (500g)</v>
+      </c>
+      <c r="D228" t="str">
+        <v>https://firstbud.in/cdn/shop/files/B076Q531B1.MAINIMAGE_b079b2b8-9a7e-4336-a91f-ebcc123bac5c.jpg?v=1711526540</v>
+      </c>
+      <c r="E228" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F228" t="str">
+        <v>Whole Foods</v>
+      </c>
+      <c r="G228">
+        <v>499</v>
+      </c>
+      <c r="H228" t="str">
+        <v>500g</v>
+      </c>
+      <c r="I228" t="str">
+        <v>First Bud Organics Pahadi Honey is a premium, 100% natural, and unprocessed raw honey sourced directly from the pristine Himalayan mountain ranges. This organic honey undergoes rigorous NMR testing to guarantee its absolute authenticity and purity, ensuring that every jar is free from adulteration, added sugars, or synthetic preservatives. Characterized by its deep golden hue and a rich, complex floral flavor profile, this honey preserves all the natural enzymes, antioxidants, and minerals often lost in commercial processing. Its smooth, thick texture makes it a delightful addition to breakfasts, teas, and healthy recipes. Beyond its exquisite taste, Pahadi Honey is celebrated for its medicinal properties, including boosting immunity, soothing sore throats, and aiding digestive health. This 500g jar is an ideal choice for health-conscious consumers seeking a wholesome, nutrient-dense alternative to refined sugar. Packaged in its most raw form, it retains the natural pollens and health-giving properties that nature intended. Whether used as a natural energy booster or a sweetener for gourmet desserts, this honey delivers a taste of the mountains in every spoonful, certified for the highest quality standards.</v>
+      </c>
+      <c r="J228" t="str">
+        <v>https://firstbud.in/</v>
+      </c>
+      <c r="K228" t="str">
+        <v>first-bud-raw-comb-honey</v>
+      </c>
+      <c r="L228" t="str">
+        <v>Pahadi Honey - 100% Unprocessed Organic Raw Honey (500g)</v>
+      </c>
+      <c r="M228" t="str">
+        <v>First Bud Organics, Pahadi Honey, Raw Honey, Organic Honey, Unprocessed Honey, Himalayan Honey, NMR Tested Honey, Natural Sweetener, Pure Honey, 500g Jar, Health Food, Immunity Booster, Antioxidant Rich, No Preservatives, Natural Enzymes, Wildflower Honey, Mountain Honey, Authentic Honey, Sugar Substitute, Healthy Living, Organic Food, Nutrient Dense, Raw Organic Honey, Sustainably Sourced, Premium Honey, Dessert Topping, Breakfast Essential, Wholesome Food, Natural Energy, Digestion Aid, Cold Pressed Honey, Non-GMO Honey, Lab Tested Honey, Ayurvedic Honey, Forest Honey, Pure Raw Honey, Sweetener, Healthy Pantry, Indian Organic Food, Local Honey, High Altitude Honey</v>
+      </c>
+      <c r="N228" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P228" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q228" t="b">
+        <v>0</v>
+      </c>
+      <c r="R228" t="b">
+        <v>0</v>
+      </c>
+      <c r="S228" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>f228</v>
+      </c>
+      <c r="B229" t="str">
+        <v>First Bud Organics</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Home Made Rajasthani Mango Pickle - 500 gm / Single</v>
+      </c>
+      <c r="D229" t="str">
+        <v>https://firstbud.in/cdn/shop/files/1_82d751f0-29f6-4840-914a-f42563c674cc.jpg?v=1711526479</v>
+      </c>
+      <c r="E229" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F229" t="str">
+        <v>Condiments &amp; Sauces</v>
+      </c>
+      <c r="G229">
+        <v>449</v>
+      </c>
+      <c r="H229" t="str">
+        <v>500 gm / Single</v>
+      </c>
+      <c r="I229" t="str">
+        <v>Experience the timeless delight of First Bud Organics' Home Made Mango Pickle, a traditional Rajasthani masterpiece. Crafted using 100% organic ingredients, this pickle features a secret recipe passed down through generations. It is infused with a spicy blend of raw mangoes and premium spices, delivering a tangy and savory flavor profile that enhances every meal. This homemade Aam Ka Achar is completely free from chemicals, artificial preservatives, and additives, ensuring pure goodness in every jar. The mango pieces are carefully selected for their quality and texture, then marinated in cold-pressed mustard oil to lock in the authentic aroma. Perfect for pairing with parathas, rice, or any Indian cuisine, it offers a rich nutritional profile including antioxidants from spices. Each batch is carefully packed and sealed to preserve its freshness. This product is certified for its quality and natural sourcing, making it a wholesome addition to your daily diet.</v>
+      </c>
+      <c r="J229" t="str">
+        <v>https://firstbud.in/</v>
+      </c>
+      <c r="K229" t="str">
+        <v>first-bud-raw-comb-honey1</v>
+      </c>
+      <c r="L229" t="str">
+        <v>Home Made Rajasthani Mango Pickle - 500 gm / Single</v>
+      </c>
+      <c r="M229" t="str">
+        <v>Organic Mango Pickle, Homemade Aam Ka Achar, Rajasthani Mango Pickle, Preservative Free Pickle, Natural Mango Pickle, Spicy Indian Condiment, First Bud Organics, Traditional Recipe, Handcrafted Pickle, Raw Mango Pickle, Healthy Condiment, Vegan Pickle, Gluten Free Pickle, Real Spices, Mustard Oil Pickle, Home Style Pickle, 500g Mango Pickle, Gourmet Indian Pickle, Side Dish, Indian Cuisine, Healthy Eating, Organic Food, Non GMO, Chemical Free, Artisan Pickle, Tangy Mango, Savory Pickle, Authentic Indian Taste, Breakfast Side</v>
+      </c>
+      <c r="N229" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P229" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q229" t="b">
+        <v>0</v>
+      </c>
+      <c r="R229" t="b">
+        <v>0</v>
+      </c>
+      <c r="S229" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>f229</v>
+      </c>
+      <c r="B230" t="str">
+        <v>First Bud Organics</v>
+      </c>
+      <c r="C230" t="str">
+        <v>First Bud Organics Mango Pickles 250 gm</v>
+      </c>
+      <c r="D230" t="str">
+        <v>https://firstbud.in/cdn/shop/files/1_82d751f0-29f6-4840-914a-f42563c674cc_3.webp?v=1713195172</v>
+      </c>
+      <c r="E230" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F230" t="str">
+        <v>Condiments &amp; Sauces</v>
+      </c>
+      <c r="G230">
+        <v>299</v>
+      </c>
+      <c r="H230" t="str">
+        <v>250 gm</v>
+      </c>
+      <c r="I230" t="str">
+        <v>First Bud Organics Homemade Mango Pickle is a timeless culinary delight crafted using a traditional secret recipe passed down through generations. This premium aam ka achar is made with organically sourced raw mangoes, sun-dried to perfection, and infused with a spicy, aromatic blend of high-quality spices. The pickle is free from harmful chemicals, artificial colors, and synthetic preservatives, ensuring a pure and authentic taste in every spoonful. Each jar is carefully packed and sealed to preserve its rich flavor profile and appetizing aroma, making it the perfect accompaniment to enrich any Indian meal, from parathas to rice dishes. It offers significant nutritional highlights as it contains natural ingredients known for digestive benefits. The texture is a delightful mix of firm mango pieces and a thick, spicy masala base. Certified for quality and taste, this homemade pickle brings the nostalgic flavor of grandmother's kitchen to your dining table, making every meal a truly delightful and wholesome experience.</v>
+      </c>
+      <c r="J230" t="str">
+        <v>https://firstbud.in/</v>
+      </c>
+      <c r="K230" t="str">
+        <v>first-bud-raw-comb-honey1</v>
+      </c>
+      <c r="L230" t="str">
+        <v>First Bud Organics Mango Pickles 250 gm</v>
+      </c>
+      <c r="M230" t="str">
+        <v>Mango Pickle, Aam Ka Achar, Organic Pickle, Homemade Pickle, First Bud Organics, Spicy Mango Pickle, Raw Mango Pickle, Indian Condiments, Traditional Pickle, Chemical Free Pickle, Preservative Free, Natural Ingredients, Authentic Indian Taste, Gourmet Pickle, Side Dish, Indian Cuisine, Healthy Condiments, Sun Dried Mango, Premium Spices, Artisanal Pickle, Tangy Mango Pickle, Digestive Aid, Vegan Pickle, Gluten Free Pickle, Real Fruit Pickle, Lunch Accompaniment, Dinner Side, Breakfast Paratha Partner, Traditional Recipe, Handcrafted Pickle, Best Mango Pickle, Buy Pickle Online, Organic Food, Healthy Eating, Nutrient Rich, No Artificial Colors, Sealed Freshness, Aromatic Spices, Heritage Flavors, Indian Food Staples, Tangy and Spicy, Farm Fresh Mangoes, Small Batch Production</v>
+      </c>
+      <c r="N230" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P230" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q230" t="b">
+        <v>0</v>
+      </c>
+      <c r="R230" t="b">
+        <v>0</v>
+      </c>
+      <c r="S230" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>f230</v>
+      </c>
+      <c r="B231" t="str">
+        <v>First Bud Organics</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Spicy Lemon Pickle</v>
+      </c>
+      <c r="D231" t="str">
+        <v>http://firstbud.in/cdn/shop/files/1_87eaa2ae-9158-4cad-b767-2ed2ef80dbe2.webp?v=1705063841</v>
+      </c>
+      <c r="E231" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F231" t="str">
+        <v>Condiments &amp; Sauces</v>
+      </c>
+      <c r="G231">
+        <v>299</v>
+      </c>
+      <c r="H231" t="str">
+        <v>250 gm</v>
+      </c>
+      <c r="I231" t="str">
+        <v>Homemade spicy lemon pickle is a zesty and flavorful condiment crafted from fresh lemons, aromatic spices, and fiery chili peppers. This tangy delight offers a burst of bold flavors, combining the citrusy tang of lemons with the warmth of traditional Indian spices. Each bite delivers a tantalizing fusion of sour, spicy, and savory notes, making it a versatile accompaniment to a wide array of dishes. Whether paired with rice, bread, or savory snacks, this homemade delicacy adds a punch of zest to every culinary adventure. This 100% natural nimbu achar is made with fresh ingredients and contain no artificial preservatives or additives. It features a perfect balance of traditional spices and tangy lemons, providing nutritional benefits and a rich flavor profile. The texture is soft yet slightly firm, typical of well-matured traditional Indian pickles, and it is certified for its organic and high-quality standards.</v>
+      </c>
+      <c r="J231" t="str">
+        <v>https://firstbud.in/</v>
+      </c>
+      <c r="K231" t="str">
+        <v>first-bud-raw-comb-honey1</v>
+      </c>
+      <c r="L231" t="str">
+        <v>Spicy Lemon Pickle</v>
+      </c>
+      <c r="M231" t="str">
+        <v>Spicy Lemon Pickle, Organic Nimbu Achar, Homemade Pickle, No Preservatives, Natural Lemon Pickle, Tangy Pickle, Indian Spices, Zesty Condiment, Fiery Chili Peppers, Traditional Indian Pickle, Authentic Flavor, Fresh Lemons, Healthy Pickle, Probiotic Food, Digestive Aid, Traditional Recipe, Spicy Condiment, Gourmet Pickle, Artisan Pickle, Preservative Free, Non-GMO, Organic Food, Indian Side Dish, Pickle Lovers, Savory Snack Accompaniment, Rice Side Dish, Bread Accompaniment, Traditional Spices, Pure Ingredients, Premium Quality, First Bud Organics</v>
+      </c>
+      <c r="N231" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P231" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q231" t="b">
+        <v>0</v>
+      </c>
+      <c r="R231" t="b">
+        <v>0</v>
+      </c>
+      <c r="S231" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>f231</v>
+      </c>
+      <c r="B232" t="str">
+        <v>First Bud Organics</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Stevia Drops Liquid 20 ml</v>
+      </c>
+      <c r="D232" t="str">
+        <v>https://firstbud.in/cdn/shop/files/1_b02f12a7-f654-4fda-bd19-7cc10e2800bd.jpg?v=1709482209</v>
+      </c>
+      <c r="E232" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F232" t="str">
+        <v>Diabetic / Low Sugar Food</v>
+      </c>
+      <c r="G232">
+        <v>350</v>
+      </c>
+      <c r="H232" t="str">
+        <v>20 ml</v>
+      </c>
+      <c r="I232" t="str">
+        <v>First Bud Organics Stevia Drops are a premium, 100% natural, and zero-calorie liquid sweetener derived from high-quality organic stevia plants. This plant-based sugar substitute is an excellent choice for health-conscious individuals and those managing diabetes, as it naturally sweetens without the guilt or health risks associated with added refined sugars. Each 20 ml bottle provides a concentrated sweetness that is perfect for enhancing the flavor of various dishes and beverages, including tea, coffee, smoothies, and desserts. The drops offer a clean, sweet taste without the bitter aftertaste often found in artificial sweeteners. With its zero-glycemic index, it helps maintain stable blood sugar levels while supporting weight management goals. This non-GMO, organic product caters to those prioritizing natural ingredients in their diet. Simply add a few drops to your favorite drink to enjoy a delicious, healthy sweetness. First Bud Organics ensures high standards of purity and quality, making these stevia drops a staple for any kitchen looking to reduce sugar intake without compromising on flavor.</v>
+      </c>
+      <c r="J232" t="str">
+        <v>https://firstbud.in/</v>
+      </c>
+      <c r="K232" t="str">
+        <v>first-bud-raw-comb-honey2</v>
+      </c>
+      <c r="L232" t="str">
+        <v>Stevia Drops Liquid 20 ml</v>
+      </c>
+      <c r="M232" t="str">
+        <v>Stevia Drops, Natural Sweetener, Sugar Free, Zero Calorie, First Bud Organics, Organic Stevia, Liquid Sweetener, Diabetic Friendly, Plant Based, Keto Friendly, Healthy Sugar Substitute, Low Glycemic, Natural Sugar Alternative, Weight Management, Non-GMO Sweetener, Pure Stevia, Coffee Sweetener, Tea Sweetener, Healthy Living, Wellness Product, Sugar Alternative, Stevia Rebaudiana, Low Carb Diet, Vegan Sweetener, No Artificial Sweeteners, Gluten Free, Natural Flavor, Baking Sweetener, Beverage Sweetener, Liquid Stevia Extract, First Bud, Organics India, Healthy Diet, Sugar Replacement, Concentrated Stevia, No Calories, Blood Sugar Support, Clean Eating, Fitness Supplements, Grocery Essentials, Pantry Staples, Best Stevia Liquid, Buy Stevia Online, Natural Health, Nutritive Sweetener</v>
+      </c>
+      <c r="N232" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P232" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q232" t="b">
+        <v>0</v>
+      </c>
+      <c r="R232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S232" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>f232</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Millet Namkeen - Desi Masala - 4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="D233" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1DesiMasalaMilletNamkeen_4ab62696-4992-429c-beb4-dab8471f0c66.jpg?v=1748495661</v>
+      </c>
+      <c r="E233" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F233" t="str">
+        <v>Snacks</v>
+      </c>
+      <c r="G233">
+        <v>255</v>
+      </c>
+      <c r="H233" t="str">
+        <v>4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="I233" t="str">
+        <v>Eat Better Co’s Crispy Millet Mixture in Desi Masala is a revolutionary take on the traditional Indian namkeen, meticulously crafted for the health-conscious snacker. This spicy and crunchy delight is made using nutrient-dense superfoods including Ragi, Jowar, and airy Rice crispies. Instead of deep-frying, these ingredients are expertly roasted to perfection alongside protein-rich peanuts and roasted channa, ensuring a satisfying crunch without the excess oil. Seasoned with a robust blend of organic Indian spices, it offers a chatpata flavor profile that perfectly balances heat and tang. This snack is naturally high in fiber and minerals, making it an excellent choice for weight management and health-conscious diets. It is free from preservatives, artificial colors, and palm oil, embodying a truly clean-label philosophy. Whether you are looking for a mid-day energy boost or a savory companion for your evening tea, this millet mixture provides guilt-free indulgence. The texture is light yet incredibly crunchy, delivering an authentic desi taste while supporting a modern, healthy lifestyle.</v>
+      </c>
+      <c r="J233" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K233" t="str">
+        <v>crispy-millet-mixture-namkeen</v>
+      </c>
+      <c r="L233" t="str">
+        <v>Millet Namkeen - Desi Masala - 4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="M233" t="str">
+        <v>Millet Namkeen, Healthy Snacks, Roasted Namkeen, Eat Better Co, Desi Masala Snack, Ragi Snacks, Jowar Mixture, Low Calorie Snacks, Tea Time Snacks, Gluten Free Namkeen, Indian Savory Snacks, High Fiber Snacks, Guilt Free Snacking, Organic Spices, No Palm Oil Snacks, Roasted Millet Mixture, Healthy Indian Namkeen, Crunchy Snacks, Chatpata Snacks, Diet Friendly Food, Superfood Snacks, Vegan Snacks India, Nutritious Munchies, Weight Loss Snacks, Protein Rich Namkeen, Zero Trans Fat, Healthy Mixture, Traditional Indian Snacks, Baked Namkeen, Natural Ingredients, Clean Label Snacks, Savoury Millet Mix, Crispy Millet Snack, Healthy Finger Food, Evening Snacks, Spicy Roasted Mix, Non Fried Snacks, Mast Masala, Superfood Mixture, Healthy Bites, Indian Namkeen, Roasted Snacks, Fiber Rich, Nutrient Dense, Diabetic Friendly, Healthy Munchies, All Natural, Plant Based, Savory Treats</v>
+      </c>
+      <c r="N233" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P233" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="b">
+        <v>0</v>
+      </c>
+      <c r="R233" t="b">
+        <v>0</v>
+      </c>
+      <c r="S233" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>f233</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Millet Namkeen - Pudina Punch - 4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="D234" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1PudinaPunchMilletNamkeen.jpg?v=1748495778</v>
+      </c>
+      <c r="E234" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F234" t="str">
+        <v>Snacks</v>
+      </c>
+      <c r="G234">
+        <v>255</v>
+      </c>
+      <c r="H234" t="str">
+        <v>4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="I234" t="str">
+        <v>Eat Better Co’s Millet Namkeen in Pudina Punch flavor is a nutritional powerhouse designed for guilt-free snacking. This crispy mixture is expertly crafted using a blend of ancient superfoods, including Ragi, Jowar, and Rice crispies, which are perfectly roasted alongside protein-rich peanuts and channa. Seasoned with a zesty mix of organic Indian spices and a refreshing hit of mint, this namkeen offers a delightful chatpata taste and a satisfyingly crunchy texture. It is a wholesome alternative to traditional deep-fried snacks, providing high fiber and essential minerals. Ideal for weight-conscious individuals and those seeking a healthy tea-time accompaniment, this snack is 100% natural and free from harmful preservatives. The Pudina Punch variant delivers a cooling yet spicy flavor profile that invigorates the palate. Each bite is packed with the goodness of millets, ensuring sustained energy levels throughout the day. Whether you are at work or home, this healthy namkeen is your go-to solution for mid-day cravings, offering both health and taste in every mouthful.</v>
+      </c>
+      <c r="J234" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K234" t="str">
+        <v>crispy-millet-mixture-namkeen</v>
+      </c>
+      <c r="L234" t="str">
+        <v>Millet Namkeen - Pudina Punch - 4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="M234" t="str">
+        <v>Millet Namkeen, Healthy Snacks, Pudina Punch, Eat Better Co, Roasted Namkeen, Gluten-Free Snacks, Ragi Snacks, Jowar Snacks, Indian Savoury Snacks, Weight Loss Snacks, Low Calorie Namkeen, High Protein Snacks, Tea Time Snacks, Healthy Indian Mixture, Superfood Snacks, Natural Ingredients, No Preservatives, Mint Flavor Snacks, Crispy Millet Mixture, Chatpata Snacks, Vegan Snacks India, Guilt-Free Snacking, Healthy Namkeen Online, Nutritious Munchies, Roasted Peanuts and Channa, Organic Spices, High Fiber Snacks, Non-Fried Snacks, Traditional Indian Snacks Healthy, Diet Friendly Snacks, Breakfast Millets, Savoury Millet Snacks, Pudina Namkeen, Millet Mixture, Eat Better Snacks, Healthy Food India, Snacks for Diabetes, Heart Healthy Snacks, Daily Snack, Fitness Snacks, Energy Boosting Snacks, Pack of 4 Snacks</v>
+      </c>
+      <c r="N234" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P234" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q234" t="b">
+        <v>0</v>
+      </c>
+      <c r="R234" t="b">
+        <v>0</v>
+      </c>
+      <c r="S234" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>f234</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Millet Namkeen - Mango Achaari - 4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="D235" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1MangoAchariMilletnamkeen.jpg?v=1748495515</v>
+      </c>
+      <c r="E235" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F235" t="str">
+        <v>Snacks</v>
+      </c>
+      <c r="G235">
+        <v>255</v>
+      </c>
+      <c r="H235" t="str">
+        <v>4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="I235" t="str">
+        <v>Eat Better Co’s Crispy Millet Mixture in Mango Achaari flavor is a delicious, crunchy, and chatpata alternative to traditional deep-fried snacks like Chivda or Bhujia. Crafted with wholesome superfoods including Ragi, Jowar, and Rice crispies, this mixture is roasted with peanuts and channa to provide a satisfying crunch. The snack is seasoned with organic Indian spices and a zesty mango pickle twist, offering a unique aromatic and tangy flavor profile. Unlike conventional snacks, it is roasted in sunflower oil and is completely free from palm oil, making it a heart-healthy choice. This nutritious namkeen is perfect for on-the-go snacking, office breaks, school lunchboxes, or as an evening treat with tea. It highlights the nutritional benefits of millets, being high in fiber and essential minerals. The texture is light and crispy, ensuring a guilt-free indulgence. It is a vegan-friendly and gluten-free option for those looking to maintain a balanced lifestyle without compromising on taste. Each pack delivers a burst of authentic Indian flavor in every bite.</v>
+      </c>
+      <c r="J235" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K235" t="str">
+        <v>crispy-millet-mixture-namkeen</v>
+      </c>
+      <c r="L235" t="str">
+        <v>Millet Namkeen - Mango Achaari - 4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="M235" t="str">
+        <v>Healthy Snacks, Millet Namkeen, Mango Achaari, Roasted Snacks, Ragi Snack, Jowar Snack, Rice Crispies, Peanuts, Channa, Indian Spices, Savoury Snacks, Guilt-Free Snacking, No Palm Oil, Gluten Free, High Fiber, Protein Rich, Tea Time Snacks, Evening Snacks, Lunchbox Snacks, On The Go Snacks, Vegan Snacks, Natural Ingredients, Organic Spices, Chatpata Snack, Traditional Flavors, Healthy Chivda, Healthy Bhujia, Crunchy Snacks, Achaari Flavor, Eat Better Co, Superfoods, Diet Friendly, Low Calorie, Nutritious Munchies, Indian Namkeen, Savoury Mixture, Crispy Millet, Whole Foods, Plant Based</v>
+      </c>
+      <c r="N235" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P235" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q235" t="b">
+        <v>0</v>
+      </c>
+      <c r="R235" t="b">
+        <v>0</v>
+      </c>
+      <c r="S235" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>f235</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Millet Namkeen - Chilli Garlic</v>
+      </c>
+      <c r="D236" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1ChilligarlicMilletNamkeen.jpg?v=1748495446</v>
+      </c>
+      <c r="E236" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F236" t="str">
+        <v>Snacks</v>
+      </c>
+      <c r="G236">
+        <v>255</v>
+      </c>
+      <c r="H236" t="str">
+        <v>4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="I236" t="str">
+        <v>Eat Better Co Crispy Millet Mixture in Chilli Garlic flavor is a revolutionary take on traditional Indian namkeen. Crafted with a powerhouse blend of superfood millets including Ragi, Jowar, and crunchy rice crispies, this snack is thoughtfully roasted to perfection rather than deep-fried. The mix is enriched with high-quality peanuts and channa, providing a satisfying protein boost. Seasoned with organic Indian spices, it delivers a bold kick of chilli balanced by the aromatic depth of garlic, making it a perfect chatpata alternative to unhealthy Chivda or Bhujia. This 100% natural, low Glycemic Index (GI) snack is specifically designed for health-conscious consumers and those on weight loss journeys. Packed with essential minerals like iron and calcium, it offers nutritional benefits alongside its addictive crunch. Ideal for anytime munching, the mixture is free from artificial preservatives and refined oils. Whether you are looking for a tea-time companion or a post-workout savory treat, this millet namkeen provides a guilt-free experience. The texture is light and crispy, ensuring every bite is flavorful and nourishing.</v>
+      </c>
+      <c r="J236" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K236" t="str">
+        <v>crispy-millet-mixture-namkeen</v>
+      </c>
+      <c r="L236" t="str">
+        <v>Chilli Garlic - 4 PaMillet Namkeen - Chilli Garlicckets (4 x 100 grams)</v>
+      </c>
+      <c r="M236" t="str">
+        <v>Eat Better Co, Healthy Namkeen, Millet Mixture, Chilli Garlic Snack, Roasted Snacks, Ragi Snacks, Jowar Snacks, High Protein Snack, Low GI Food, Weight Loss Snacks, Healthy Indian Snacks, Chatpata Namkeen, No Preservatives, Organic Spices, Vegan Snacks, Gluten Free Snacks, Tea Time Snacks, Healthy Chivda Alternative, Iron Rich Snacks, Calcium Rich Snacks, Nutrient Dense, Guilt Free Munching, Natural Ingredients, Superfood Snacks, Roasted Peanuts, Roasted Channa, Indian Savory Mix, Healthy Diet Food, Crunchy Millet Snack, Savoury Snacks, Garlic Infused Snacks, Spicy Namkeen</v>
+      </c>
+      <c r="N236" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P236" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q236" t="b">
+        <v>0</v>
+      </c>
+      <c r="R236" t="b">
+        <v>0</v>
+      </c>
+      <c r="S236" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>f236</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Millet Bhujia - Pudina Masti (2*100 grams)</v>
+      </c>
+      <c r="D237" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1-_15.jpg?v=1749547728</v>
+      </c>
+      <c r="E237" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F237" t="str">
+        <v>Snacks</v>
+      </c>
+      <c r="G237">
+        <v>179</v>
+      </c>
+      <c r="H237" t="str">
+        <v>4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="I237" t="str">
+        <v>Experience a crunchy, joyful twist on the classic Indian Bhujia with Eat Better Co’s Millet Bhujia in Pudina Masti flavor. This snack is meticulously crafted using wholesome millets and a blend of aromatic spices, then roasted to perfection rather than deep-fried to ensure a healthier profile. Infused with the refreshing essence of mint, it offers a crispy texture and a burst of flavor in every bite. Ideal for those seeking a guilt-free munching option, this bhujia is a great source of fiber and energy. It is free from palm oil and artificial preservatives, making it a nutritious addition to your tea-time or any time you crave a savory treat. Each pack contains two 100g servings, ensuring freshness and portion control. Enjoy the authentic taste of tradition reimagined with modern health standards. Perfect for all ages, this Pudina Masti bhujia is set to become your favorite go-to snack for daily refreshment and delight. The combination of millets and mint provides a unique sensory experience that satisfies cravings while being light on the stomach.</v>
+      </c>
+      <c r="J237" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K237" t="str">
+        <v>crispy-millet-mixture-namkeen</v>
+      </c>
+      <c r="L237" t="str">
+        <v>Millet Bhujia - Pudina Masti (2*100 grams)</v>
+      </c>
+      <c r="M237" t="str">
+        <v>Millet Bhujia, Pudina Masti, Healthy Snacks, Roasted Snacks, Gluten Free Snacks, Eat Better Co, Mint Flavored Snacks, Tea Time Snacks, Indian Savory Snacks, Low Calorie Snacks, Vegan Snacks, Natural Ingredients, No Palm Oil, High Fiber Snacks, Millet Based Food, Crispy Bhujia, Healthy Indian Namkeen, Weight Loss Snacks, Diet Friendly Snacks, Traditional Snacks with a Twist, Nutritious Munchies, guilt free snacking, aromatic spices, wholesome ingredients, crunchy texture, refreshing mint, savory treats, daily snacks, festive snacks, pack of 2, healthy munching, roasted bhujia, fiber rich, travel snacks, tea time accompaniment, guilt-free treats, snacks for kids, wholesome snacking, pudina bhujia, snack pack, healthy gifts</v>
+      </c>
+      <c r="N237" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P237" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q237" t="b">
+        <v>0</v>
+      </c>
+      <c r="R237" t="b">
+        <v>0</v>
+      </c>
+      <c r="S237" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>f237</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Quinoa Namkeen - Chilli Lime - 4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="D238" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1QuinoaNamkeenChilliLime.jpg?v=1748944798</v>
+      </c>
+      <c r="E238" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F238" t="str">
+        <v>Snacks</v>
+      </c>
+      <c r="G238">
+        <v>369</v>
+      </c>
+      <c r="H238" t="str">
+        <v>4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="I238" t="str">
+        <v>Satisfy your cravings with a burst of flavor and wholesome goodness in every bite with our Chilli Lime Quinoa Namkeen Mixture. Expertly crafted and made from nutritious superfoods, this savory snack combines the tangy zest of lime with a hint of chilli heat for an irresistible taste experience. It is made with high-quality ingredients including Quinoa, Rice crispies, peanuts, Pumpkin seeds, and a specialized Chilli &amp; Lime seasoning, all roasted in sunflower oil to ensure a nutritious snack time. Unlike traditional snacks, this namkeen is roasted, not fried, and is completely free from palm oil and harmful additives. It serves as a perfect, crunchy, and chatpata alternative to unhealthy Chivda, Bhujia, or chips. Packed with essential nutrients like protein, iron, and calcium, it supports muscle health, boosts energy, and improves overall wellness. This snack is ideal for on-the-go snacking, lunchboxes, or evening treats. It is certified for quality and offers a unique texture that is both crispy and satisfying, making it a favorite for both kids and adults looking for a healthier lifestyle choice.</v>
+      </c>
+      <c r="J238" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K238" t="str">
+        <v>crispy-millet-mixture-namkeen</v>
+      </c>
+      <c r="L238" t="str">
+        <v>Quinoa Namkeen - Chilli Lime - 4 Packets (4 x 100 grams)</v>
+      </c>
+      <c r="M238" t="str">
+        <v>Healthy Snacks, Quinoa Namkeen, Chilli Lime Snack, Roasted Namkeen, No Palm Oil, Protein Rich Snacks, Gluten Free Snacks, Healthy Indian Namkeen, Eat Better Co, Savoury Snacks, Guilt Free Snacking, Superfood Snacks, Ragi Jowar Snack, Vegan Snacks, Low Calorie Snacks, Tea Time Snacks, Healthy Munchies, Natural Ingredients, No Preservatives, Iron Rich Food, Calcium Rich Snacks, Weight Loss Snacks, Diet Friendly, Chatpata Snack, Crispy Mixture, Nutrient Dense, Fitness Snacks, Kids Healthy Snacks, Office Snacks, Travel Snacks, Gourmet Snacks, Artisan Snacks, Plant Based Protein, Healthy Lifestyle, Wholesome Food, Non Fried Snacks, Energy Boosting, Healthy Cravings, Tangy Snacks, Spicy Snacks</v>
+      </c>
+      <c r="N238" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P238" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q238" t="b">
+        <v>0</v>
+      </c>
+      <c r="R238" t="b">
+        <v>0</v>
+      </c>
+      <c r="S238" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>f238</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Hazelnut Chocolate Laddoos - No Added Sugar | Dates, Dry-Fruits &amp; Nuts</v>
+      </c>
+      <c r="D239" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1HazelnutChocolateDatesandDryFruitLaddoo.jpg?v=1748424682</v>
+      </c>
+      <c r="E239" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F239" t="str">
+        <v>Sweets / Desserts</v>
+      </c>
+      <c r="G239">
+        <v>129</v>
+      </c>
+      <c r="H239" t="str">
+        <v>7 Laddoos (70 gm Pack)</v>
+      </c>
+      <c r="I239" t="str">
+        <v>Hazelnut Chocolate Laddoos by Eat Better Co are a premium, guilt-free treat designed to satisfy sweet cravings without the sugar crash. These nutrient-dense energy balls are crafted using a 100% natural blend of dates, hazelnuts, almonds, cacao, vanilla extract, chia seeds, and a pinch of sea salt. Free from added sugar, artificial flavors, and preservatives, they offer a wholesome snacking experience suitable for both adults and children. The texture is a delightful combination of soft, chewy dates and crunchy nuts, while the flavor profile is dominated by rich, earthy cacao and toasted hazelnuts. These laddoos are vegan, gluten-free, and high in fiber and healthy fats, making them an excellent pre-workout snack or post-meal dessert. Every bite is packed with antioxidants from cacao and the goodness of plant-based protein. Certified natural and sustainably sourced, these treats represent a modern take on traditional Indian sweets, prioritizing health without compromising on the classic, indulgent taste of a chocolate-nut pairing.</v>
+      </c>
+      <c r="J239" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K239" t="str">
+        <v>crispy-millet-mixture-namkeen1</v>
+      </c>
+      <c r="L239" t="str">
+        <v>Hazelnut Chocolate Laddoos - No Added Sugar | Dates, Dry-Fruits &amp; Nuts</v>
+      </c>
+      <c r="M239" t="str">
+        <v>Hazelnut Chocolate Laddoos, Healthy Laddoos, No Added Sugar, Vegan Sweets, Gluten Free Snacks, Eat Better Co, Dry Fruit Laddu, Date Based Sweets, Healthy Desserts, Natural Energy Balls, Cacao Laddoos, Nutty Snacks, Kids Healthy Snacks, Preservative Free, High Fiber, Plant Based Protein, Hazelnut Snacks, Chia Seed Laddu, Guilt Free Dessert, Indian Healthy Sweets, Better Laddoos, Clean Label Food, Whole Food Snacks, Superfood Treats, Artisanal Laddoos, Nutrient Dense, Healthy Gifting, Keto Friendly Sweets, Sugar Free Chocolate, High Energy Snack</v>
+      </c>
+      <c r="N239" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P239" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q239" t="b">
+        <v>0</v>
+      </c>
+      <c r="R239" t="b">
+        <v>0</v>
+      </c>
+      <c r="S239" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>f239</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Peanut Chocolate Laddoos - No Added Sugar | Dates, Dry-Fruits &amp; Nuts Laddoo</v>
+      </c>
+      <c r="D240" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1PeanutChocolateDatesandDryFruitLaddoo.jpg?v=1748424977</v>
+      </c>
+      <c r="E240" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F240" t="str">
+        <v>Sweets / Desserts</v>
+      </c>
+      <c r="G240">
+        <v>79</v>
+      </c>
+      <c r="H240" t="str">
+        <v>7 Laddoos (70 gm Pack)</v>
+      </c>
+      <c r="I240" t="str">
+        <v>Eat Better Co's Peanut Chocolate Laddoos are a gourmet, health-conscious treat that perfectly marries the intense flavor of premium cacao with the crunch of roasted peanuts and cashews. Often likened to a healthy version of a Snickers bar, these laddoos are crafted using only the finest natural ingredients, including dates for natural sweetness, chia seeds for added nutrition, and a hint of vanilla and sea salt for a balanced finish. They are 100% natural, vegan, and gluten-free, containing absolutely no added sugar, artificial flavors, or preservatives. These nutrient-dense bites are rich in plant-based proteins and healthy fats, making them an ideal post-workout snack or a guilt-free dessert. The texture is a delightful mix of fudgy dates and chunky nut pieces, offering a satisfying mouthfeel. Whether you are managing blood sugar levels or simply seeking a cleaner lifestyle, these laddoos provide sustained energy and satisfy sweet cravings without the sugar crash. Each bite is a testament to clean eating and artisanal quality.</v>
+      </c>
+      <c r="J240" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K240" t="str">
+        <v>crispy-millet-mixture-namkeen1</v>
+      </c>
+      <c r="L240" t="str">
+        <v>Peanut Chocolate Laddoos - No Added Sugar | Dates, Dry-Fruits &amp; Nuts Laddoo</v>
+      </c>
+      <c r="M240" t="str">
+        <v>Peanut Chocolate Laddoos, Healthy Snacks, No Added Sugar, Vegan Desserts, Gluten Free Snacks, Date Based Sweets, Eat Better Co, Dry Fruit Laddu, High Protein Snacks, Snickers Alternative, Natural Energy Bites, Cacao Laddoos, Cashew Nut Snacks, Chia Seed Snacks, Clean Label Food, Indian Sweets, Healthy Mithai, Guilt Free Dessert, Low Glycemic Food, Nutty Chocolate Bites, Post Workout Snack, Mid Day Cravings, Artisan Sweets, Plant Based Treats, Healthy Gifting, Keto Friendly, Paleo Snacks, Superfood Bites, Antioxidant Rich, Sugar Free Laddoos, Fiber Rich Snacks, Kids Healthy Snacks, Office Snacks, Travel Friendly Food, Healthy Snacking India, Zero Preservatives, Nutrient Dense, Whole Food Snacks, Guilt-Free Treats</v>
+      </c>
+      <c r="N240" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P240" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="b">
+        <v>0</v>
+      </c>
+      <c r="R240" t="b">
+        <v>0</v>
+      </c>
+      <c r="S240" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>f240</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Vanilla Chocolate Laddoos - No Added Sugar | Dates, Dry-Fruits &amp; Nuts</v>
+      </c>
+      <c r="D241" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1VanillaChocolateDatesandDryFruitLaddoo.jpg?v=1748425113</v>
+      </c>
+      <c r="E241" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F241" t="str">
+        <v>Sweets / Desserts</v>
+      </c>
+      <c r="G241">
+        <v>129</v>
+      </c>
+      <c r="H241" t="str">
+        <v>7 Laddoos (70 gm Pack)</v>
+      </c>
+      <c r="I241" t="str">
+        <v>Eat Better Co presents Vanilla Chocolate Laddoos, a guilt-free indulgence that perfectly blends rich, creamy vanilla with smooth, deep cacao. These soft and chewy laddoos are handcrafted using premium ingredients like dates, almonds, cashews, and coconut, providing a naturally sweet profile without any added sugar. The addition of chia seeds adds a subtle crunch and nutritional boost, while a hint of sea salt balances the sweetness. These snacks are 100% natural, vegan, and gluten-free, making them an ideal choice for health-conscious individuals and those with dietary restrictions. Each bite offers a satisfying texture and a delightful flavor profile that satiates sweet cravings while providing sustained energy from dry fruits and nuts. Perfect as a midday snack, post-workout treat, or a healthy dessert alternative, these laddoos are free from preservatives and artificial additives, ensuring a wholesome experience that aligns with a clean-eating lifestyle. The inclusion of vanilla extract enhances the aromatic appeal, making it a gourmet snack for all ages.</v>
+      </c>
+      <c r="J241" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K241" t="str">
+        <v>crispy-millet-mixture-namkeen1</v>
+      </c>
+      <c r="L241" t="str">
+        <v>Vanilla Chocolate Laddoos - No Added Sugar | Dates, Dry-Fruits &amp; Nuts</v>
+      </c>
+      <c r="M241" t="str">
+        <v>Vanilla Chocolate Laddoos, No Added Sugar, Healthy Snacks, Eat Better Co, Dates Laddoos, Dry Fruit Laddoos, Vegan Sweets, Gluten Free Desserts, Cacao Laddoos, Vanilla Extract, Chia Seeds, Healthy Energy Balls, Natural Sweets, Sugar Free Mithai, Guilt Free Snacks, Almond Laddoos, Cashew Snacks, Coconut Laddoos, Plant Based Protein, No Preservatives, Healthy Indian Snacks, Artisanal Laddoos, Clean Label Food, Weight Management Snacks, Diabetic Friendly Sweets, Nutrient Dense, Superfood Bites, Travel Snacks, Kids Snacks, Healthy Gift, Post Workout Snack, High Fiber, Non GMO Snacks, Wholesome Laddoos, Low GI Sweets</v>
+      </c>
+      <c r="N241" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P241" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q241" t="b">
+        <v>0</v>
+      </c>
+      <c r="R241" t="b">
+        <v>0</v>
+      </c>
+      <c r="S241" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>f241</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Orange Chocolate Laddoos - No Added Sugar | Dates, Dry Fruits &amp; Nuts Laddoo</v>
+      </c>
+      <c r="D242" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1OrangeChocolateDatesandDryfruitLaddoos.jpg?v=1748424060</v>
+      </c>
+      <c r="E242" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F242" t="str">
+        <v>Sweets / Desserts</v>
+      </c>
+      <c r="G242">
+        <v>84</v>
+      </c>
+      <c r="H242" t="str">
+        <v>7 Laddoos (70 gm Pack)</v>
+      </c>
+      <c r="I242" t="str">
+        <v>Eat Better Co's Orange Chocolate Laddoos offer a delightful and health-conscious alternative to traditional confectionery. Combining the zesty, bright notes of fresh oranges with the deep, indulgent flavor of premium cacao, these laddoos create a unique sensory experience. Each piece is crafted from a wholesome base of dates and roasted almonds, enriched with coconut, vanilla extract, and chia seeds, then finished with a pinch of sea salt to enhance the natural flavors. This nutrient-dense snack is 100% natural, vegan, and gluten-free, with no added sugars or artificial additives, making it perfect for those following a clean-eating lifestyle or looking for diabetic-friendly options. The texture is satisfyingly chewy with a crunch from the nuts, while the flavor profile moves from sweet caramel to nutty almond and tangy citrus. These laddoos are ideal for fueling workouts, satisfying mid-day cravings, or as a guilt-free dessert. Packed with fiber and healthy fats, they represent a modern take on Indian heritage sweets, focusing on transparency and quality ingredients. Certifications include being non-GMO and plant-based, ensuring a premium snacking experience for all health enthusiasts.</v>
+      </c>
+      <c r="J242" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K242" t="str">
+        <v>crispy-millet-mixture-namkeen1</v>
+      </c>
+      <c r="L242" t="str">
+        <v>Orange Chocolate Laddoos - No Added Sugar | Dates, Dry Fruits &amp; Nuts Laddoo</v>
+      </c>
+      <c r="M242" t="str">
+        <v>Orange Chocolate Laddoos, No Added Sugar Laddoos, Date Laddoos, Healthy Indian Sweets, Vegan Laddoos, Gluten Free Snacks, Nut Based Laddoos, Eat Better Co, Cacao Snacks, Orange Flavor Sweets, Healthy Desserts, Natural Energy Balls, Dry Fruit Laddoos, Sugar Free Snacks, Clean Label Food, Plant Based Protein, Almond Laddoos, Chia Seed Snacks, Healthy Gifting, guilt free treats, paleo friendly snacks, artisan laddoos, premium dry fruit snacks, healthy festive sweets, snack for weight loss, energy snacks for kids, non-GMO snacks, keto friendly desserts, fiber rich snacks, antioxidant rich cacao, real orange zest sweets, handcrafted snacks, traditional sweets with a twist, Indian superfoods, wholesome snacks, zero cholesterol sweets, chemical free food, high fiber sweets, protein rich laddoos, healthy office snacks, travel friendly snacks</v>
+      </c>
+      <c r="N242" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P242" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="b">
+        <v>0</v>
+      </c>
+      <c r="R242" t="b">
+        <v>0</v>
+      </c>
+      <c r="S242" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>f242</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Coffee Almond Laddoos - No Added Sugar | Dates, Dry-Fruits &amp; Nuts Laddoo</v>
+      </c>
+      <c r="D243" t="str">
+        <v>http://eatbetterco.com/cdn/shop/files/1CoffeeAlmondDatesanddryfruitladdoo.jpg?v=1748423877</v>
+      </c>
+      <c r="E243" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F243" t="str">
+        <v>Sweets / Desserts</v>
+      </c>
+      <c r="G243">
+        <v>460</v>
+      </c>
+      <c r="H243" t="str">
+        <v>7 Laddoos (70 gm Pack)</v>
+      </c>
+      <c r="I243" t="str">
+        <v>Coffee Almond Laddoos from Eat Better Co are a sophisticated blend of rich coffee flavor and the crunch of premium almonds. Crafted for coffee enthusiasts seeking a healthy energy boost, these laddoos are made using only natural ingredients like dates, almonds, coconuts, oats, chia seeds, and a hint of sea salt. They are 100% natural, vegan, and gluten-free, with absolutely no added sugar, artificial flavors, or preservatives. Each bite offers a chewy yet satisfying texture, making them an excellent hunger hack or a guilt-free replacement for traditional sweets and chocolates. High in protein and fiber, they are perfect for on-the-go snacking, pre-workout fuel, or a healthy treat for children. The natural oils released by the nuts over time signify their pure, unprocessed quality. These laddoos provide a refreshing experience akin to a cup of coffee but in a convenient, nutrient-dense form that supports a healthy lifestyle without compromising on taste.</v>
+      </c>
+      <c r="J243" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K243" t="str">
+        <v>crispy-millet-mixture-namkeen1</v>
+      </c>
+      <c r="L243" t="str">
+        <v>Coffee Almond Laddoos - No Added Sugar | Dates, Dry-Fruits &amp; Nuts Laddoo</v>
+      </c>
+      <c r="M243" t="str">
+        <v>Coffee Almond Laddoos, Healthy Snacks, No Added Sugar, Vegan Sweets, Gluten Free Snacks, Energy Bites, Dry Fruit Laddoo, Dates and Nuts, High Protein Snacks, Eat Better Co, Natural Ingredients, Coffee Lovers Treat, Guilt Free Dessert, Indian Snacks, Traditional Laddoos, Clean Label Food, No Preservatives, Chia Seeds, Almond Snacks, Healthy Gifting, Keto Friendly, Low Calorie Sweets, On the go Energy, Fiber Rich, Breakfast Snacks, Kids Healthy Food, Plant Based, Artisan Snacks, Sugar Free Candy, Gourmet Laddoos, Nutritious Bites, Snack Replacement, Energy Balls, Coffee Flavor, Date Based Sweets, Healthy Indian Dessert, Guilt Free Snacking, Nutrient Dense, Superfoods, Coffee Infused</v>
+      </c>
+      <c r="N243" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P243" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q243" t="b">
+        <v>0</v>
+      </c>
+      <c r="R243" t="b">
+        <v>0</v>
+      </c>
+      <c r="S243" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>f243</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Eat Better Co</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Orange Ginger Laddoos - No Added Sugar | Dates, Dry-Fruits &amp; Nuts Laddoo</v>
+      </c>
+      <c r="D244" t="str">
+        <v>https://eatbetterco.com/cdn/shop/files/1OrangeGingerDatesandDryFruitLadoo.jpg?v=1748433376</v>
+      </c>
+      <c r="E244" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F244" t="str">
+        <v>Sweets / Desserts</v>
+      </c>
+      <c r="G244">
+        <v>89</v>
+      </c>
+      <c r="H244" t="str">
+        <v>7 Laddoos (70 gm Pack)</v>
+      </c>
+      <c r="I244" t="str">
+        <v>Orange Ginger Laddoos by Eat Better Co are a perfect blend of health and taste, meticulously crafted for those who crave a sweet treat without the guilt. These laddoos feature a unique combination of chewy dates, crunchy cashews, almonds, and raisins, infused with the refreshing zing of orange oil and a hint of warm ginger. Naturally sweetened with dates and free from added sugars, they offer a rich source of energy and fiber. The texture is soft and chewy, complemented by the nuttiness of the ingredients. These vegan and gluten-free snacks are 100% natural, containing no artificial flavors or preservatives. Perfect for mid-day cravings or as a healthy post-meal dessert, they provide a balanced flavor profile of citrusy sweetness and earthy spice. Certified natural and made with premium whole foods, these laddoos are a nutritious alternative to traditional Indian sweets. They are easy to carry and provide a sustained energy release, making them an ideal choice for busy lifestyles.</v>
+      </c>
+      <c r="J244" t="str">
+        <v>https://eatbetterco.com/</v>
+      </c>
+      <c r="K244" t="str">
+        <v>crispy-millet-mixture-namkeen1</v>
+      </c>
+      <c r="L244" t="str">
+        <v>Orange Ginger Laddoos - No Added Sugar | Dates, Dry-Fruits &amp; Nuts Laddoo</v>
+      </c>
+      <c r="M244" t="str">
+        <v>Orange Ginger Laddoos, Healthy Snacks, No Added Sugar, Dates Ladoo, Dry Fruit Sweet, Vegan Snacks, Gluten Free, Eat Better Co, Natural Ingredients, High Fiber, Energy Balls, Cashew Almond Ladoo, Chia Seeds, Healthy Desserts, Indian Healthy Sweets, Sugar Free Ladoo, Clean Label, No Preservatives, Nutritious Snacking, Orange Flavor, Ginger Spice, Handcrafted Sweets, Guilt Free, Paleo Friendly, High Energy, Whole Foods, Citrusy Ladoo, Healthy Gifting, Kids Snacks, Diet Friendly, Post Workout Food, Artisan Snacks, Fiber Rich, Energy Booster, Wellness Foods</v>
+      </c>
+      <c r="N244" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P244" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q244" t="b">
+        <v>0</v>
+      </c>
+      <c r="R244" t="b">
+        <v>0</v>
+      </c>
+      <c r="S244" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>pc1</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Rosemary Peppermint Body Wash (300ml)</v>
+      </c>
+      <c r="D245" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Rosemary_Peppermint_Body_Wash_300ml_Rustic_Art_fdde449158740125_1024x.png?v=1768722396</v>
+      </c>
+      <c r="E245" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F245" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G245">
+        <v>350</v>
+      </c>
+      <c r="H245" t="str">
+        <v>300ml</v>
+      </c>
+      <c r="I245" t="str">
+        <v>Rustic Art Organic Rosemary Peppermint Body Wash is a revitalizing liquid soap formulated with the invigorating scents of organic rosemary and cooling peppermint. This 300ml body wash is specifically designed to provide a refreshing and energizing bathing experience while offering significant herbal benefits for the skin. It effectively fights body acne and works to brighten the skin's overall appearance, leaving it clear and radiant. As a natural, SLS-free formula, it ensures a gentle cleanse without stripping the skin of its natural oils. The cooling sensation of mint makes it ideal for use after a long day or a workout, providing instant relief and a sense of freshness. The texture is a smooth liquid that lathers well despite being free from harsh chemicals. Key ingredients include organic essential oils that offer aromatherapeutic benefits, promoting mental clarity and physical relaxation. This product is certified organic and vegan, adhering to high standards of purity and sustainability. Use daily for best results, applying to wet skin and rinsing thoroughly to reveal soft, revitalized skin.</v>
+      </c>
+      <c r="J245" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/organic-rosemary-peppermint-body-wash-300ml</v>
+      </c>
+      <c r="K245" t="str">
+        <v>rustic1</v>
+      </c>
+      <c r="L245" t="str">
+        <v>Rosemary Peppermint Body Wash (300ml)</v>
+      </c>
+      <c r="M245" t="str">
+        <v>Organic Body Wash, Rosemary Peppermint, SLS-Free, Paraben-Free, Vegan Skincare, Natural Body Wash, Body Acne Treatment, Cooling Body Wash, Refreshing Shower Gel, Rustic Art, Organic Rosemary, Peppermint Oil, Herbal Skin Care, Brightening Body Wash, Eco-friendly, Sustainable Beauty, Chemical Free, Essential Oils, Energizing Bath, Indian Beauty Brand, Cruelty Free, Organic Ingredients, Liquid Soap, Aromatherapy, Skin Detox, Deep Cleansing, Sensitive Skin, Daily Body Wash, Holistic Beauty, Non-Toxic, Sulfate Free, Phthalate Free, Bio-degradable, Handcrafted, Cold Processed, Nourishing, Hydrating, Skin Health, Refreshing Scent, Bath and Shower, Personal Care, Organic Certified, Pure Essential Oils, Natural Glow, Detoxifying, Muscle Relief, Morning Routine, Summer Essentials, Wellness, Zero Waste</v>
+      </c>
+      <c r="N245" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P245" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q245" t="b">
+        <v>0</v>
+      </c>
+      <c r="R245" t="b">
+        <v>0</v>
+      </c>
+      <c r="S245" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>pc2</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Rose Sandal Body Wash (300ml)</v>
+      </c>
+      <c r="D246" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Rose_Sandal_Body_Wash_300ml_Rustic_Art_c4cb9bc5dc3338f7_1024x.jpg?v=1768722445</v>
+      </c>
+      <c r="E246" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F246" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G246">
+        <v>350</v>
+      </c>
+      <c r="H246" t="str">
+        <v>300ml</v>
+      </c>
+      <c r="I246" t="str">
+        <v>Rustic Art Rose Sandal Body Wash brings a luxurious Ayurvedic shower experience to your home. Formulated with organic ingredients like Rose, Sandalwood, and Turmeric, it helps in achieving a natural glow while reducing the effects of tanning. The addition of Triphala—consisting of Amla, Bhibhitaki, and Haritaki—ensures that your skin is deep-cleaned and nourished with essential nutrients. This body wash is designed to make the skin firm and smooth, making it suitable for all skin types. It is completely organic, vegan, and free from harmful chemicals like sulfates and parabens. The soothing aroma of rose and sandalwood provides a relaxing bathing experience that lingers. Rich in antioxidants from turmeric and vitamin C from amla, it promotes skin health and rejuvenation. Its gentle texture ensures that the skin's natural moisture barrier remains intact. This product is a perfect blend of ancient wisdom and modern convenience, providing a refreshing cleanse that leaves your skin feeling pampered, hydrated, and healthy every day.</v>
+      </c>
+      <c r="J246" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rose-sandal-body-wash-with-tripahala-turmeric</v>
+      </c>
+      <c r="K246" t="str">
+        <v>rustic1</v>
+      </c>
+      <c r="L246" t="str">
+        <v>Rose Sandal Body Wash (300ml)</v>
+      </c>
+      <c r="M246" t="str">
+        <v>Rustic Art, Rose Sandal Body Wash, Organic Body Wash, Sandalwood Body Wash, Rose Water, Turmeric Skin Care, Triphala for Skin, Ayurvedic Body Wash, Natural Cleanser, Tan Removal, Skin Brightening, Glowing Skin, Firm Skin, Chemical Free, Vegan Body Wash, Cruelty Free, Paraben Free, SLS Free, Sustainable Beauty, Indian Skin Care, Traditional Beauty, Luxury Bath, Eco Friendly, Herbal Body Wash, Skin Nourishment, Amla for Skin, Haritaki Benefits, Bhibhitaki, Essential Oils, Aromatherapy, Daily Skincare, Unisex Body Wash, All Skin Types, Radiant Skin, Hydrating Body Wash, Rustic Art Products, Bath and Shower, Natural Ingredients, Bio-degradable, Non-toxic</v>
+      </c>
+      <c r="N246" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P246" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q246" t="b">
+        <v>0</v>
+      </c>
+      <c r="R246" t="b">
+        <v>0</v>
+      </c>
+      <c r="S246" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>pc3</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Floral Shower Body Wash (300ml)</v>
+      </c>
+      <c r="D247" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Floral_Shower_Body_Wash_300ml_Rustic_Art_2513882420e4c92e_1024x.png?v=1768722445</v>
+      </c>
+      <c r="E247" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F247" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G247">
+        <v>350</v>
+      </c>
+      <c r="H247" t="str">
+        <v>300ml</v>
+      </c>
+      <c r="I247" t="str">
+        <v>Rustic Art Organic Floral Shower Body Wash brings the luxurious experience of bathing in fresh flower petals directly to your daily routine. This literal spa in a bottle is carefully formulated with an enticing bouquet of Rajnigandha, Raatrani, Rose, and Sunflower to provide a refreshing and happy start to your day. The powerful combination of exfoliating tomato and brightening papaya works effectively to remove tan, reduce pigmentation, and address skin concerns like wrinkles and eczema. Enriched with moisturizing Sal butter and a nourishing blend of organic oils—including Coconut, Olive, Ricebran, Castor, and Flaxseed—it deeply cleanses dirt and pollution while quenching the skin's thirst. The addition of vegetable glycerin ensures a feather-light moisturizing cap, leaving your skin soft and blooming. Free from harsh chemicals, this body wash is suitable for all skin types and serves as a perfect solution for washing away the day's fatigue. Experience the rejuvenating power of nature's best ingredients for a healthy, glowing complexion.</v>
+      </c>
+      <c r="J247" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/organic-floral-shower-body-wash-with-tomato-papaya</v>
+      </c>
+      <c r="K247" t="str">
+        <v>rustic1</v>
+      </c>
+      <c r="L247" t="str">
+        <v>Floral Shower Body Wash (300ml)</v>
+      </c>
+      <c r="M247" t="str">
+        <v>Organic Body Wash, Natural Shower Gel, Floral Body Wash, Rustic Art, Sulfate Free, Paraben Free, Vegan Skin Care, Cruelty Free, Tomato Extract, Papaya Skin Care, Tan Removal, Pigmentation Treatment, Moisturizing Body Wash, Rajnigandha, Raatrani, Rose Body Wash, Sunflower Oil, Sal Butter, Ayurvedic Bath, Eco Friendly, Sustainable Beauty, Chemical Free, All Skin Types, Deep Cleansing, Skin Brightening, Anti Aging, Eczema Relief, Natural Glow, Essential Oils, Handcrafted, Made in India, Bio Degradable, Non Toxic, Herbal Bath, Luxury Body Wash, Body Care, Daily Essentials, Aromatherapy, Refreshing Shower, Radiant Skin, Cold Pressed Oils</v>
+      </c>
+      <c r="N247" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P247" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q247" t="b">
+        <v>0</v>
+      </c>
+      <c r="R247" t="b">
+        <v>0</v>
+      </c>
+      <c r="S247" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>pc4</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Rose Sandal Body Wash Concentrate</v>
+      </c>
+      <c r="D248" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Rose_Sandal_Body_Wash_Concentrate_Rustic_Art_981012aa1241e601_1024x.jpg?v=1768722439</v>
+      </c>
+      <c r="E248" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F248" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G248">
+        <v>375</v>
+      </c>
+      <c r="H248" t="str">
+        <v>200g</v>
+      </c>
+      <c r="I248" t="str">
+        <v>Rustic Art Organic Rose Sandal Body Wash Concentrate is a luxurious, water-efficient bath solution that combines the aromatic elegance of Rose and Sandalwood with the therapeutic properties of Turmeric. Formulated as a potent concentrate, this body wash ensures that a small amount goes a long way, providing a rich, creamy lather that cleanses deeply without stripping the skin of its natural moisture. The blend of Rose and Sandalwood works to brighten the complexion and reduce the appearance of tanning, while Turmeric adds an antiseptic quality that promotes a healthy, glowing skin tone. Infused with the traditional Ayurvedic Triphala mix—Amla, Bibhitaki, and Haritaki—it offers a powerful antioxidant boost that firms and rejuvenates the skin. This product is completely free from sulfates, parabens, and synthetic fragrances, making it an ideal choice for sensitive skin and eco-conscious consumers. Its texture is thick and smooth, transforming into a silky foam upon contact with water. Certified organic and vegan, it represents a sustainable approach to personal hygiene. To use, simply massage a pea-sized amount onto wet skin using a loofah for best results, then rinse thoroughly for a refreshed, fragrant finish.</v>
+      </c>
+      <c r="J248" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/organic-rose-sandal-body-wash-concentrate</v>
+      </c>
+      <c r="K248" t="str">
+        <v>rustic-art-rose-sandal-body-wash77</v>
+      </c>
+      <c r="L248" t="str">
+        <v>Rose Sandal Body Wash Concentrate</v>
+      </c>
+      <c r="M248" t="str">
+        <v>Rose Body Wash, Sandalwood Body Wash, Organic Body Wash, Body Wash Concentrate, Rustic Art, Natural Skincare, Glowing Skin, Tan Removal, Firming Body Wash, Turmeric Skincare, Triphala Benefits, Sulfate Free, Paraben Free, Vegan Body Wash, Eco Friendly Beauty, Sustainable Skincare, Luxury Bath, Ayurvedic Ingredients, Amla for Skin, Essential Oils, Deep Cleansing, Moisturizing Body Wash, Chemical Free, Handmade Skincare, Indian Beauty, Herbal Body Wash, Radiant Skin, Daily Hygiene, Aromatherapy Bath, Non Toxic Beauty, Rose and Sandalwood, Bio Degradable, Water Efficient, Travel Friendly, Concentrated Formula, Skin Brightening, Antiseptic Body Wash, Natural Glow, Refreshing Bath, Ayurvedic Skincare</v>
+      </c>
+      <c r="N248" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P248" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q248" t="b">
+        <v>0</v>
+      </c>
+      <c r="R248" t="b">
+        <v>0</v>
+      </c>
+      <c r="S248" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>pc5</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Tomato Walnut Body &amp; Face Scrub Concentrate (100gm)</v>
+      </c>
+      <c r="D249" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/tomato_scrub_100gm_-_1_1024x.jpg?v=1766491297</v>
+      </c>
+      <c r="E249" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F249" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G249">
+        <v>325</v>
+      </c>
+      <c r="H249" t="str">
+        <v>200g</v>
+      </c>
+      <c r="I249" t="str">
+        <v>Rustic Art Tomato Walnut Body &amp; Face Scrub Concentrate is an organic skincare solution meticulously formulated to cater to all skin types. This concentrate features super-fine, soft walnut powder that provides gentle exfoliation without damaging the delicate skin barrier. Regular use through circular massaging motions helps effectively remove dead skin cells, revealing a soft, silky, and supple complexion underneath. Infused with the goodness of tomato, it helps in brightening and revitalizing the skin. The scrub is 100% natural, vegan, and free from harmful chemicals, sulfates, and parabens, ensuring a clean beauty experience. Its unique concentrate form means a little goes a long way, making it an eco-friendly and cost-effective choice for your hygiene routine. The texture is grainy yet non-abrasive, perfect for deep cleansing while maintaining moisture. Certified organic ingredients ensure that your skin receives only the purest nourishment. Ideal for both body and face, this scrub improves blood circulation and promotes a healthy, radiant glow. Simply take a small amount, mix with water, and massage onto wet skin for a refreshing bath experience.</v>
+      </c>
+      <c r="J249" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-tomato-walnut-body-scrub-concentrate-100g</v>
+      </c>
+      <c r="K249" t="str">
+        <v>rustic-art-rose-sandal-body-wash77</v>
+      </c>
+      <c r="L249" t="str">
+        <v>Tomato Walnut Body &amp; Face Scrub Concentrate (100gm)</v>
+      </c>
+      <c r="M249" t="str">
+        <v>Rustic Art, Tomato Walnut Scrub, Body Scrub, Face Scrub, Organic Skincare, Natural Exfoliation, Vegan Beauty, Sulfate Free, Paraben Free, Dead Skin Removal, Glowing Skin, Skin Brightening, Handmade Scrub, Cruelty Free, Sustainable Beauty, Eco Friendly, Indian Skincare, Herbal Scrub, Gentle Exfoliant, Skin Care Routine, Body Care, Walnut Powder, Tomato Benefits, Silky Skin, Supple Skin, Chemical Free, Ayurvedic, Detox Skin, Deep Cleansing, Radiant Glow, Scrub Concentrate, Zero Waste, Non Toxic, Nourishing Scrub, Skin Repair, Healthy Skin, Bath and Body, Self Care, Luxury Skincare, Wellness, Pure Ingredients, Plant Based, Daily Exfoliator, Smooth Skin, Refreshing Scrub</v>
+      </c>
+      <c r="N249" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P249" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q249" t="b">
+        <v>0</v>
+      </c>
+      <c r="R249" t="b">
+        <v>0</v>
+      </c>
+      <c r="S249" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>pc6</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Organic Rosemary Peppermint Body Wash Concentrate - Cooling &amp; Energizing for All Skin Types | Anti-Acne &amp; Deep Cleansing | SLS &amp; Paraben Free (200gm)</v>
+      </c>
+      <c r="D250" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Organic_Rosemary_Peppermint_Body_Wash_Concentrate_-_Cooling_Energizing_for_All_Skin_Types_Anti-Acne_Deep_Cleansing_SLS_Paraben_Free_200gm_Rustic_Art_e75435fd3a0b341f_1024x.jpg?v=1768722541</v>
+      </c>
+      <c r="E250" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F250" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G250">
+        <v>375</v>
+      </c>
+      <c r="H250" t="str">
+        <v>200g</v>
+      </c>
+      <c r="I250" t="str">
+        <v>Rustic Art Rosemary Peppermint Body Wash Concentrate is a revolutionary organic hygiene solution designed for all skin types. This cooling and energizing concentrate provides a deep cleansing experience, effectively removing impurities while targeting body acne to improve overall skin texture. Infused with potent rosemary and peppermint essential oils, it delivers a refreshing morning tingle that revitalizes the senses. The unique concentrated formula is highly efficient, lasting up to three times longer than standard liquid body washes, making it a sustainable choice for eco-conscious consumers. It is completely free from SLS, parabens, and harsh synthetic chemicals, ensuring a safe and gentle cleanse for daily use. The texture is a dense, rich concentrate that transforms into a luxurious lather when mixed with water. Key benefits include intense purification, anti-inflammatory properties from essential oils, and long-lasting hydration. Certified organic and cruelty-free, this product represents a commitment to green beauty without compromising on professional-grade performance. It leaves the skin feeling exceptionally fresh, smooth, and rejuvenated after every shower.</v>
+      </c>
+      <c r="J250" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-rosemary-peppermint-body-wash-concentrate</v>
+      </c>
+      <c r="K250" t="str">
+        <v>rustic-art-rose-sandal-body-wash77</v>
+      </c>
+      <c r="L250" t="str">
+        <v>Organic Rosemary Peppermint Body Wash Concentrate - Cooling &amp; Energizing for All Skin Types | Anti-Acne &amp; Deep Cleansing | SLS &amp; Paraben Free (200gm)</v>
+      </c>
+      <c r="M250" t="str">
+        <v>Rosemary Peppermint Body Wash, Organic Body Wash, Body Wash Concentrate, Anti-Acne Body Wash, Deep Cleansing, SLS Free, Paraben Free, Natural Skin Care, Cooling Body Wash, Energizing Shower Gel, Rustic Art, Vegan Body Wash, Eco-friendly Hygiene, Sustainable Beauty, Essential Oil Body Wash, Peppermint Oil, Rosemary Oil, Sensitive Skin Safe, Cruelty Free, Indian Beauty Brand, Chemical Free Cleanser, Morning Routine, Refreshing Shower, Skin Texture Improvement, Concentrated Formula, Ayurvedic Body Wash, Bio-degradable, Plastic Free Packaging, Herbal Body Wash, Non Toxic, Daily Cleanser, Hydrating Body Wash</v>
+      </c>
+      <c r="N250" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P250" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q250" t="b">
+        <v>0</v>
+      </c>
+      <c r="R250" t="b">
+        <v>0</v>
+      </c>
+      <c r="S250" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>pc7</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Floral Shower Body Wash Concentrate</v>
+      </c>
+      <c r="D251" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Floral_Shower_Body_Wash_Concentrate_Rustic_Art_5aed85b383f0dd19_1024x.jpg?v=1768722541</v>
+      </c>
+      <c r="E251" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F251" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G251">
+        <v>375</v>
+      </c>
+      <c r="H251" t="str">
+        <v>200g</v>
+      </c>
+      <c r="I251" t="str">
+        <v>Rustic Art Organic Floral Shower Body Wash Concentrate brings your dream sequence of bathing in flower petals to reality. This unique, water-efficient concentrate is carefully formulated with a potent bouquet of Rajnigandha, Raatrani, Rose, and Sunflower to bring joy to your daily cleansing ritual. The formula features exfoliating tomato to gently refine skin texture, moisturizing Sal butter for deep hydration, and a blend of nourishing cold-pressed oils that ensure your skin remains soft and supple. This body wash concentrate is a sustainable alternative to traditional liquid soaps, requiring less water per use and reducing environmental impact. The texture is a rich, creamy paste that lathers luxuriously when mixed with water, providing a sensory aromatherapy experience. It is free from sulfates, parabens, and synthetic fragrances, making it suitable for all skin types including sensitive skin. Certified organic and vegan, it ensures a pure, non-toxic cleanse while leaving a delicate, long-lasting floral fragrance on the skin. Use a pea-sized amount on a loofah or wet palms for a complete body wash experience.</v>
+      </c>
+      <c r="J251" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-floral-shower-body-wash-concentrate</v>
+      </c>
+      <c r="K251" t="str">
+        <v>rustic-art-rose-sandal-body-wash77</v>
+      </c>
+      <c r="L251" t="str">
+        <v>Floral Shower Body Wash Concentrate</v>
+      </c>
+      <c r="M251" t="str">
+        <v>Rustic Art, Body Wash, Shower Gel, Organic Body Wash, Natural Cleanser, Floral Scent, Rajnigandha, Raatrani, Rose, Sunflower, Sal Butter, Tomato Extract, Exfoliating, Moisturizing, Body Care, Personal Care, Vegan, Cruelty Free, Paraben Free, Sulfate Free, Sustainable Beauty, Zero Waste, Concentrate, Eco Friendly, Indian Skin Care, Herbal Bath, Essential Oils, Skin Nourishment, Hydrating, Soft Skin, Daily Ritual, Luxury Bath, Botanical, Chemical Free, Non Toxic, Handcrafted, Aromatherapy, Refreshing, Glowing Skin, Mild Cleanser, Environmentally Friendly, Biodegradable, Plastic Free Packaging, Pure Ingredients, Ayurvedic</v>
+      </c>
+      <c r="N251" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P251" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q251" t="b">
+        <v>0</v>
+      </c>
+      <c r="R251" t="b">
+        <v>0</v>
+      </c>
+      <c r="S251" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>pc8</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Vetiver Soap (100gm)</v>
+      </c>
+      <c r="D252" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Vetiver_Soap_100gm_Rustic_Art_42262b1993730b3c_1024x.jpg?v=1768722539</v>
+      </c>
+      <c r="E252" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F252" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G252">
+        <v>200</v>
+      </c>
+      <c r="H252" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I252" t="str">
+        <v>Rustic Art Organic Vetiver Soap is an exceptional body care solution often referred to as the fountain of youth. Specifically designed to provide potent regeneration and anti-aging properties, this soap is a perfect companion for individuals over thirty. The key ingredient, Vetiver oil, is renowned for its skin-regenerating abilities, which helps in deeply nourishing the skin while effectively reducing the appearance of scars and acne. Additionally, it contains linseed oil, which is exceptionally rich in omega-3 essential fatty acids to keep the skin hydrated and healthy. The soap offers a smooth texture that lathers gently, providing a refreshing and cooling sensation during use. This product is ideal for daily hygiene routines, helping to detoxify and repair damaged skin tissues. Being a product from Rustic Art, it is formulated with organic, plant-based ingredients and avoids harsh synthetic chemicals, ensuring a safe and natural cleansing experience. It is suitable for all skin types and works towards restoring natural glow, elasticity, and health. The soap is handcrafted, eco-friendly, and cruelty-free, reflecting a commitment to sustainable beauty.</v>
+      </c>
+      <c r="J252" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-vetiver-soap</v>
+      </c>
+      <c r="K252" t="str">
+        <v>rustic-art-rose-sandal-body-wash7</v>
+      </c>
+      <c r="L252" t="str">
+        <v>Vetiver Soap (100gm)</v>
+      </c>
+      <c r="M252" t="str">
+        <v>Organic soap, Vetiver soap, anti-aging soap, natural skincare, handmade soap, Rustic Art, acne treatment, scar reduction, regenerating soap, linseed oil, omega-3 skincare, herbal soap, moisturizing soap, vegan soap, chemical free soap, cold processed soap, aromatherapy, skin nourishment, sustainable beauty, eco-friendly, bath products, body care, skin repair, anti-inflammatory, detoxifying, cooling soap, Indian herbs, Ayurvedic soap, healthy skin, cruelty-free, plastic-free, toxin-free, artisan soap</v>
+      </c>
+      <c r="N252" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P252" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q252" t="b">
+        <v>0</v>
+      </c>
+      <c r="R252" t="b">
+        <v>0</v>
+      </c>
+      <c r="S252" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>pc9</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Vanilla Soap (100gm)</v>
+      </c>
+      <c r="D253" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Vanilla_Soap_100gm_Rustic_Art_00f8c25cc31dca76_1024x.jpg?v=1768722540</v>
+      </c>
+      <c r="E253" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F253" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G253">
+        <v>178</v>
+      </c>
+      <c r="H253" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I253" t="str">
+        <v>Rustic Art Organic Vanilla Soap offers a nostalgic bathing experience, reminiscent of childhood vanilla ice cream. This artisanal soap is formulated with organic ingredients designed for both kids and adults, providing deep cleansing without stripping the skin of its natural oils. Enriched with the goodness of Aloe Vera and Coconut Milk Extract, it offers superior hydration and nourishment. The rich, creamy lather cleanses effectively while the soothing properties of aloe vera calm the skin. Coconut milk acts as a natural moisturizer, ensuring your skin feels soft and supple after every wash. The warm, comforting fragrance of vanilla lingers on the skin, providing a sensory delight throughout the day. This soap is crafted to be gentle yet effective, making it suitable for all skin types. It is free from harsh chemicals, synthetic fragrances, and parabens, adhering to organic standards. The texture is smooth and firm, ensuring a long-lasting bar that maintains its integrity. Regular use promotes healthy, glowing skin by maintaining moisture balance and providing essential nutrients. Ideal for a refreshing shower or a relaxing bath, this Vanilla Soap is a perfect addition to your daily personal care routine, ensuring a clean, hydrated, and beautifully scented finish.</v>
+      </c>
+      <c r="J253" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-vanilla-soap</v>
+      </c>
+      <c r="K253" t="str">
+        <v>rustic-art-rose-sandal-body-wash7</v>
+      </c>
+      <c r="L253" t="str">
+        <v>Vanilla Soap (100gm)</v>
+      </c>
+      <c r="M253" t="str">
+        <v>Rustic Art, Vanilla Soap, Organic Soap, Natural Cleanser, Skin Care, Bath and Body, Aloe Vera Soap, Coconut Milk Soap, Hydrating Soap, Handmade Soap, Chemical Free, Paraben Free, Sulfate Free, Cruelty Free, Vegan Soap, Sustainable Beauty, Herbal Soap, Gentle Cleansing, Kids Friendly Soap, Moisturizing Soap, Fragrant Soap, Essential Oils, Pure Ingredients, Indian Brand, Eco Friendly, Daily Essentials, Sensitive Skin Soap, Nourishing Bath, Aromatherapy Soap, Luxury Soap, Artisan Soap, Cold Process Soap, Traditional Soap, Healthy Skin, Glowing Skin, Natural Fragrance, Vanilla Scent, Skin Hydration, Body Wash Alternative, Non Toxic Skin Care, Bio Degradable, Organic Ingredients, Holistic Wellness</v>
+      </c>
+      <c r="N253" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P253" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q253" t="b">
+        <v>0</v>
+      </c>
+      <c r="R253" t="b">
+        <v>0</v>
+      </c>
+      <c r="S253" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>pc10</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Turmeric Soap (100gm)</v>
+      </c>
+      <c r="D254" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Turmeric_Soap_100gm_Rustic_Art_f715822dfbe2e606_1024x.jpg?v=1768722537</v>
+      </c>
+      <c r="E254" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F254" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G254">
+        <v>178</v>
+      </c>
+      <c r="H254" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I254" t="str">
+        <v>Adding that golden spice to your skin! Glow like you were always meant to. Rustic Art Organic Turmeric Soap is right off the good books of many. Turmeric is not only recommended by the elders, but also by our culture! Removing tan, nourishing the skin, anti-acne, and anti-septic, the benefits are endless. Infused with coconut milk, this soap provides exceptional moisturizing properties to keep your skin soft and supple. Turmeric is renowned for its skin-brightening properties, helping to effectively reduce dark spots and acne scars. This soap is handcrafted using the traditional cold-pressed method, ensuring that the natural goodness of the organic oils is retained. Key ingredients include organic coconut oil, organic mahua oil, turmeric extract, and coconut milk. It is suitable for all skin types and delivers a rich, creamy lather with a pleasant earthy fragrance. Completely free from sulfates, parabens, and synthetic fragrances, it is certified organic and vegan. Use it daily to achieve a natural glow and maintain healthy, protected skin.</v>
+      </c>
+      <c r="J254" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-turmeric-soap</v>
+      </c>
+      <c r="K254" t="str">
+        <v>rustic-art-rose-sandal-body-wash7</v>
+      </c>
+      <c r="L254" t="str">
+        <v>Turmeric Soap (100gm)</v>
+      </c>
+      <c r="M254" t="str">
+        <v>Rustic Art, Organic Turmeric Soap, Natural Soap, Vegan Soap, Handmade Soap, Cold Processed Soap, Turmeric for Skin, Skin Brightening, Anti Acne Soap, Anti Septic Soap, Tan Removal, Moisturizing Soap, Coconut Milk Soap, Herbal Soap, Chemical Free Soap, Paraben Free, Sulfate Free, Cruelty Free, Sustainable Beauty, Eco Friendly Soap, Ayurvedic Soap, Glow Skin, Dark Spot Reduction, Acne Scar Treatment, Traditional Indian Beauty, Essential Oils Soap, Mahua Oil Soap, Organic Personal Care, Body Care, Bath and Shower, Holistic Skincare, Non-Toxic, Indian Skin Care, Brightening Soap, Nourishing</v>
+      </c>
+      <c r="N254" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P254" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q254" t="b">
+        <v>0</v>
+      </c>
+      <c r="R254" t="b">
+        <v>0</v>
+      </c>
+      <c r="S254" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>pc11</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Tea Tree Rosemary Soap</v>
+      </c>
+      <c r="D255" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/tea_tree_soap_mobile_-_1_1024x.jpg?v=1766040776</v>
+      </c>
+      <c r="E255" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F255" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G255">
+        <v>178</v>
+      </c>
+      <c r="H255" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I255" t="str">
+        <v>Rustic Art Tea Tree Rosemary Soap is a premium, organic cleansing bar designed to offer comprehensive protection against bacteria, fungi, and microbes. This potent formula features tea tree oil, renowned for its antimicrobial and anti-inflammatory benefits, making it an excellent choice for reducing acne and calming skin irritations for a smoother, glowing complexion. Complementing this is rosemary oil, which helps protect the skin against environmental stressors while uplifting the senses with its refreshing herbal aroma. Handcrafted using the traditional cold-process method, the soap contains a nourishing base of organic oils like coconut, mahua, and neem oil, which deeply moisturize and maintain the skin's natural balance. Its rich, creamy texture provides a luxurious bathing experience without the use of harsh chemicals, sulfates, or synthetic fragrances. Perfect for oily and acne-prone skin types, this soap is 100% vegan, biodegradable, and cruelty-free. To use, simply lather the bar with water, massage onto damp skin, and rinse well for a clean, revitalized feel. This soap not only cares for your skin but also supports the environment through its sustainable, plastic-free approach.</v>
+      </c>
+      <c r="J255" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-tea-tree-rosemary-soap</v>
+      </c>
+      <c r="K255" t="str">
+        <v>rustic-art-rose-sandal-body-wash7</v>
+      </c>
+      <c r="L255" t="str">
+        <v>Tea Tree Rosemary Soap - 100gm</v>
+      </c>
+      <c r="M255" t="str">
+        <v>Organic Tea Tree Rosemary Soap, Rustic Art, Body Care, Natural Soap, Handmade Soap, Vegan Soap, Acne Treatment, Tea Tree Oil, Rosemary Oil, Cold Processed Soap, Organic Ingredients, Sustainable Beauty, Eco-friendly, Paraben Free, Sulfate Free, Chemical Free, Skin Clearing, Anti-inflammatory, Antimicrobial, Moisturizing Soap, Herbal Soap, Bio-degradable, Cruelty Free, Indian Beauty Brand, Bath and Body, Skin Protection, Refreshing Scent, Essential Oils, Neem Oil, Mahua Oil, Coconut Oil Soap, Detoxifying Soap, Daily Cleansing, Glow Skin, Healthy Skin, Non-toxic Skin Care, Plastic Free Packaging, Zero Waste, Holistic Wellness</v>
+      </c>
+      <c r="N255" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P255" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q255" t="b">
+        <v>0</v>
+      </c>
+      <c r="R255" t="b">
+        <v>0</v>
+      </c>
+      <c r="S255" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>pc12</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Spa Soap (100gm)</v>
+      </c>
+      <c r="D256" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Spa_Soap_100gm_Rustic_Art_6c7c8d01ce5582ae_1024x.jpg?v=1768722535</v>
+      </c>
+      <c r="E256" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F256" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G256">
+        <v>200</v>
+      </c>
+      <c r="H256" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I256" t="str">
+        <v>Rustic Art Spa Soap is a rejuvenating cleansing bar designed to ignite your inner spark and provide a professional-grade spa experience at home. This organic formulation features potent Ashwagandha, which actively works to combat the harmful effects of environmental pollution and oxidative stress on the skin. Complementing this is Geranium essential oil, renowned for its natural anti-fungal, anti-bacterial, and anti-microbial properties, ensuring a deep and hygienic cleanse. The soap creates a rich, creamy lather that gently removes impurities while maintaining the skin's natural moisture balance. Ideal for starting a busy morning with energy or unwinding after a long day, its texture is smooth and nourishing. This product is vegan, cruelty-free, and contains no harsh chemicals like sulfates or parabens. Regular use leaves the skin feeling refreshed, soft, and therapeutically treated. The soothing floral aroma of geranium provides aromatherapeutic benefits, calming the mind while the herbal extracts revitalize the body, making it the perfect addition to any skincare routine.</v>
+      </c>
+      <c r="J256" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-spa-soap</v>
+      </c>
+      <c r="K256" t="str">
+        <v>rustic-art-rose-sandal-body-wash7</v>
+      </c>
+      <c r="L256" t="str">
+        <v>Spa Soap (100gm)</v>
+      </c>
+      <c r="M256" t="str">
+        <v>Spa Soap, Organic Soap, Handmade Soap, Rustic Art, Ashwagandha Soap, Geranium Soap, Natural Cleanser, Body Care, Vegan Soap, Cruelty Free, Pollution Protection, Anti Bacterial Soap, Essential Oils, Skin Care, Bath and Body, Herbal Soap, Chemical Free, Paraben Free, Sulfate Free, Eco Friendly, Sustainable Beauty, Indian Skin Care, Rejuvenating Soap, Aromatherapy, Deep Cleansing, Moisturizing Soap, Daily Essential, Self Care, Ayurvedic Ingredients, Holistic Beauty, Artisan Soap, Cold Processed, Healthy Skin, Glowing Skin, Non Toxic, Sustainable Living, Natural Fragrance, Spa at Home</v>
+      </c>
+      <c r="N256" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P256" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q256" t="b">
+        <v>0</v>
+      </c>
+      <c r="R256" t="b">
+        <v>0</v>
+      </c>
+      <c r="S256" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>pc13</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Patchouli Soap (100gm)</v>
+      </c>
+      <c r="D257" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Patchouli_Soap_100gm_Rustic_Art_97fa57f7e07c6816_1024x.jpg?v=1768722533</v>
+      </c>
+      <c r="E257" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F257" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G257">
+        <v>178</v>
+      </c>
+      <c r="H257" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I257" t="str">
+        <v>Rustic Art Patchouli Soap is a handcrafted, organic cold-processed soap designed for deep skin regeneration and effective body odor control. Infused with pure Patchouli essential oil, it offers a grounding earthy fragrance that acts as a natural deodorizer while providing powerful anti-fungal and anti-inflammatory benefits. This soap is formulated with a nourishing blend of Linseed oil, which balances the skin's natural oil production and reduces inflammation to promote rapid skin repair. Additionally, Cedarwood essential oil helps heal minor cuts and wounds, making it an essential addition to any skincare routine. The texture is creamy and moisturizing, leaving the skin feeling soft without stripping away natural moisture. Certified organic and free from harsh chemicals, sulfates, and parabens, this soap is suitable for all skin types, particularly those prone to irritation. Regular use helps in maintaining a healthy skin barrier while providing a calming aromatherapeutic experience during every bath. Experience the purity of traditional soap-making combined with modern dermatological benefits for refreshed, healthy skin.</v>
+      </c>
+      <c r="J257" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-patchouli-soap</v>
+      </c>
+      <c r="K257" t="str">
+        <v>rustic-art-rose-sandal-body-wash7</v>
+      </c>
+      <c r="L257" t="str">
+        <v>Patchouli Soap (100gm)</v>
+      </c>
+      <c r="M257" t="str">
+        <v>Patchouli Soap, Organic Soap, Handmade Soap, Natural Body Care, Rustic Art, Cold Process Soap, Skin Regeneration, Anti Fungal Soap, Anti Inflammatory, Deodorizing Soap, Essential Oils, Patchouli Oil, Cedarwood Oil, Linseed Oil, Chemical Free Soap, Sulfate Free, Paraben Free, Vegan Soap, Cruelty Free, Sustainable Beauty, Herbal Soap, Aromatherapy Soap, Earthy Fragrance, Skin Repair, Healing Soap, Sensitive Skin, Eco Friendly, Indian Brand, Bath and Body, Daily Hygiene, Nourishing Soap, Moisturizing Soap, Artisan Soap, Traditional Soap, Wellness</v>
+      </c>
+      <c r="N257" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P257" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q257" t="b">
+        <v>0</v>
+      </c>
+      <c r="R257" t="b">
+        <v>0</v>
+      </c>
+      <c r="S257" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>pc14</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Sandal Soap</v>
+      </c>
+      <c r="D258" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Sandal_Soap_100gm_Rustic_Art_96c344af021f08da_1024x.jpg?v=1768722534</v>
+      </c>
+      <c r="E258" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F258" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G258">
+        <v>200</v>
+      </c>
+      <c r="H258" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I258" t="str">
+        <v>Rustic Art Organic Sandal Soap is a premium hand-crafted bathing bar designed for those seeking a rejuvenated and youthful appearance. Infused with the timeless benefits of sandalwood, this soap acts as a powerful anti-ageing ally that helps maintain skin elasticity and glow. It is highly effective in removing tan, treating acne, and soothing skin inflammation. The signature fragrance is a sophisticated blend of sandalwood, cedar wood, and patchouli, which not only leaves a rich, long-lasting aroma but also provides a distinct cooling effect post-use. Patchouli works to naturally deodorize the skin, while the base oils provide deep hydration for a supple feel. This soap is formulated without harsh chemicals, ensuring a gentle yet effective cleanse suitable for daily use. Its texture is firm and produces a creamy lather that rinses off easily. Ideal for all skin types, especially those prone to irritation or sun damage. To use, wet skin, apply the soap to create a lather, and rinse thoroughly. This organic product is certified to be eco-friendly and vegan, aligning with sustainable personal care practices.</v>
+      </c>
+      <c r="J258" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-sandal-soap</v>
+      </c>
+      <c r="K258" t="str">
+        <v>rustic-art-rose-sandal-body-wash7</v>
+      </c>
+      <c r="L258" t="str">
+        <v>Sandal Soap (100gm)</v>
+      </c>
+      <c r="M258" t="str">
+        <v>Sandal soap, organic soap, handmade soap, anti-ageing soap, acne treatment, tan removal, cooling soap, rustic art, vegan soap, natural skincare, body care, aromatherapy soap, sandalwood, patchouli, cedarwood, herbal soap, chemical free, paraben free, sulfate free, sustainable beauty, indian skincare, traditional soap, artisanal soap, skin inflammation, deodorizing soap, hydrating soap, eco friendly, toxin free, handcrafted soap, daily essential, bath and shower</v>
+      </c>
+      <c r="N258" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P258" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q258" t="b">
+        <v>0</v>
+      </c>
+      <c r="R258" t="b">
+        <v>0</v>
+      </c>
+      <c r="S258" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>pc15</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Organic Orange &amp; Cinnamon Soap</v>
+      </c>
+      <c r="D259" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Orange_Cinnamon_Soap_100gm_Rustic_Art_10979760b58388be_1024x.jpg?v=1768722532</v>
+      </c>
+      <c r="E259" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F259" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G259">
+        <v>178</v>
+      </c>
+      <c r="H259" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I259" t="str">
+        <v>Rustic Art Orange &amp; Cinnamon Soap is a powerful organic cleanser designed to combat acne and skin inflammation effectively. Infused with the potent combination of orange and cinnamon, this soap not only prevents breakouts but actively targets the bacteria responsible for skin irritation. It is further enriched with turmeric oil, renowned for its antibacterial properties, providing a multi-layered defense against acne-causing agents. Beyond its cleansing capabilities, this soap aids in the natural healing process of minor cuts, wounds, and burns, making it a versatile addition to your hygiene routine. The lingering citrus and spicy fragrance provides a mood-boosting sensory experience, leaving you feeling refreshed and happy throughout the day. Its smooth texture ensures a gentle yet thorough cleanse without stripping the skin of essential moisture. This eco-friendly soap is formulated with organic ingredients, free from harsh chemicals, and is suitable for various skin types prone to inflammation. Regular use promotes a clearer, healthier complexion while providing the soothing benefits of natural essential oils and traditional Ayurvedic ingredients for holistic skin health.</v>
+      </c>
+      <c r="J259" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-orange-cinnamon-soap</v>
+      </c>
+      <c r="K259" t="str">
+        <v>rustic-art-neem-soap</v>
+      </c>
+      <c r="L259" t="str">
+        <v>Orange &amp; Cinnamon Soap (100gm)</v>
+      </c>
+      <c r="M259" t="str">
+        <v>Organic Soap, Orange Soap, Cinnamon Soap, Acne Treatment, Antibacterial Soap, Natural Skin Care, Rustic Art, Handmade Soap, Turmeric Oil, Healing Soap, Body Care, Vegan Soap, Chemical Free, Ayurvedic Soap, Essential Oils, Skin Inflammation, Clear Skin, Citrus Soap, Spicy Fragrance, Eco Friendly, Sustainable Beauty, Herbal Soap, Deep Cleansing, Moisturizing Soap, Sensitive Skin, Indian Skincare, Cold Processed, Bio Degradable, Cruelty Free, Bath and Body, Daily Hygiene, Aromatherapy, Detox Soap, Pimple Care, Radiant Skin, Natural Glow, Holistic Beauty, Artisan Soap, Non Toxic, Paraben Free, Sulfate Free, Phthalate Free, Skin Healing, Refreshing Soap, Mood Enhancer</v>
+      </c>
+      <c r="N259" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P259" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q259" t="b">
+        <v>0</v>
+      </c>
+      <c r="R259" t="b">
+        <v>0</v>
+      </c>
+      <c r="S259" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>pc16</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Organic Neem Soap</v>
+      </c>
+      <c r="D260" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Neem_Soap_100gm_Rustic_Art_616ebaf018451eb2_1024x.jpg?v=1768722531</v>
+      </c>
+      <c r="E260" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F260" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G260">
+        <v>178</v>
+      </c>
+      <c r="H260" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I260" t="str">
+        <v>Rustic Art Organic Neem Soap is a premium cold-processed antibacterial soap specifically formulated for sensitive skin. This 100gm bar is crafted using certified organic neem, basil, eucalyptus, and lemongrass oils, providing a gentle yet effective cleansing experience. Its natural antifungal and anti-acne properties make it ideal for managing skin irritations and breakouts while maintaining skin health. The texture is smooth and provides a rich, creamy lather that leaves the skin feeling refreshed without stripping away natural moisture. Free from harsh chemicals, it ensures a safe and eco-friendly bathing routine. Regular use helps in soothing inflammation and preventing bacterial growth. This artisanal soap is biodegradable and follows sustainable manufacturing practices. Suitable for daily use on the body and face, it delivers the therapeutic benefits of traditional Ayurvedic herbs in a modern, convenient format.</v>
+      </c>
+      <c r="J260" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-neem-soap</v>
+      </c>
+      <c r="K260" t="str">
+        <v>rustic-art-neem-soap</v>
+      </c>
+      <c r="L260" t="str">
+        <v>Organic Neem Soap</v>
+      </c>
+      <c r="M260" t="str">
+        <v>Organic Neem Soap, Rustic Art, Antibacterial Soap, Neem Basil Soap, Natural Antifungal, Anti-Acne Soap, Cold Processed Soap, Sensitive Skin Care, Organic Body Care, Herbal Soap, Eucalyptus Oil, Lemongrass Oil, Sustainable Beauty, Vegan Soap, Biodegradable Soap, Chemical Free Soap, Ayurvedic Skin Care, Deep Cleansing, Eco Friendly, Handmade Soap, Indian Skin Care, Soothing Soap, Skin Inflammation, Healthy Skin, Daily Hygiene, Bath and Body, Natural Ingredients, Detoxifying Soap, Clear Skin, Non Toxic</v>
+      </c>
+      <c r="N260" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P260" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q260" t="b">
+        <v>0</v>
+      </c>
+      <c r="R260" t="b">
+        <v>0</v>
+      </c>
+      <c r="S260" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>pc17</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Lemon Charcoal Soap (100gm)</v>
+      </c>
+      <c r="D261" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Lemon_Charcoal_Soap_100gm_Rustic_Art_e6321e54354117d3_1024x.jpg?v=1768722530</v>
+      </c>
+      <c r="E261" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F261" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G261">
+        <v>178</v>
+      </c>
+      <c r="H261" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I261" t="str">
+        <v>The Rustic Art Organic Lemon Charcoal Soap is a professional-grade deep oil excavator designed to provide intense cleansing for the skin. Formulated with organic ingredients, this soap effectively removes excess oil, grime, and environmental pollutants from the pores. It features activated charcoal, known for its powerful detoxifying properties, which draws out impurities while the zesty lemon extract provides additional cleansing power and a refreshing citric fragrance. This soap is an excellent choice for individuals with oily or acne-prone skin, as it helps maintain a matte finish without stripping the skin of essential moisture. Its rich, creamy lather is derived from a blend of cold-pressed oils including organic coconut, neem, and mahua, ensuring a nourishing bath experience. Free from synthetic fragrances, dyes, and harsh chemicals like sulfates or parabens, this soap is both eco-friendly and skin-safe. Certified organic and vegan, it embodies a sustainable lifestyle. Regular usage leaves the skin feeling exceptionally clean, smooth, and revitalized with a balanced texture that lasts throughout the day.</v>
+      </c>
+      <c r="J261" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-lemon-charcoal-soap</v>
+      </c>
+      <c r="K261" t="str">
+        <v>rustic-art-neem-soap</v>
+      </c>
+      <c r="L261" t="str">
+        <v>Lemon Charcoal Soap (100gm)</v>
+      </c>
+      <c r="M261" t="str">
+        <v>Rustic Art, Lemon Charcoal Soap, Organic Soap, Natural Body Care, Activated Charcoal Soap, Deep Cleansing, Oily Skin Solution, Handmade Soap, Vegan Skincare, Cruelty-Free, Paraben-Free, Sulfate-Free, Eco-Friendly Bathing, Sustainable Beauty, Cold Pressed Soap, Detoxifying Soap, Men's Grooming, Women's Skincare, Citric Fragrance, Skin Detox, Pore Cleansing, Chemical-Free Soap, Indian Skincare Brand, Ayurvedic Ingredients, Coconut Oil Soap, Neem Oil Soap, Mahua Oil Soap, Anti-Acne Soap, Refreshing Bath, Natural Exfoliation, Biodegradable, Plastic-Free, Essential Oils, Pure Ingredients, Skin Brightening, Healthy Skin, Daily Cleanser, Organic Certified, Zero Waste, Holistic Beauty, Traditional Soap Making, Radiant Skin, Skin Rejuvenation, Non-Toxic, Artisan Soap, Herbal Soap</v>
+      </c>
+      <c r="N261" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P261" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q261" t="b">
+        <v>0</v>
+      </c>
+      <c r="R261" t="b">
+        <v>0</v>
+      </c>
+      <c r="S261" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>pc18</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Jasmine Soap (100gm)</v>
+      </c>
+      <c r="D262" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Lavender_Soap_100gm_Rustic_Art_ec5152aa476c215b_1024x.jpg?v=1768722530</v>
+      </c>
+      <c r="E262" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F262" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G262">
+        <v>178</v>
+      </c>
+      <c r="H262" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I262" t="str">
+        <v>Rustic Art Organic Lavender Soap is designed to provide a calming and soothing bathing experience. Infused with the gentle fragrance of lavender, it helps regulate mood and triggers the sleep senses of the brain, making it perfect for relaxation. This deep-cleansing soap is a versatile workhorse for skin care, enriched with Lemon and Orange to brighten and refresh the skin. Handcrafted with organic ingredients, it features a rich, creamy lather that leaves skin feeling soft and clean without harsh chemicals. Lavender's natural properties provide all-around care for both the skin and the mind. Ideal for daily use, this soap is free from synthetic fragrances and colors. The texture is firm yet smooth, ensuring a long-lasting bar. It is certified organic and vegan, aligning with eco-friendly grooming standards. Usage involves lathering the soap between wet palms or on a washcloth and applying it to the body before rinsing thoroughly.</v>
+      </c>
+      <c r="J262" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-lavender-soap</v>
+      </c>
+      <c r="K262" t="str">
+        <v>rustic-art-neem-soap</v>
+      </c>
+      <c r="L262" t="str">
+        <v>Jasmine Soap (100gm)</v>
+      </c>
+      <c r="M262" t="str">
+        <v>Lavender Soap, Organic Soap, Rustic Art, Body Care, Handmade Soap, Natural Cleanser, Calming Soap, Skin Care, Aromatherapy, Vegan Soap, Chemical Free, Essential Oils, Lavender Oil, Deep Cleansing, Eco Friendly, Sustainable Beauty, Herbal Soap, Brightening Soap, Orange Oil, Lemon Oil, Relaxation, Bath and Body, Cruelty Free, Indian Beauty, Holistic Care, Sleep Aid, Mood Enhancer, Cold Processed, Organic Ingredients, Nourishing Soap, Refreshing Bath, Gentle Cleansing, Toxic Free, Paraben Free, Sulfate Free, Artisanal Soap, Luxury Bathing, Healthy Skin, Glowing Skin, Moisturizing Soap</v>
+      </c>
+      <c r="N262" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P262" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q262" t="b">
+        <v>0</v>
+      </c>
+      <c r="R262" t="b">
+        <v>0</v>
+      </c>
+      <c r="S262" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>pc19</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Jasmine Soap (100gm)</v>
+      </c>
+      <c r="D263" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Jasmine_Soap_100gm_Rustic_Art_662bfb95301c0e13_1024x.jpg?v=1768722528</v>
+      </c>
+      <c r="E263" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F263" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G263">
+        <v>198</v>
+      </c>
+      <c r="H263" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I263" t="str">
+        <v>Rustic Art Jasmine Soap is a luxurious handcrafted bathing bar designed to transport you to a world of serenity and skin rejuvenation. Infused with the exquisite essence of Jasmine, this soap does more than just cleanse; it actively protects your skin from environmental stressors and natural pollutants. One of the standout ingredients is Peanut oil, which is naturally rich in resveratrol—a potent antioxidant that effectively promotes healthy skin growth while ensuring deep nourishment and hydration. The inclusion of Ylang Ylang further enhances the experience, contributing to a youthful appearance and an uplifted mood, helping to lower daily stress levels through aromatherapeutic benefits. This soap features a smooth, creamy lather and a delicate floral fragrance that lingers pleasantly. Ideal for daily use in the bath or shower, it caters to those seeking a natural, chemical-free skincare routine. By combining traditional soap-making methods with high-quality organic oils, Rustic Art ensures a product that is as kind to the planet as it is to your skin, making it a perfect addition to any holistic personal care regimen.</v>
+      </c>
+      <c r="J263" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-jasmine-soap</v>
+      </c>
+      <c r="K263" t="str">
+        <v>rustic-art-neem-soap</v>
+      </c>
+      <c r="L263" t="str">
+        <v>Jasmine Soap (100gm)</v>
+      </c>
+      <c r="M263" t="str">
+        <v>Jasmine Soap, Rustic Art, Natural Soap, Organic Skin Care, Handmade Soap, Bath and Body, Essential Oils, Peanut Oil Skincare, Antioxidant Soap, Resveratrol, Ylang Ylang, Floral Fragrance, Stress Relief, Skin Rejuvenation, Nourishing Soap, Chemical Free, Vegan Soap, Cruelty Free, Sustainable Beauty, Indian Skin Care, Aromatherapy, Gentle Cleanser, Radiant Skin, Youthful Glow, Traditional Soap, Herbal Bathing, Eco-Friendly, Moisturizing Soap, Skin Protection, Detox Soap, Luxury Soap, Jasmine Oil, Holistic Care, Bath Essentials, Daily Skincare, Natural Ingredients, Handcrafted Beauty, Refreshing Soap, Soothing Lather, Healthy Skin, Bio-degradable, No Parabens, No Sulfates, Non-Toxic, Pure Essential Oils, Body Care, Hygiene Care</v>
+      </c>
+      <c r="N263" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P263" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q263" t="b">
+        <v>0</v>
+      </c>
+      <c r="R263" t="b">
+        <v>0</v>
+      </c>
+      <c r="S263" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>pc20</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Exfoliate Soap (100gm)</v>
+      </c>
+      <c r="D264" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Exfoliate_Soap_100gm_Rustic_Art_8a97b1d06ef4558a_1024x.jpg?v=1768722525</v>
+      </c>
+      <c r="E264" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F264" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G264">
+        <v>178</v>
+      </c>
+      <c r="H264" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I264" t="str">
+        <v>Rustic Art Exfoliate Soap is a premium body care solution designed to refresh and rejuvenate your skin through natural exfoliation. Formulated with potent ingredients like Cypress oil and Lavender oil, it effectively helps you bid farewell to dead skin cells, whiteheads, and blackheads, revealing a smooth and glowing complexion. Cypress oil contains monoterpenes, which are specifically beneficial for improving the appearance of oily skin by balancing sebum. The perfect combination of cypress and lavender oils provides a calming effect on the mind, significantly uplifting your mood post-shower. This cold-processed, handmade soap is crafted without harmful chemicals or palm oil, ensuring a natural and eco-friendly cleansing experience. The texture provides a gentle yet effective scrub that is suitable for regular use. It is vegan, cruelty-free, and adheres to high standards of organic personal care. Regular usage helps in deep pore cleansing, maintaining skin elasticity, and providing a healthy, radiant look. Ideal for all skin types, this soap turns a daily chore into a therapeutic aromatherapy session.</v>
+      </c>
+      <c r="J264" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-exfoliate-soap</v>
+      </c>
+      <c r="K264" t="str">
+        <v>rustic-art-neem-soap</v>
+      </c>
+      <c r="L264" t="str">
+        <v>Exfoliate Soap (100gm)</v>
+      </c>
+      <c r="M264" t="str">
+        <v>Exfoliate Soap, Rustic Art, Body Care, Natural Soap, Handmade Soap, Cold Processed Soap, Cypress Oil, Lavender Oil, Dead Skin Removal, Blackhead Treatment, Whitehead Treatment, Glowing Skin, Oily Skin Solution, Vegan Skincare, Cruelty-Free, Palm Oil Free, Sustainable Beauty, Organic Body Soap, Aromatherapy Bath, Refreshing Soap, Skin Rejuvenation, Pore Cleansing, Natural Exfoliant, Bath and Shower, Herbal Soap, Indian Skincare Brand, Artisanal Soap, Chemical Free Soap, Smooth Skin, Essential Oils Soap, Daily Cleanser, Healthy Skin</v>
+      </c>
+      <c r="N264" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P264" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q264" t="b">
+        <v>0</v>
+      </c>
+      <c r="R264" t="b">
+        <v>0</v>
+      </c>
+      <c r="S264" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>pc21</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Facial Soap (100gm)</v>
+      </c>
+      <c r="D265" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Facial_Soap_100gm_Rustic_Art_daae46434d1da23f_1024x.jpg?v=1768722526</v>
+      </c>
+      <c r="E265" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F265" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G265">
+        <v>200</v>
+      </c>
+      <c r="H265" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I265" t="str">
+        <v>Rustic Art Facial Soap is a powerful, organic solution designed for deep cleansing and purifying the skin. A name that's no stranger to the conscious consumer, this soap is specifically formulated to target blackheads, whiteheads, and acne right from the roots. The unique blend features organic essential oils of Nutmeg, Cedarwood, Tea Tree, and Turmeric, which provide potent anti-bacterial and anti-fungal properties to keep the skin healthy and clear. These ingredients work in harmony to ensure that blemishes do not last long on your face while maintaining the skin's natural moisture. Handcrafted using the cold-process method, the soap retains all the natural glycerin and goodness of its botanical oils. The texture is smooth and creates a rich, creamy lather that feels gentle yet effective on the skin. Ideal for oily and combination skin types, it leaves the face feeling refreshed and detoxified. This product is certified organic, cruelty-free, and vegan, reflecting a commitment to sustainable and ethical beauty. Simply lather on a wet face, massage gently, and rinse for a revitalized complexion.</v>
+      </c>
+      <c r="J265" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-facial-soap</v>
+      </c>
+      <c r="K265" t="str">
+        <v>rustic-art-neem-soap</v>
+      </c>
+      <c r="L265" t="str">
+        <v>Facial Soap (100gm)</v>
+      </c>
+      <c r="M265" t="str">
+        <v>Skin Care, Facial Soap, Organic Soap, Rustic Art, Acne Control, Blackhead Removal, Whiteheads, Nutmeg Oil, Cedarwood Oil, Tea Tree Oil, Turmeric Oil, Anti-bacterial, Anti-fungal, Oily Skin Care, Natural Cleanser, Handcrafted Soap, Vegan Skin Care, Cruelty Free, Chemical Free, Cold Processed Soap, Clear Skin, Blemish Control, Deep Cleansing, Eco-friendly Beauty, Sustainable Skincare, Herbal Soap, Face Wash Alternative, Pure Essential Oils, Purifying Soap, Ayurvedic, Bio-degradable, No Sulphates, No Parabens, Natural Beauty</v>
+      </c>
+      <c r="N265" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P265" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q265" t="b">
+        <v>0</v>
+      </c>
+      <c r="R265" t="b">
+        <v>0</v>
+      </c>
+      <c r="S265" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>pc22</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Aloevera Soap (100gm)</v>
+      </c>
+      <c r="D266" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Aloevera_Soap_100gm_Rustic_Art_f60919ddbd46b3f6_1024x.jpg?v=1768722516</v>
+      </c>
+      <c r="E266" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F266" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G266">
+        <v>178</v>
+      </c>
+      <c r="H266" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I266" t="str">
+        <v>The Rustic Art Aloe Vera Soap is a premium artisanal cleansing bar designed to soothe and hydrate the skin effectively. Formulated with high-quality natural ingredients like Aloe Vera, Jojoba oil, and Palmarosa, this soap provides a cooling sensation that calms skin inflammation and serves as a natural barrier against sun damage. Aloe Vera is renowned for its ability to retain moisture, making it ideal for those seeking to keep their skin soft and supple throughout the day. Jojoba oil, being rich in essential multivitamins, plays a crucial role in skin repair and damage control, while Palmarosa essential oil deeply hydrates and balances the skin's natural oils. This cold-processed soap maintains the integrity of its nutrients, offering a rich, creamy lather that cleanses without stripping away natural moisture. Suitable for all skin types, it is especially beneficial for sensitive or sun-exposed skin. Regular use promotes a healthy, glowing complexion. Handcrafted with care, this soap reflects Rustic Art's commitment to sustainable, vegan, and chemical-free personal care solutions, ensuring your daily shower routine is both eco-friendly and luxuriously nourishing.</v>
+      </c>
+      <c r="J266" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-aloevera-soap</v>
+      </c>
+      <c r="K266" t="str">
+        <v>rustic-art-neem-soap</v>
+      </c>
+      <c r="L266" t="str">
+        <v>Aloevera Soap (100gm)</v>
+      </c>
+      <c r="M266" t="str">
+        <v>Soap, Aloe Vera, Handmade Soap, Natural Skin Care, Body Care, Rustic Art, Vegan Soap, Organic Soap, Moisturizing Soap, Cooling Soap, Sensitive Skin, Jojoba Oil, Palmarosa, Hydrating, Sun Protection, Inflammation Relief, Chemical Free, Paraben Free, Sulfate Free, Artisanal Soap, Skin Repair, Damage Control, Cold Processed Soap, Cruelty Free, Sustainable Beauty, Herbal Soap, Bath and Shower, Daily Cleansing, Refreshing, Nourishing, Indian Skincare, Eco Friendly, Bio Degradable, Non Toxic, Skin Soothing, Radiant Glow, Healthy Skin, Essential Oils, Multivitamins, Ayurvedic, Luxury Soap, Gift Idea, Plastic Free, Zero Waste</v>
+      </c>
+      <c r="N266" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P266" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="b">
+        <v>0</v>
+      </c>
+      <c r="R266" t="b">
+        <v>0</v>
+      </c>
+      <c r="S266" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>pc23</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Baby Soap (100gm)</v>
+      </c>
+      <c r="D267" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Baby_Soap_100gm_Rustic_Art_69873afc0bd75ba9_1024x.jpg?v=1768722518</v>
+      </c>
+      <c r="E267" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F267" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G267">
+        <v>200</v>
+      </c>
+      <c r="H267" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I267" t="str">
+        <v>Rustic Art Organic Baby Soap is a meticulously crafted cleansing bar designed specifically for a baby’s delicate and developing skin. This soap offers a dual benefit of gentle cleansing while providing deep nourishment for the entire body. It features Coconut Nectar, which is naturally rich in essential amino acids that serve as the building blocks for healthy skin development. To ensure the skin remains soft and hydrated during bath time, the formula includes a potent blend of Coconut Milk and Aloe Vera, both recognized as super moisturizers. These organic ingredients work together to prevent dryness and irritation, effectively maintaining the natural moisture barrier. The texture is exceptionally smooth and creates a creamy, rich lather that rinses off easily, leaving no sticky residue. This product is completely free from harsh chemicals, synthetic fragrances, and artificial preservatives, making it safe for newborns and those with sensitive skin. It is certified organic, ensuring the highest standards of purity and environmental sustainability. Ideal for daily use, this baby soap promotes a healthy, glowing complexion while keeping the skin supple and protected.</v>
+      </c>
+      <c r="J267" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-baby-soap</v>
+      </c>
+      <c r="K267" t="str">
+        <v>rustic-art-neem-soap</v>
+      </c>
+      <c r="L267" t="str">
+        <v>Baby Soap (100gm)</v>
+      </c>
+      <c r="M267" t="str">
+        <v>Baby Soap, Organic Baby Care, Rustic Art, Gentle Cleanser, Natural Baby Soap, Coconut Nectar Soap, Coconut Milk, Aloe Vera, Sensitive Skin Care, Newborn Essentials, Chemical Free Soap, Handmade Soap, Vegan Baby Product, Sulfate Free, Paraben Free, Non Toxic, Moisturizing Soap, Skin Nourishment, Eco Friendly, Sustainable Beauty, Cruelty Free, Indian Brand, Ayurvedic Soap, Baby Bath, Soft Skin, Hypoallergenic, Cold Processed Soap, Artisan Soap, Baby Toiletries, Herbal Baby Soap, Organic Ingredients, Healthy Skin, Mild Fragrance, Safe For Kids, Toxin Free, Body Care, Personal Care, Natural Moisturizer, Skin Hydration, Bio Degradable, Plastic Free</v>
+      </c>
+      <c r="N267" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P267" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q267" t="b">
+        <v>0</v>
+      </c>
+      <c r="R267" t="b">
+        <v>0</v>
+      </c>
+      <c r="S267" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>pc24</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C268" t="str">
+        <v>Coffee Soap (100gm)</v>
+      </c>
+      <c r="D268" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Coffee_Soap_100gm_Rustic_Art_82dd11b5e0b3ae5c_1024x.jpg?v=1768722521</v>
+      </c>
+      <c r="E268" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F268" t="str">
+        <v>Body Care</v>
+      </c>
+      <c r="G268">
+        <v>178</v>
+      </c>
+      <c r="H268" t="str">
+        <v>100gm</v>
+      </c>
+      <c r="I268" t="str">
+        <v>Rustic Art Coffee Soap is the ultimate way to wake up your skin and senses. Much like a fresh cup of coffee, this soap provides a refreshing and invigorating experience that helps regulate the mood with its calming effect. Infused with potent natural ingredients like Hemp and Vanilla oil, it works effectively to slow down the aging process while providing intense moisturization to the skin. The caffeine content from the coffee helps in reducing the appearance of dark circles and aids in balancing skin contours for a smoother, more toned look. This handcrafted bar is cold-processed to ensure that the vital nutrients and moisturizing properties of the oils remain intact. It features a rich, creamy lather and a firm texture that cleanses deeply without being harsh. Free from sulfates, parabens, and synthetic fragrances, this vegan soap is perfect for those seeking a sustainable and eco-friendly bathing solution. Ideal for daily use in the bath or shower, it leaves your skin feeling hydrated, rejuvenated, and glowing with health.</v>
+      </c>
+      <c r="J268" t="str">
+        <v>https://www.rusticart.in/collections/bath-shower/products/rustic-art-coffee-soap</v>
+      </c>
+      <c r="K268" t="str">
+        <v>rustic-art-neem-soap</v>
+      </c>
+      <c r="L268" t="str">
+        <v>Coffee Soap (100gm)</v>
+      </c>
+      <c r="M268" t="str">
+        <v>Coffee Soap, Rustic Art, Body Care, Natural Soap, Handmade Soap, Organic Skincare, Hemp Oil Soap, Vanilla Oil, Anti-Aging Soap, Moisturizing Soap, Dark Circle Reduction, Skin Contouring, Cold Processed Soap, Vegan Soap, Chemical Free, Paraben Free, Sulfate Free, Sustainable Beauty, Eco-friendly Personal Care, Bath and Body, Skin Rejuvenation, Morning Routine, Calming Effect, Artisan Soap, Herbal Soap, Bio-degradable, Indian Beauty Brand, Cruelty Free, Glowing Skin, Refreshing Bath, Aromatic Soap, Skin Hydration, Luxury Soap, Natural Cleanser, Daily Essentials, Coffee Infused, Non-Toxic Skincare, Gentle Cleansing, Body Wash Alternative</v>
+      </c>
+      <c r="N268" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P268" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q268" t="b">
+        <v>0</v>
+      </c>
+      <c r="R268" t="b">
+        <v>0</v>
+      </c>
+      <c r="S268" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>pc25</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C269" t="str">
+        <v>Neem Basil Face Wash Concentrate (50gm)</v>
+      </c>
+      <c r="D269" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Neem_Basil_Face_Wash_Concentrate_50gm_Rustic_Art_89186899a141b81a_1024x.webp?v=1768722394</v>
+      </c>
+      <c r="E269" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F269" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G269">
+        <v>200</v>
+      </c>
+      <c r="H269" t="str">
+        <v>50gm</v>
+      </c>
+      <c r="I269" t="str">
+        <v>Rustic Art Neem Basil Face Wash Concentrate is a premium organic solution specifically formulated for oily and acne-prone skin. This deep cleansing concentrate is enriched with the potent antibacterial and antifungal properties of neem and basil, which work together to unclog pores, control excess oil production, and prevent future breakouts. Being a concentrate, this product is highly efficient, lasting up to three times longer than conventional liquid face washes, making it an eco-friendly and travel-convenient choice. It is completely free from SLS, parabens, and synthetic fragrances, ensuring a safe and natural skincare routine. The texture is a unique paste-like consistency that lathers beautifully with water to provide a refreshing and cooling sensation. Key benefits include improved skin clarity, reduced inflammation, and a balanced complexion without over-drying. This vegan and cruelty-free product is certified organic, reflecting a commitment to purity and environmental sustainability. For best results, use a pea-sized amount on wet skin, massaging gently to remove impurities and leave the face feeling rejuvenated and clean.</v>
+      </c>
+      <c r="J269" t="str">
+        <v>https://www.rusticart.in/collections/organic-face-wash/products/rustic-art-neem-basil-face-wash-concentrate</v>
+      </c>
+      <c r="K269" t="str">
+        <v>rustic-art-neem-basil-face-wash-concentrate1</v>
+      </c>
+      <c r="L269" t="str">
+        <v>Neem Basil Face Wash Concentrate (50gm)</v>
+      </c>
+      <c r="M269" t="str">
+        <v>organic face wash, neem face wash, basil face wash, anti acne face wash, oily skin care, natural face wash, sls free, paraben free, rustic art, face wash concentrate, travel size face wash, deep cleansing, acne control, pimple control, vegan skincare, cruelty free, organic beauty, herbal face wash, pore cleanser, skin detox, essential oil face wash, eco friendly skincare, sustainable beauty, indian skincare brand, chemical free, organic neem, organic basil, anti bacterial face wash, skin clearing, matte finish, ayurvedic face wash, concentrated face wash, clear skin, natural glow, non toxic beauty, bio degradable, artisan face wash, foaming face wash, daily face wash, grooming, skincare routine</v>
+      </c>
+      <c r="N269" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P269" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="b">
+        <v>0</v>
+      </c>
+      <c r="R269" t="b">
+        <v>0</v>
+      </c>
+      <c r="S269" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>pc26</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C270" t="str">
+        <v>Sandal Face Wash Concentrate (50gm)</v>
+      </c>
+      <c r="D270" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Sandal_Face_Wash_Concentrate_50gm_Rustic_Art_1ee37fad0fda36d4_1024x.png?v=1768722497</v>
+      </c>
+      <c r="E270" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F270" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G270">
+        <v>200</v>
+      </c>
+      <c r="H270" t="str">
+        <v>50gm</v>
+      </c>
+      <c r="I270" t="str">
+        <v>Rustic Art Sandal Face Wash Concentrate is a unique, organic, and vegan mild soap paste that brings the traditional benefits of Haldi and Chandan to your daily skincare routine. Formulated with natural ingredients, this face wash concentrate is designed to suit all skin types, providing a deep yet gentle cleanse. Sandalwood, known for its soothing properties, helps in reducing blemishes, preventing acne whiteheads, and removing unwanted tan, while leaving a refreshing cooling effect on the skin after every wash. This water-efficient concentrate requires only a small amount to create a rich lather, making it a sustainable choice for conscious consumers. The inclusion of turmeric (Haldi) offers anti-inflammatory and antioxidant benefits, promoting a radiant and even skin tone. This product is free from harsh chemicals, synthetic fragrances, and preservatives, ensuring a pure and safe experience. Its thick, paste-like texture ensures a luxurious feel, while the natural aroma provides a calming sensory experience. Certified as organic and vegan, it is an ideal solution for those seeking traditional herbal wisdom combined with modern eco-friendly packaging. Use daily to maintain healthy, glowing, and blemish-free skin effortlessly.</v>
+      </c>
+      <c r="J270" t="str">
+        <v>https://www.rusticart.in/collections/organic-face-wash/products/rustic-art-sandal-face-wash-concentrate</v>
+      </c>
+      <c r="K270" t="str">
+        <v>rustic-art-neem-basil-face-wash-concentrate1</v>
+      </c>
+      <c r="L270" t="str">
+        <v>Sandal Face Wash Concentrate (50gm)</v>
+      </c>
+      <c r="M270" t="str">
+        <v>Sandal Face Wash, Organic Skin Care, Vegan Face Wash, Rustic Art, Haldi Chandan, Natural Cleanser, Blemish Reduction, Acne Prevention, Tan Removal, Cooling Face Wash, Soap Paste, Herbal Beauty, Chemical Free, Sustainable Skincare, Handcrafted, Indian Skincare, Turmeric Face Wash, Sandalwood Benefits, Eco Friendly, Non Toxic, Cruelty Free, Glowing Skin, Daily Face Wash, Mild Cleanser, Concentrated Face Wash, Ayurvedic Skincare, Skin Brightening, Organic Ingredients, Plastic Free, Traditional Beauty, Radiant Complexion, Paraben Free, Sulphate Free, Essential Oils, Natural Glow, Deep Cleansing, Sensitive Skin Safe, Detoxifying Face Wash, Refreshing Wash, Zero Waste Beauty</v>
+      </c>
+      <c r="N270" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P270" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q270" t="b">
+        <v>0</v>
+      </c>
+      <c r="R270" t="b">
+        <v>0</v>
+      </c>
+      <c r="S270" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>pc27</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Geranium Charcoal Face Wash Concentrate (50gm)</v>
+      </c>
+      <c r="D271" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Geranium_Charcoal_Face_Wash_Concentrate_50gm_Rustic_Art_8133e1dd7cedaf3c_1024x.png?v=1768722496</v>
+      </c>
+      <c r="E271" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F271" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G271">
+        <v>200</v>
+      </c>
+      <c r="H271" t="str">
+        <v>50gm</v>
+      </c>
+      <c r="I271" t="str">
+        <v>Rustic Art Geranium Charcoal Face Wash Concentrate is an innovative, organic, and vegan mild soap paste designed specifically for oily to normal skin types, particularly those prone to whiteheads. This high-performance concentrate is packed with the deep-cleansing power of activated charcoal, which effectively mines impurities, toxins, and excess oil from deep within the skin pores. Enriched with a therapeutic blend of essential oils including Geranium, Patchouli, and Peppermint, it offers a calming fragrance and a cooling, refreshing sensation. The formula is a unique water-efficient concentrate, meaning a small pea-sized amount is sufficient for a thorough cleanse, making it exceptionally travel-friendly and long-lasting. It creates a rich, creamy lather that leaves the skin feeling clean, balanced, and rejuvenated without stripping away essential moisture or disrupting the natural pH balance. Certified organic and completely free from synthetic fragrances, preservatives, or harsh chemicals, it ensures a natural glow and significantly refined skin texture. Usage involves massaging a tiny amount onto a wet face and rinsing thoroughly. This face wash is a sustainable, zero-waste choice for conscious consumers looking for high-impact, nature-based skincare solutions that deliver visible results.</v>
+      </c>
+      <c r="J271" t="str">
+        <v>https://www.rusticart.in/collections/organic-face-wash/products/rustic-art-geranium-charcoal-face-wash-concentrate</v>
+      </c>
+      <c r="K271" t="str">
+        <v>rustic-art-neem-basil-face-wash-concentrate1</v>
+      </c>
+      <c r="L271" t="str">
+        <v>Geranium Charcoal Face Wash Concentrate (50gm)</v>
+      </c>
+      <c r="M271" t="str">
+        <v>Rustic Art, Geranium Charcoal Face Wash, Organic Face Wash, Vegan Skincare, Natural Cleanser, Charcoal Cleanser, Deep Cleansing, Oily Skin Care, Whiteheads Treatment, Essential Oils, Patchouli, Peppermint, Eco-friendly Beauty, Sustainable Skincare, Waterless Beauty, Concentrated Face Wash, Chemical Free, Paraben Free, Sulfate Free, Handmade Soap Paste, Ayurvedic Skincare, Indian Beauty Brand, Pore Cleansing, Skin Detox, Organic Ingredients, Cruelty Free, Travel Friendly Beauty, Skin Rejuvenation, Natural Glow, Mild Soap, Bio-degradable, Zero Waste, Men's Grooming, Unisex Face Wash, Skin Refining, Acne Prone Skin, Non Toxic Beauty, Holistic Skincare, Rustic Art Skincare, Activated Charcoal</v>
+      </c>
+      <c r="N271" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P271" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q271" t="b">
+        <v>0</v>
+      </c>
+      <c r="R271" t="b">
+        <v>0</v>
+      </c>
+      <c r="S271" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>pc28</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Wild Rose Face Wash Concentrate (50gm)</v>
+      </c>
+      <c r="D272" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Wild_Rose_Face_Wash_Concentrate_50gm_Rustic_Art_a2d1e66e3cad7ad7_1024x.png?v=1768722494</v>
+      </c>
+      <c r="E272" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F272" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G272">
+        <v>200</v>
+      </c>
+      <c r="H272" t="str">
+        <v>50gm</v>
+      </c>
+      <c r="I272" t="str">
+        <v>Rustic Art Wild Rose Face Wash Concentrate is a premium, organic, natural, and vegan mild soap paste specifically formulated for dry to normal skin types. This unique concentrate features the goodness of almonds, which help rejuvenate the skin after a long, exhausting day, while Mango Butter and Glycerin provide deep hydration and nourishment. Unlike traditional liquid face washes, this concentrate is water-efficient and requires a very small amount for a thorough cleanse. The presence of wild rose extract offers a gentle floral aroma and soothing properties, leaving your skin feeling soft, supple, and glowing. It is free from harsh chemicals, sulphates, and parabens, making it an eco-friendly choice for conscious consumers. The creamy texture of the soap paste transforms into a rich lather that effectively removes impurities without stripping the skin of its natural oils. This product is certified organic and emphasizes sustainability through its concentrated form, making it a perfect addition to a clean beauty routine.</v>
+      </c>
+      <c r="J272" t="str">
+        <v>https://www.rusticart.in/collections/organic-face-wash/products/rustic-art-wild-rose-face-wash-concentrate</v>
+      </c>
+      <c r="K272" t="str">
+        <v>rustic-art-neem-basil-face-wash-concentrate1</v>
+      </c>
+      <c r="L272" t="str">
+        <v>Wild Rose Face Wash Concentrate (50gm)</v>
+      </c>
+      <c r="M272" t="str">
+        <v>organic face wash, wild rose skin care, vegan soap paste, natural face wash, rustic art concentrate, almond oil face wash, mango butter skin care, chemical free cleanser, sulfate free face wash, paraben free skin care, eco friendly beauty, sustainable skin care, hydrating face wash, dry skin cleanser, normal skin care, rose extract beauty, ayurvedic face wash, handcrafted soap, cruelty free cleanser, water efficient beauty, luxury skin care, glowing skin secret, herbal face wash, botanical cleanser, skin nourishment, deep hydration, mild face wash, non toxic beauty, indian skincare brand, organic beauty products, face wash for women, face wash for men, daily skin routine, aromatic face wash, rose scented cleanser, premium soap paste, biodegradable face wash, travel friendly skincare, artisan beauty, natural glow, clear skin routine, healthy skin products, essential oil skincare</v>
+      </c>
+      <c r="N272" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P272" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q272" t="b">
+        <v>0</v>
+      </c>
+      <c r="R272" t="b">
+        <v>0</v>
+      </c>
+      <c r="S272" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>pc29</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Juniper Berry Face Wash Concentrate (50gm)</v>
+      </c>
+      <c r="D273" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/face_wash_50g_3_1024x.png?v=1765520127</v>
+      </c>
+      <c r="E273" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F273" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G273">
+        <v>200</v>
+      </c>
+      <c r="H273" t="str">
+        <v>50gm</v>
+      </c>
+      <c r="I273" t="str">
+        <v>Indulge in the refreshing goodness of citrus fruits with the Rustic Art Juniper Berry Face Wash Concentrate. This organic, natural, and vegan soap paste is specially formulated for dry to normal skin types. Featuring a potent blend of Juniper berry, Orange, Grapeseed, Lime, and Olive oils, it acts like a fruit basket for your fatigued skin. The deep cleansing formula effectively removes dirt and pollution while maintaining the skin's natural moisture balance. As a concentrate, it requires only a small amount per wash, making it highly efficient and long-lasting. The texture is a rich, mild soap paste that provides a gentle lather without harsh chemicals like sulfates or parabens. It offers antioxidant benefits that help rejuvenate and brighten the complexion. This product is eco-friendly, biodegradable, and cruelty-free, ensuring a sustainable skincare routine. Its uplifting citrus aroma provides a spa-like experience at home, leaving your face feeling fresh, clean, and radiant after every use.</v>
+      </c>
+      <c r="J273" t="str">
+        <v>https://www.rusticart.in/collections/organic-face-wash/products/rustic-art-juniper-berry-face-wash-concentrate</v>
+      </c>
+      <c r="K273" t="str">
+        <v>rustic-art-neem-basil-face-wash-concentrate1</v>
+      </c>
+      <c r="L273" t="str">
+        <v>Juniper Berry Face Wash Concentrate (50gm)</v>
+      </c>
+      <c r="M273" t="str">
+        <v>Rustic Art, Juniper Berry, Face Wash, Organic, Natural, Vegan, Skincare, Deep Cleansing, Fruit Basket, Orange Oil, Grapeseed, Lime, Olive Oil, Eco-friendly, Sustainable, No Parabens, No Sulfates, Paste, Concentrate, Dry Skin, Normal Skin, Refreshing, Antioxidant, Radiant Skin, Daily Use, Mild Soap, Chemical Free, Handmade, Indian Brand, Cruelty Free, Bio-degradable, Non-toxic, Essential Oils, Aromatherapy, Detox</v>
+      </c>
+      <c r="N273" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P273" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q273" t="b">
+        <v>0</v>
+      </c>
+      <c r="R273" t="b">
+        <v>0</v>
+      </c>
+      <c r="S273" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>pc30</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C274" t="str">
+        <v>Organic Neem Basil Face Wash</v>
+      </c>
+      <c r="D274" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Neem_Basil_Face_Wash_100ml_Rustic_Art_99cb78314b8703ac_1024x.jpg?v=1768722505</v>
+      </c>
+      <c r="E274" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F274" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G274">
+        <v>230</v>
+      </c>
+      <c r="H274" t="str">
+        <v>100ml</v>
+      </c>
+      <c r="I274" t="str">
+        <v>Rustic Art Organic Neem Basil Face Wash is a specialized anti-acne formulation designed to provide a deep cleanse while ensuring the skin remains soft and refreshed. Specifically crafted for oily and sensitive skin, this organic face wash utilizes the powerful antibacterial properties of organic neem oil and the calming, antimicrobial benefits of basil essential oil. The unique blend effectively targets active acne, reduces redness, and prevents future breakouts by regulating sebum production and removing environmental pollutants without compromising the skin's natural moisture barrier. The product features a lightweight, liquid texture that creates a mild lather, making the cleansing ritual both effective and enjoyable. It is entirely free from sulfates, parabens, synthetic fragrances, and artificial preservatives, maintaining a strictly non-toxic profile. This vegan and cruelty-free cleanser is certified organic, highlighting a dedication to sustainable beauty. Regular application helps refine skin texture, minimizes pores, and promotes a clear, radiant complexion. Suitable for daily use, it leaves the face feeling squeaky clean and revitalized.</v>
+      </c>
+      <c r="J274" t="str">
+        <v>https://www.rusticart.in/collections/organic-face-wash/products/rustic-art-neem-basil-face-wash</v>
+      </c>
+      <c r="K274" t="str">
+        <v>rustic-art-neem-basil-face-wash</v>
+      </c>
+      <c r="L274" t="str">
+        <v>100ml</v>
+      </c>
+      <c r="M274" t="str">
+        <v>organic face wash, neem face wash, basil face wash, anti acne, oily skin care, sensitive skin care, rustic art, vegan face wash, natural cleanser, chemical free, herbal face wash, skin detox, clear skin, ayurvedic skincare, sustainable beauty, cruelty free, sulfate free, paraben free, essential oils, neem oil, basil oil, face cleanser, organic beauty, eco friendly, skincare routine, acne treatment, pore cleansing, sebum control, non toxic, pure ingredients, indian beauty brand, ethical skincare, deep cleaning, refreshing wash, skin healing, antibacterial, antifungal, glow skin, daily cleanser, moisture balance, facial hygiene, organic skincare india, natural glow, zero waste beauty, cold processed, toxin free</v>
+      </c>
+      <c r="N274" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P274" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q274" t="b">
+        <v>0</v>
+      </c>
+      <c r="R274" t="b">
+        <v>0</v>
+      </c>
+      <c r="S274" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>pc31</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Sandal Face Wash (100ml)</v>
+      </c>
+      <c r="D275" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Sandal_Face_Wash_100ml_Rustic_Art_51235c120ca3054e_1024x.jpg?v=1768722507</v>
+      </c>
+      <c r="E275" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F275" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G275">
+        <v>230</v>
+      </c>
+      <c r="H275" t="str">
+        <v>100ml</v>
+      </c>
+      <c r="I275" t="str">
+        <v>Rustic Art Organic Sandal Face Wash is a luxurious, natural, and vegan cleansing solution designed to cater to all skin types. This mild face wash is formulated with pure sandalwood and enriched with turmeric essential oil, renowned for its therapeutic properties. The combination of these potent ingredients effectively reduces blemishes, prevents the formation of acne whiteheads, and efficiently removes tan, leaving the skin with a soothing cooling effect after every use. Its gentle gel texture produces a soft lather that cleanses deeply without stripping the skin of its vital moisture. This product is free from harmful chemicals, sulfates, and parabens, ensuring it is as kind to the planet as it is to your face. Certified organic and cruelty-free, it highlights the best of traditional Ayurvedic wisdom paired with modern sustainable practices. To use, apply a small amount on wet face, massage in circular motions, and rinse thoroughly. Experience a visible glow and a rich, traditional aroma that enhances your daily skincare ritual while promoting long-term skin health.</v>
+      </c>
+      <c r="J275" t="str">
+        <v>https://www.rusticart.in/collections/organic-face-wash/products/rustic-art-sandal-face-wash</v>
+      </c>
+      <c r="K275" t="str">
+        <v>rustic-art-neem-basil-face-wash</v>
+      </c>
+      <c r="L275" t="str">
+        <v>100ml</v>
+      </c>
+      <c r="M275" t="str">
+        <v>Organic Face Wash, Sandalwood Face Wash, Turmeric Cleanser, Vegan Skincare, Natural Beauty, Ayurvedic Face Wash, Anti-Acne, Tan Removal, Cooling Effect, Rustic Art, Sulfate Free, Paraben Free, Chemical Free Cleanser, Blemish Control, Cruelty Free Beauty, Sustainable Skincare, Essential Oils, Skin Brightening, Daily Cleanser, Herbal Face Wash, Eco-Friendly Skincare, All Skin Types, Radiant Glow, Pure Sandalwood, Turmeric Oil, Mild Cleansing, Gentle Face Wash, Indian Beauty Brand, Organic Ingredients, Detoxifying Cleanser, Skin Health, Pore Cleanser, Clear Skin, Refreshing Face Wash, Traditional Skincare, Bio-Degradable, Artisan Beauty, Natural Glow, Deep Pore Cleansing, Non-Toxic Beauty, Rejuvenating Cleanser, Soft Skin, Moisturizing Wash</v>
+      </c>
+      <c r="N275" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P275" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q275" t="b">
+        <v>0</v>
+      </c>
+      <c r="R275" t="b">
+        <v>0</v>
+      </c>
+      <c r="S275" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>pc32</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Organic Wild Rose Face Wash</v>
+      </c>
+      <c r="D276" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Wild_Rose_Face_Wash_100ml_Rustic_Art_c1124aeaf07a66a9_1024x.jpg?v=1768722506</v>
+      </c>
+      <c r="E276" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F276" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G276">
+        <v>230</v>
+      </c>
+      <c r="H276" t="str">
+        <v>100ml</v>
+      </c>
+      <c r="I276" t="str">
+        <v>Rustic Art Wild Rose Face Wash is a premium organic cleanser that harnesses the strength of wild roses to provide a gentle yet powerful cleaning experience. Perfect for a refreshing end to an exhausting day, this face wash is enriched with nourishing almonds and deeply hydrating Mango Butter and Glycerin, ensuring your skin remains supple and moisturized. As an organic, natural, and vegan product, it is handcrafted to maintain the highest quality standards. The unique blend of ingredients works to remove surface impurities while maintaining the skin's natural pH balance. Its texture is smooth and creamy, providing a luxurious lather that feels soothing upon application. Free from sulfates, parabens, and synthetic fragrances, it is certified for its purity and environmental friendliness. Regular usage helps in revitalizing the skin, leaving it soft, glowing, and healthy. This product is ideal for those seeking a sustainable and effective skincare solution that avoids harsh chemicals and focuses on botanical excellence.</v>
+      </c>
+      <c r="J276" t="str">
+        <v>https://www.rusticart.in/collections/organic-face-wash/products/rustic-art-wild-rose-face-wash</v>
+      </c>
+      <c r="K276" t="str">
+        <v>rustic-art-neem-basil-face-wash</v>
+      </c>
+      <c r="L276" t="str">
+        <v>100ml</v>
+      </c>
+      <c r="M276" t="str">
+        <v>Organic Face Wash, Wild Rose, Skin Care, Natural Cleanser, Vegan Face Wash, Handcrafted, Mango Butter, Almond Oil, Hydrating, Gentle Cleanser, Rustic Art, Cruelty-Free, Sulfate-Free, Paraben-Free, Herbal, Botanical, Daily Cleanser, Glowing Skin, Moisturizing, Soft Skin, Organic Ingredients, Personal Care, Indian Beauty, Eco-friendly, Sustainable, Non-Toxic, Wild Rose Extracts, Glycerin, Face Care, Healthy Skin, Clean Beauty, Chemical Free, Nourishing, Refreshing, Daily Skincare, Plant-Based, Essential Oils, Sensitive Skin, Deep Cleansing, Brightening, Natural Glow, Ayurvedic, Pure Skincare</v>
+      </c>
+      <c r="N276" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P276" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q276" t="b">
+        <v>0</v>
+      </c>
+      <c r="R276" t="b">
+        <v>0</v>
+      </c>
+      <c r="S276" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>pc33</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Juniper Berry Face Wash (100ml)</v>
+      </c>
+      <c r="D277" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/website_8_1024x.jpg?v=1766146631</v>
+      </c>
+      <c r="E277" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F277" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G277">
+        <v>230</v>
+      </c>
+      <c r="H277" t="str">
+        <v>100ml</v>
+      </c>
+      <c r="I277" t="str">
+        <v>Rustic Art Juniper Berry Face Wash is a concentrated, organic, and vegan formula designed to revitalize fatigued skin. Enriched with a potent fruit basket of natural ingredients, including Juniper Berry, Orange, Grapeseed, Lime, and Olive oils, this mild cleanser effectively removes impurities while maintaining the skin's natural moisture balance. It is specifically formulated for individuals with dry to normal skin types, offering a deep cleansing experience that leaves the face feeling hydrated and refreshed. As a water-efficient product, it requires less water to rinse off compared to conventional face washes. The texture is smooth and lathers gently, providing a luxurious sensory experience. This product is free from harsh chemicals like sulfates, parabens, and synthetic fragrances, aligning with Rustic Art's commitment to sustainable and eco-friendly personal care. Regular use helps in brightening the complexion and protecting the skin from environmental stressors. It is certified organic and cruelty-free, making it an ideal choice for conscious consumers looking for effective, nature-based hygiene. Simply apply a small amount to a wet face, massage in circular motions, and rinse for a healthy glow.</v>
+      </c>
+      <c r="J277" t="str">
+        <v>https://www.rusticart.in/collections/organic-face-wash/products/rustic-art-juniper-berry-face-wash</v>
+      </c>
+      <c r="K277" t="str">
+        <v>rustic-art-neem-basil-face-wash</v>
+      </c>
+      <c r="L277" t="str">
+        <v>100ml</v>
+      </c>
+      <c r="M277" t="str">
+        <v>Organic Face Wash, Vegan Face Wash, Juniper Berry Skincare, Natural Cleanser, Rustic Art, Dry Skin Care, Normal Skin Care, Sulfate Free, Paraben Free, Cruelty Free, Eco Friendly Beauty, Sustainable Skincare, Hydrating Face Wash, Deep Cleansing, Chemical Free, Essential Oils, Orange Extract, Grapeseed Oil, Olive Oil, Lime Oil, Brightening Cleanser, Indian Beauty Brand, Artisanal Skincare, Non Toxic, Mild Cleanser, Concentrated Face Wash, Water Saving Product, Organic Ingredients, Skin Detox, Radiant Skin, Daily Face Wash, Herbal Beauty, Plastic Free Packaging, Bio Degradable, Natural Glow, Refreshing Face Wash, Aromatherapy Skincare, Preservative Free, Made in India, Personal Care Products</v>
+      </c>
+      <c r="N277" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P277" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q277" t="b">
+        <v>0</v>
+      </c>
+      <c r="R277" t="b">
+        <v>0</v>
+      </c>
+      <c r="S277" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>pc34</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Rose Lip Moisturizer (9gm)</v>
+      </c>
+      <c r="D278" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Rose_Lip_Moisturizer_9gm_Rustic_Art_72e9c5e27885ee4d_1024x.jpg?v=1768722455</v>
+      </c>
+      <c r="E278" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F278" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G278">
+        <v>225</v>
+      </c>
+      <c r="H278" t="str">
+        <v>9gm</v>
+      </c>
+      <c r="I278" t="str">
+        <v>Rustic Art Rose Lip Moisturizer is a premium organic lip balm designed to provide deep hydration and long-lasting protection against dryness. Formulated with 100% natural ingredients, it features a nourishing blend of cold-pressed Moringa, Avocado, and Almond oils combined with rich Mango and Sal butters. These ingredients work synergistically to treat chapped lips while Vitamin E offers essential antioxidant benefits. The texture is creamy yet non-greasy, making it perfect for daily use or as an intensive overnight treatment. This vegan and biodegradable product is hand-blended and completely free from preservatives, synthetic fragrances, and mineral oils. Certified for its organic quality, it ensures that your lips remain soft, supple, and healthy throughout the year. The soothing scent of organic rose provides a luxurious sensory experience. Simply apply a small amount to your lips whenever they feel dry or as part of your morning and evening skincare routines. Enjoy the confidence of naturally beautiful, moisturized lips with this eco-friendly and effective personal care essential.</v>
+      </c>
+      <c r="J278" t="str">
+        <v>https://www.rusticart.in/collections/lip-moisturizer/products/rustic-art-rose-lip-moisturizer</v>
+      </c>
+      <c r="K278" t="str">
+        <v>rustic-art-rose-lip-moisturizer</v>
+      </c>
+      <c r="L278" t="str">
+        <v>Rose Lip Moisturizer (9gm)</v>
+      </c>
+      <c r="M278" t="str">
+        <v>Rustic Art, Rose Lip Moisturizer, Organic Lip Balm, Natural Lip Care, Vegan Lip Moisturizer, Hydrating Lip Treatment, Chapped Lips Remedy, Moringa Oil, Avocado Oil, Almond Oil, Mango Butter, Sal Butter, Vitamin E Lip Balm, Preservative Free, Biodegradable Lip Balm, Cruelty Free, Eco Friendly Skincare, Hand Blended, Cold Pressed Oils, Soft Lips, Supple Lips, Dry Lips Treatment, Lip Hydration, Chemical Free, Sustainable Beauty, Indian Skincare Brand, Pure Rose Lip Balm, Daily Lip Care, Intensive Lip Therapy, Nourishing Lip Balm, Natural Ingredients, Antioxidant Lip Care, Non Greasy Lip Balm, Smooth Lips, Glossy Lips, Floral Lip Balm, Skin Care Essentials, Personal Care, Healthy Lips</v>
+      </c>
+      <c r="N278" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P278" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q278" t="b">
+        <v>0</v>
+      </c>
+      <c r="R278" t="b">
+        <v>0</v>
+      </c>
+      <c r="S278" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>pc35</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Almond Saffron Lip Moisturizer</v>
+      </c>
+      <c r="D279" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Almond_Saffron_Lip_Moisturizer_9_gm_Rustic_Art_598c55b117ee6ddf_1024x.jpg?v=1768722452</v>
+      </c>
+      <c r="E279" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F279" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G279">
+        <v>325</v>
+      </c>
+      <c r="H279" t="str">
+        <v>9 gm</v>
+      </c>
+      <c r="I279" t="str">
+        <v>Rustic Art Almond Saffron Lip Moisturizer is a premium organic solution designed to heal and protect dry, chapped lips. Formulated with a potent blend of natural oils and butters, including cold-pressed almond oil and exotic saffron, this moisturizer provides deep, long-lasting nourishment. The saffron works effectively to lighten dark lips, restoring their natural pink hue, while almond oil ensures intense hydration. This 100% vegan and biodegradable product is free from synthetic fragrances, preservatives, and petroleum-based ingredients. Its smooth, buttery texture glides effortlessly, creating a protective barrier against environmental stressors. Ideal for daily use, it offers a subtle natural glow without feeling sticky. Certified for its organic integrity, it is a sustainable choice for conscious consumers. To use, apply a small amount to clean lips whenever they feel dry. The rich combination of antioxidants and essential fatty acids promotes cellular repair, making your lips soft, supple, and healthy.</v>
+      </c>
+      <c r="J279" t="str">
+        <v>https://www.rusticart.in/collections/lip-moisturizer/products/almond-saffron-lip-moisturizer</v>
+      </c>
+      <c r="K279" t="str">
+        <v>rustic-art-rose-lip-moisturizer</v>
+      </c>
+      <c r="L279" t="str">
+        <v>Almond Saffron Lip Moisturizer</v>
+      </c>
+      <c r="M279" t="str">
+        <v>Rustic Art, Almond Saffron Lip Moisturizer, Natural Lip Balm, Organic Lip Care, Vegan Lip Moisturizer, Dry Lips Treatment, Chapped Lips Remedy, Dark Lips Lightening, Saffron Lip Care, Almond Oil Lip Balm, Chemical Free Lip Care, Handmade Lip Balm, Sustainable Beauty, Eco Friendly Lip Balm, Ayurvedic Lip Care, Intense Hydration, Paraben Free, Sulfate Free, Petroleum Free, Cruelty Free, Indian Skin Care, Biodegradable Lip Care, Nourishing Lip Butter, Lip Repair Balm, Soft Lips, Healthy Lips, Daily Lip Care, Cold Pressed Oils, Plant Based Lip Care, Antioxidant Lip Balm, Lip Softener, Winter Lip Care, Summer Lip Care, Unisex Lip Balm, Travel Size Lip Balm, 9gm Lip Balm, Non Sticky Lip Balm, Transparent Lip Moisturizer, Healing Lip Balm, Luxury Lip Care, Premium Organic Skin Care, Indian Brand Skin Care, Natural Glow, Lip Exfoliation Support, Soothing Lip Balm</v>
+      </c>
+      <c r="N279" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P279" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q279" t="b">
+        <v>0</v>
+      </c>
+      <c r="R279" t="b">
+        <v>0</v>
+      </c>
+      <c r="S279" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>pc36</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Raspberry Mint Lip Moisturizer (9gm)</v>
+      </c>
+      <c r="D280" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Raspberry_Mint_Lip_Moisturizer_9gm_Rustic_Art_b6642f6fccf5f678_1024x.jpg?v=1768722455</v>
+      </c>
+      <c r="E280" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F280" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G280">
+        <v>225</v>
+      </c>
+      <c r="H280" t="str">
+        <v>9gm</v>
+      </c>
+      <c r="I280" t="str">
+        <v>Rustic Art Raspberry Mint Lip Moisturizer is a premium skincare essential designed to provide long-lasting hydration and protection for your lips. This cooling formula is enriched with organic raspberry extracts and mint, offering a refreshing sensation while defending against the harsh effects of pollution and sun damage through its natural SPF properties. Handcrafted and vegan, this lip balm is made from cold-pressed oils and organic butters that penetrate deeply to repair chapped skin and maintain a smooth, supple texture. It is entirely biodegradable and free from synthetic fragrances, mineral oils, and harmful chemicals, making it a sustainable choice for your daily beauty routine. The non-greasy texture ensures a comfortable wear throughout the day, whether used as a base for lipstick or on its own for a natural, healthy glow. Ideal for all skin types, it provides an effective barrier against environmental stressors while keeping your breath fresh with a subtle minty aroma. Experience the purity of natural ingredients and the benefit of artisanal craftsmanship with this concentrated lip care solution.</v>
+      </c>
+      <c r="J280" t="str">
+        <v>https://www.rusticart.in/collections/lip-moisturizer/products/rustic-art-raspberry-mint-lip-moisturizer</v>
+      </c>
+      <c r="K280" t="str">
+        <v>rustic-art-rose-lip-moisturizer</v>
+      </c>
+      <c r="L280" t="str">
+        <v>Raspberry Mint Lip Moisturizer (9gm)</v>
+      </c>
+      <c r="M280" t="str">
+        <v>Raspberry Mint Lip Balm, Organic Lip Moisturizer, Sun Protection Lip Care, Natural Lip Balm, Vegan Lip Balm, Biodegradable Lip Care, Cooling Lip Balm, Pollution Defense, Long Lasting Lip Care, Raspberry Mint, Rustic Art, SPF Protection, Lip Care for Men and Women, Non-toxic Lip Balm, Chemical Free Lip Care, Handmade Lip Balm, Sustainable Beauty, Cruelty Free, Eco Friendly, Raspberry Flavor, Minty Fresh, Lip Hydration, Dry Lips Remedy, Chapped Lips, Winter Lip Care, Daily Lip Care, Organic Ingredients, Essential Oils, Lip Butter, 9gm, Personal Care, Indian Beauty Brand, Artisanal Lip Balm, Natural Sunscreen for Lips, Paraben Free</v>
+      </c>
+      <c r="N280" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P280" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q280" t="b">
+        <v>0</v>
+      </c>
+      <c r="R280" t="b">
+        <v>0</v>
+      </c>
+      <c r="S280" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>pc37</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Mango Vanilla Lip Moisturizer</v>
+      </c>
+      <c r="D281" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/mango_lip_balm_1024x.jpg?v=1763891609</v>
+      </c>
+      <c r="E281" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F281" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G281">
+        <v>225</v>
+      </c>
+      <c r="H281" t="str">
+        <v>9gm</v>
+      </c>
+      <c r="I281" t="str">
+        <v>Rustic Art Mango Vanilla Lip Moisturizer is a premium organic lip care solution designed specifically to repair dry and chapped lips. This high-performance balm provides extreme moisturization, effectively locking in hydration to ensure your lips remain soft and supple throughout the day. Formulated with a blend of natural oils and organic mango and vanilla extracts, it works to retain lip elasticity, preventing further damage and aging. The product is entirely vegan and biodegradable, aligning with eco-conscious beauty standards. Its rich, buttery texture glides smoothly over the lips, delivering immediate relief and a pleasant, natural aroma. Ideal for daily use, this lip moisturizer is free from synthetic chemicals, parabens, and mineral oils, making it safe for all skin types. Whether facing harsh winter winds or dry summer heat, this balm offers a protective barrier and deep nourishment. Regular application enhances the natural texture of your lips, leaving them healthy and revitalized. It is a perfect addition to any skincare routine focused on natural, sustainable ingredients.</v>
+      </c>
+      <c r="J281" t="str">
+        <v>https://www.rusticart.in/collections/lip-moisturizer/products/rustic-art-mango-vanilla-lip-moisturizer</v>
+      </c>
+      <c r="K281" t="str">
+        <v>rustic-art-rose-lip-moisturizer</v>
+      </c>
+      <c r="L281" t="str">
+        <v>Mango Vanilla Lip Moisturizer</v>
+      </c>
+      <c r="M281" t="str">
+        <v>lip balm, natural lip balm, organic lip balm, mango vanilla, lip care, dry lips, chapped lips, vegan lip balm, eco-friendly, biodegradable, rustic art, skin care, lip repair, hydration, lip elasticity, essential oils, handmade, herbal, chemical free, paraben free, sulfate free, cruelty free, sustainable, intense moisturization, winter care, daily lip care, nourishing, smooth lips, soft lips, indian skincare, lip moisturizer, vanilla lip balm, mango lip balm, lip therapy, moisturizing balm</v>
+      </c>
+      <c r="N281" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P281" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q281" t="b">
+        <v>0</v>
+      </c>
+      <c r="R281" t="b">
+        <v>0</v>
+      </c>
+      <c r="S281" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>pc38</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Calendula Lip Moisturizer for Babies &amp; Kids (9gm)</v>
+      </c>
+      <c r="D282" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Calendula_Lip_Moisturizer_for_Babies_Kids_9gm_Rustic_Art_88be828371ac0142_1024x.jpg?v=1768722454</v>
+      </c>
+      <c r="E282" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F282" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G282">
+        <v>300</v>
+      </c>
+      <c r="H282" t="str">
+        <v>9gm</v>
+      </c>
+      <c r="I282" t="str">
+        <v>Rustic Art Calendula Lip Moisturizer is a gentle, 100% natural, vegan, and organic formula specifically designed for babies and kids. This organic lip balm provides long-lasting nourishment and is safe for even the most sensitive lips. Key ingredients include calendula, known for its soothing properties, and organic oils that create a protective barrier against dryness and chapping. The texture is smooth and easy to apply, perfect for young children. It is biodegradable and free from harsh chemicals, synthetic fragrances, and preservatives. Use daily or as needed to maintain soft, hydrated lips. This product is certified organic and follows sustainable practices. Benefits include deep hydration, protection from environmental stressors, and skin-soothing relief. It features a non-sticky finish that kids love. The formulation ensures that moisture is locked in throughout the day, preventing painful cracks. Certified vegan and cruelty-free, it aligns with conscious parenting choices. This 9gm pack is travel-friendly and ensures long-lasting use for your little ones' delicate skin.</v>
+      </c>
+      <c r="J282" t="str">
+        <v>https://www.rusticart.in/collections/lip-moisturizer/products/calendula-lip-moisturizer-for-babies-kids</v>
+      </c>
+      <c r="K282" t="str">
+        <v>rustic-art-rose-lip-moisturizer</v>
+      </c>
+      <c r="L282" t="str">
+        <v>Calendula Lip Moisturizer for Babies &amp; Kids (9gm)</v>
+      </c>
+      <c r="M282" t="str">
+        <v>natural lip balm, organic lip moisturizer, baby lip care, kids lip balm, calendula lip balm, vegan lip care, chemical free, non toxic, sensitive skin, rustic art, organic skincare, baby skin care, moisturizer for kids, safe for babies, handmade, sustainable, biodegradable, herbal lip balm, soothing lips, dry lip relief, hydrating lip balm, paraben free, sulfate free, cruelty free, indian brand, eco friendly, baby shower gift, daily lip care, winter lip care, protective lip balm, lip nourishment, organic ingredients, gentle formula, kids toiletries, natural oils, skin protection, safe for toddlers, allergen free, toxin free, handmade lip balm</v>
+      </c>
+      <c r="N282" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P282" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q282" t="b">
+        <v>0</v>
+      </c>
+      <c r="R282" t="b">
+        <v>0</v>
+      </c>
+      <c r="S282" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>pc39</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Ginger Lemon Lip Moisturizer (9gm)</v>
+      </c>
+      <c r="D283" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Ginger_Lemon_Lip_Moisturizer_9gm_Rustic_Art_62b7917760c001f0_1024x.jpg?v=1768722454</v>
+      </c>
+      <c r="E283" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F283" t="str">
+        <v>Skin Care</v>
+      </c>
+      <c r="G283">
+        <v>225</v>
+      </c>
+      <c r="H283" t="str">
+        <v>9gm</v>
+      </c>
+      <c r="I283" t="str">
+        <v>Rustic Art Ginger Lemon Lip Moisturizer is a premium, 100% natural, and vegan solution designed specifically for individuals seeking effective lip care without the high-gloss finish. Infused with the refreshing and potent extracts of ginger and lemon, this lip balm offers powerful anti-pigmentation properties that help restore the natural tone of your lips over time. It is meticulously formulated with organic ingredients to provide long-lasting hydration and protection against environmental stressors like pollution and harsh weather conditions. The non-glossy, matte finish makes it an ideal choice for men or anyone preferring a subtle, natural look. The smooth texture glides effortlessly, ensuring deep penetration of moisture into the delicate skin of the lips. Free from synthetic chemicals and artificial fragrances, it emphasizes the brand's commitment to sustainable and ethical personal care. Regular application ensures your lips remain soft, supple, and healthy. This 9gm travel-friendly pack is perfect for on-the-go nourishment. Whether you are dealing with dryness or looking to prevent dark spots, this lip moisturizer serves as a comprehensive treatment, leaving your lips rejuvenated and protected throughout the day.</v>
+      </c>
+      <c r="J283" t="str">
+        <v>https://www.rusticart.in/collections/lip-moisturizer/products/rustic-art-ginger-lemon-lip-moisturizer</v>
+      </c>
+      <c r="K283" t="str">
+        <v>rustic-art-rose-lip-moisturizer</v>
+      </c>
+      <c r="L283" t="str">
+        <v>Ginger Lemon Lip Moisturizer (9gm)</v>
+      </c>
+      <c r="M283" t="str">
+        <v>Ginger Lemon Lip Moisturizer, Rustic Art Lip Balm, Anti-Pigmentation Lip Care, Natural Lip Balm for Men, Vegan Lip Moisturizer, Organic Lip Balm India, Non-Glossy Lip Balm, Matte Finish Lip Care, Sustainable Beauty Products, Chemical Free Lip Care, Ginger Extract Lip Balm, Lemon Oil Lip Treatment, Handcrafted Lip Care, Cruelty Free Beauty, Eco Friendly Personal Care, Lip Care for Smoker Pigmentation, Sun Protection for Lips, Hydrating Lip Treatment, Winter Lip Care, Daily Use Lip Balm, Nourishing Lip Butter, Rustic Art Skin Care, Paraben Free Lip Balm, Sulphate Free Beauty, Ayurvedic Lip Care, Essential Oil Lip Balm, Detoxifying Lip Balm, Healing Lip Salve, Dark Lip Treatment, Moisturizing Lip Balm, Travel Size Lip Care, Grooming for Men, Natural Ingredients, Healthy Lips, Soft Lips, Supple Lips, Lip Health, Pollution Protection, Bio Degradable Packaging, Holistic Lip Care, Refreshing Ginger Lemon, Indian Skin Care Brands, Effective Lip Hydration</v>
+      </c>
+      <c r="N283" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P283" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q283" t="b">
+        <v>0</v>
+      </c>
+      <c r="R283" t="b">
+        <v>0</v>
+      </c>
+      <c r="S283" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>m1</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Pepperine Organic Deodorant Balm with Vitamin E (12g)</v>
+      </c>
+      <c r="D284" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Pepperine_Organic_Deodorant_Balm_with_Vitamin_E_12g_Rustic_Art_8d045c61332a10f0_1024x.jpg?v=1768722430</v>
+      </c>
+      <c r="E284" t="str">
+        <v>Men</v>
+      </c>
+      <c r="F284" t="str">
+        <v>Deodorants &amp; Perfumes</v>
+      </c>
+      <c r="G284">
+        <v>400</v>
+      </c>
+      <c r="H284" t="str">
+        <v>12g</v>
+      </c>
+      <c r="I284" t="str">
+        <v>Rustic Art Pepperine Organic Deodorant Balm is a premium, water-less formula designed to keep you fresh and odour-free throughout the day. This unisex vegan deodorant balm features a sophisticated blend of jasmine, pepper, and nutmeg, delivering a rich, spicy scent profile balanced with citrusy freshness. Enriched with natural Vitamin E, the balm is gentle on the skin and provides a non-greasy texture that absorbs quickly without leaving any sticky residue. Following the #LessIsMore philosophy, this highly concentrated product requires only a small amount for effective protection. It is certified organic and completely free from harsh chemicals, parabens, and artificial fragrances, making it an ideal choice for health-conscious individuals. The compact 12g tin is perfect for travel or on-the-go application. This deodorant works by neutralizing body odour naturally while nourishing the delicate underarm skin. Its organic ingredients ensure it is skin-friendly and suitable for daily use, offering a sustainable and eco-friendly alternative to traditional aerosol deodorants.</v>
+      </c>
+      <c r="J284" t="str">
+        <v>https://www.rusticart.in/collections/deodorant/products/pepperine-vegan-organic-deodorant-balm-with-vitamin-e-12g</v>
+      </c>
+      <c r="K284" t="str">
+        <v>rustic-art-deodorant-balm</v>
+      </c>
+      <c r="L284" t="str">
+        <v>Pepperine Organic Deodorant Balm with Vitamin E (12g)</v>
+      </c>
+      <c r="M284" t="str">
+        <v>Pepperine, Organic, Deodorant Balm, Vegan, Skin Friendly, Vitamin E, Rustic Art, Natural Deodorant, Waterless Deodorant, Unisex Deodorant, Spicy Fragrance, Jasmine, Pepper, Nutmeg, Citrusy Freshness, Body Odour Protection, Long Lasting, Non-Greasy, Eco-Friendly, Sustainable Beauty, Cruelty Free, Chemical Free, Paraffin Free, Paraben Free, Handmade, Essential Oils, Refreshing, Travel Size, Organic Skincare, Personal Care, Indian Brand, Sustainable Lifestyle, Zero Waste, Holistic Beauty, Natural Fragrance, Odour Control, Daily Use, Nourishing, Soothing, High Quality, Artisan</v>
+      </c>
+      <c r="N284" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P284" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q284" t="b">
+        <v>0</v>
+      </c>
+      <c r="R284" t="b">
+        <v>0</v>
+      </c>
+      <c r="S284" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>m2</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Gingerange Organic Deodorant Balm with Vitamin E (12g)</v>
+      </c>
+      <c r="D285" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Gingerange_Organic_Deodorant_Balm_with_Vitamin_E_12g_Rustic_Art_c58f780c16851133_1024x.jpg?v=1768722431</v>
+      </c>
+      <c r="E285" t="str">
+        <v>Men</v>
+      </c>
+      <c r="F285" t="str">
+        <v>Deodorants &amp; Perfumes</v>
+      </c>
+      <c r="G285">
+        <v>400</v>
+      </c>
+      <c r="H285" t="str">
+        <v>12g</v>
+      </c>
+      <c r="I285" t="str">
+        <v>Rustic Art Gingerange Organic Deodorant Balm is a meticulously crafted vegan formula designed to keep you fresh and confident throughout the day. Infused with the invigorating essence of ginger, orange, tangerine, grapefruit, and peppermint, this balm offers a unique citrusy freshness that is both warm and cooling. The inclusion of Vitamin E ensures your skin remains nourished and protected, making it a skin-friendly alternative to harsh chemical deodorants. This organic balm features a non-greasy texture that absorbs quickly into the skin, effectively neutralizing body odor without clogging pores or leaving residues. Perfect for active individuals, it provides long-lasting protection even during intense physical activity. Its compact 12g size makes it an ideal travel companion. Free from synthetic fragrances and parabens, it is certified organic and cruelty-free. To use, simply apply a small amount to clean underarms and massage gently. Enjoy the refreshing blend of essential oils that promote a cool, clean sensation while supporting your skin's natural health with premium botanical ingredients.</v>
+      </c>
+      <c r="J285" t="str">
+        <v>https://www.rusticart.in/collections/deodorant/products/gingerange-vegan-organic-deodorant-balm-with-vitamin-e-12g</v>
+      </c>
+      <c r="K285" t="str">
+        <v>rustic-art-deodorant-balm</v>
+      </c>
+      <c r="L285" t="str">
+        <v>Gingerange Organic Deodorant Balm with Vitamin E (12g)</v>
+      </c>
+      <c r="M285" t="str">
+        <v>Organic Deodorant, Vegan Deodorant, Natural Deodorant Balm, Rustic Art, Ginger Orange Deodorant, Aluminum Free, Paraben Free, Essential Oil Deodorant, Vitamin E Skin Care, Body Odour Protection, Sustainable Beauty, Cruelty Free, Chemical Free, Handmade Deodorant, Refreshing Fragrance, Non-Greasy Deodorant, Citrus Deodorant, Ginger Essential Oil, Orange Essential Oil, Peppermint Deodorant, Travel Size Deodorant, Organic Personal Care, Eco-Friendly Beauty, Skin Friendly, Unisex Deodorant, Long Lasting Freshness, Botanical Deodorant, Detox Deodorant, Indian Organic Brands, No Synthetic Fragrance</v>
+      </c>
+      <c r="N285" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P285" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q285" t="b">
+        <v>0</v>
+      </c>
+      <c r="R285" t="b">
+        <v>0</v>
+      </c>
+      <c r="S285" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>pc40</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Mint Eucalyptus Shampoo Butter (50g)| Oily to Normal Hair | Mild Dandruff Prone Scalp |</v>
+      </c>
+      <c r="D286" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Mint_Eucalyptus_Shampoo_Butter_50g_Oily_to_Normal_Hair_Mild_Dandruff_Prone_Scalp_Rustic_Art_3f33484b1f99d7ac_1024x.jpg?v=1768722462</v>
+      </c>
+      <c r="E286" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F286" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G286">
+        <v>236</v>
+      </c>
+      <c r="H286" t="str">
+        <v>50g</v>
+      </c>
+      <c r="I286" t="str">
+        <v>Rustic Art Organic Mint Eucalyptus Shampoo Butter is a refreshing hair care solution designed specifically for oily to normal hair and mild dandruff-prone scalps. Formulated with organic peppermint and lemon essential oils, it provides an immediate cooling sensation while deeply cleansing the scalp. The inclusion of eucalyptus adds powerful anti-fungal and anti-bacterial properties, ensuring a clean and healthy environment for hair growth. This highly concentrated shampoo butter requires significantly less quantity than conventional liquid shampoos, making it an eco-friendly and cost-effective choice for sustainable living. Its rich, buttery texture transforms into a luxurious lather that effectively removes impurities and excess sebum without stripping the hair of its vital natural oils. Ideal for those seeking a holistic, natural solution for scalp freshness, it is certified organic and completely free from harsh synthetic chemicals, sulfates, and parabens. To use, simply take a small pea-sized amount, rub it between your palms to activate, and massage thoroughly onto a wet scalp and hair before rinsing. Enjoy the invigorating aroma and the lasting cooling effect that revitalizes your senses while maintaining healthy, balanced, and vibrant hair.</v>
+      </c>
+      <c r="J286" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-butter/products/rustic-art-mint-eucalyptus-shampoo-butter-50-g</v>
+      </c>
+      <c r="K286" t="str">
+        <v>rustic-art-shampoo-butter</v>
+      </c>
+      <c r="L286" t="str">
+        <v>Mint Eucalyptus Shampoo Butter (50g)| Oily to Normal Hair | Mild Dandruff Prone Scalp |</v>
+      </c>
+      <c r="M286" t="str">
+        <v>Organic Shampoo, Shampoo Butter, Mint Eucalyptus, Hair Care, Dandruff Treatment, Oily Hair, Normal Hair, Rustic Art, Natural Shampoo, Eco-friendly, Scalp Care, Peppermint Oil, Lemon Oil, Eucalyptus Oil, Anti-fungal, Anti-bacterial, Cooling Shampoo, Deep Cleansing, Vegan Hair Care, Sulfate Free, Paraben Free, Cruelty Free, Indian Beauty, Sustainable, Chemical Free, Essential Oils, Refreshing, Hair Health, Scalp Refresh, Concentrated</v>
+      </c>
+      <c r="N286" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P286" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q286" t="b">
+        <v>0</v>
+      </c>
+      <c r="R286" t="b">
+        <v>0</v>
+      </c>
+      <c r="S286" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>pc41</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C287" t="str">
+        <v>Cypress Hemp Oil Shampoo Butter(50g) | Dry, Damaged Hair | Frizzy Hair</v>
+      </c>
+      <c r="D287" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Cypress_Hemp_Oil_Shampoo_Butter_50g_Dry_Damaged_Hair_Frizzy_Hair_Rustic_Art_7682a4d22fb3e585_1024x.png?v=1768722461</v>
+      </c>
+      <c r="E287" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F287" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G287">
+        <v>236</v>
+      </c>
+      <c r="H287" t="str">
+        <v>50g</v>
+      </c>
+      <c r="I287" t="str">
+        <v>Rustic Art Organic Cypress Hemp Oil Shampoo Butter is a revolutionary hydration solution specifically designed for dry, damaged, and frizzy hair. This ultra-concentrated formula is packed with nourishing Hemp Seed Oil and Cypress, which work in tandem to cleanse and hydrate the scalp while effectively closing the hair cuticle for a smoother finish. Unlike traditional liquid shampoos, this butter contains a high concentration of a natural silicone alternative, providing the slip and shine your hair craves without the buildup. It deeply moisturizes the scalp, ensuring long-lasting health from root to tip. Being a water-efficient product, it requires less water to rinse off and lasts longer than conventional shampoos. The texture is a rich, creamy butter that transforms into a luxurious lather upon contact with water. Formulated with organic ingredients, it is free from harsh sulfates and synthetic fragrances. Ideal for those seeking a sustainable and effective hair care routine, it leaves hair soft, manageable, and revitalized with every wash.</v>
+      </c>
+      <c r="J287" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-butter/products/rustic-art-cypress-hemp-oil-shampoo-butter-50-g</v>
+      </c>
+      <c r="K287" t="str">
+        <v>rustic-art-shampoo-butter</v>
+      </c>
+      <c r="L287" t="str">
+        <v>Cypress Hemp Oil Shampoo Butter(50g) | Dry, Damaged Hair | Frizzy Hair</v>
+      </c>
+      <c r="M287" t="str">
+        <v>Cypress Hemp Oil Shampoo, Shampoo Butter, Rustic Art Hair Care, Dry Hair Treatment, Damaged Hair Repair, Frizzy Hair Solution, Organic Shampoo, Natural Hair Care, Hemp Seed Oil for Hair, Cypress Essential Oil, Sulfate Free Shampoo, Water Efficient Beauty, Concentrated Shampoo, Eco Friendly Hair Care, Sustainable Beauty, Scalp Moisturizer, Hair Cuticle Repair, Silicone Alternative, Vegan Hair Care, Cruelty Free Beauty, Herbal Shampoo, Ayurvedic Hair Care, Intense Hydration, Hair Softening, Manageable Hair, Indian Beauty Brand, Chemical Free Shampoo, Nutrient Rich Shampoo, Glossy Hair, Healthy Scalp</v>
+      </c>
+      <c r="N287" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P287" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q287" t="b">
+        <v>0</v>
+      </c>
+      <c r="R287" t="b">
+        <v>0</v>
+      </c>
+      <c r="S287" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>pc42</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C288" t="str">
+        <v>Cinnamon Rosemary Shampoo Butter 50gm</v>
+      </c>
+      <c r="D288" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Cinnamon_Rosemary_Shampoo_Butter_50gm_Itchy_Scalp_All_Hair_Types_Rustic_Art_6d47daa8de584720_1024x.png?v=1768722461</v>
+      </c>
+      <c r="E288" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F288" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G288">
+        <v>236</v>
+      </c>
+      <c r="H288" t="str">
+        <v>50g</v>
+      </c>
+      <c r="I288" t="str">
+        <v>Rustic Art Organic Cinnamon Rosemary Shampoo Butter is a concentrated, sulfate-free hair cleanser designed to relax and comfort your mind, hair, and soul. Formulated with a potent arsenal of natural ingredients, it features an aromatic blend of cinnamon, rosemary, juniper, lavender, and geranium essential oils that work in synergy to nourish both the scalp and hair follicles. Infused with cold-pressed oils like Hemp Seed, this shampoo butter effectively tackles common hair concerns such as dry scales, mild dandruff, and frizz, providing deep hydration without stripping away natural oils. The unique buttery texture creates a rich lather that gently removes impurities while promoting a healthy scalp environment. Suitable for all hair types, particularly those prone to itchiness, it leaves hair feeling soft, manageable, and revitalized. This eco-friendly product is free from harsh chemicals, synthetic fragrances, and preservatives, ensuring a pure and sustainable grooming experience. To use, take a small amount, lather with water, massage into the scalp, and rinse thoroughly to enjoy the invigorating herbal scent and restorative benefits.</v>
+      </c>
+      <c r="J288" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-butter/products/rustic-art-cinnamon-rosemary-shampoo-butter-50-g</v>
+      </c>
+      <c r="K288" t="str">
+        <v>rustic-art-shampoo-butter</v>
+      </c>
+      <c r="L288" t="str">
+        <v>Cinnamon Rosemary Shampoo Butter 50gm</v>
+      </c>
+      <c r="M288" t="str">
+        <v>shampoo butter, cinnamon rosemary, itchy scalp treatment, all hair types, rustic art, organic hair care, sulfate free, hemp seed oil, dandruff control, frizz free hair, natural shampoo, essential oils, rosemary for hair, cinnamon for scalp, vegan beauty, eco friendly shampoo, sustainable hair care, waterless shampoo, hair nourishment, scalp health, herbal hair cleanser, chemical free shampoo, aromatherapy hair care, lavender oil, geranium oil, juniper oil, cold pressed oils, hair repair, manageable hair, indian beauty brand</v>
+      </c>
+      <c r="N288" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P288" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q288" t="b">
+        <v>0</v>
+      </c>
+      <c r="R288" t="b">
+        <v>0</v>
+      </c>
+      <c r="S288" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>pc43</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C289" t="str">
+        <v>Organic Yarrow Moringa Shampoo Butter for Babies &amp; Kids</v>
+      </c>
+      <c r="D289" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/yarrow_moringa_50_gm_1024x.jpg?v=1772434083</v>
+      </c>
+      <c r="E289" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F289" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G289">
+        <v>236</v>
+      </c>
+      <c r="H289" t="str">
+        <v>50 g</v>
+      </c>
+      <c r="I289" t="str">
+        <v>Rustic Art Organic Yarrow Moringa Shampoo Butter for Babies and Kids offers a luxurious and innovative hair wash experience tailored for delicate scalps. This scientifically advanced formula is rich in essential oils, vegetable oils, and natural glycerin, providing a deep yet gentle cleanse. Moringa and Yarrow work synergistically to nourish the hair follicles while ensuring the scalp remains hydrated and moisturized, preventing dryness common in traditional shampoos. The unique butter texture transforms the routine into a spa-like experience, making hair soft, manageable, and healthy. It is free from harsh chemicals, sulfates, and parabens, ensuring safety for infants and toddlers. Regular use helps maintain natural oils, promoting a healthy environment for hair growth. This product is vegan, cruelty-free, and packaged sustainably, aligning with eco-conscious parenting. Simply take a small amount, lather onto a wet scalp, and rinse thoroughly. Perfect for daily or occasional use, it provides a soothing effect on the scalp, leaving a faint, pleasant natural aroma.</v>
+      </c>
+      <c r="J289" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-butter/products/rustic-art-yarrow-moringa-shampoo-butter-for-babies-kids-50-g</v>
+      </c>
+      <c r="K289" t="str">
+        <v>rustic-art-shampoo-butter</v>
+      </c>
+      <c r="L289" t="str">
+        <v>Organic Yarrow Moringa Shampoo Butter for Babies &amp; Kids</v>
+      </c>
+      <c r="M289" t="str">
+        <v>Organic Baby Shampoo, Moringa Shampoo, Yarrow Hair Care, Shampoo Butter, Kids Hair Wash, Rustic Art, Natural Hair Care, Sulfate Free Shampoo, Paraben Free, Vegan Baby Care, Sustainable Beauty, Scalp Hydration, Gentle Cleanser, Essential Oils, Vegetable Oils, Glycerin Shampoo, Baby Grooming, Eco-Friendly, Cruelty Free, Chemical Free, Infused Hair Care, Moringa Benefits, Yarrow Benefits, Moisturizing Shampoo, Baby Essentials, Toddler Hair Care, Non-Toxic, Pure Ingredients, Ayurvedic Hair Care, Indian Skincare Brand, Organic Ingredients, Safe for Kids, Healthy Scalp, Hair Softness, Manageable Hair, Baby Bath Time, Natural Grooming, Herbal Shampoo, Cold Pressed Oils, Artisan Hair Care</v>
+      </c>
+      <c r="N289" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P289" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q289" t="b">
+        <v>0</v>
+      </c>
+      <c r="R289" t="b">
+        <v>0</v>
+      </c>
+      <c r="S289" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>pc44</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Amla Shikakai Shampoo Bar | All Hair Types (75g)</v>
+      </c>
+      <c r="D290" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Amla_Shikakai_Shampoo_Bar_All_Hair_Types_Rustic_Art_21497e2fa94c8ab5_1024x.png?v=1768722465</v>
+      </c>
+      <c r="E290" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F290" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G290">
+        <v>338</v>
+      </c>
+      <c r="H290" t="str">
+        <v>75g</v>
+      </c>
+      <c r="I290" t="str">
+        <v>Rustic Art Amla Shikakai Organic Shampoo Bar is a sustainable and vegan hair care solution meticulously crafted to provide everyday nourishment for all hair types. This organic shampoo bar is enriched with powerful natural ingredients including Amla and Shikakai, which are traditionally known to strengthen hair roots and promote healthy growth. Infused with Methi (Fenugreek) and Ginger extracts, it effectively controls hair fall while adding a natural shine and bounce. The addition of creamy Mango Butter and Aloe Vera ensures that the hair remains hydrated and soft, preventing dryness. Loaded with Vitamin E, it protects the scalp and hair from environmental damage. This eco-friendly bar is completely plastic-free and long-lasting, making it an ideal choice for environmentally conscious consumers. Its compact solid texture creates a rich lather that cleanses without stripping natural oils. Certified vegan and cruelty-free, it is suitable for both teenagers and adults looking for a chemical-free cleansing experience. Simply rub the bar on wet hair to experience the revitalizing benefits of traditional Indian herbs in a modern, convenient format.</v>
+      </c>
+      <c r="J290" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-bar/products/rustic-art-amla-shikakai-organic-shampoo-bar</v>
+      </c>
+      <c r="K290" t="str">
+        <v>rustic-art-shampoo-butter1</v>
+      </c>
+      <c r="L290" t="str">
+        <v>Amla Shikakai Shampoo Bar | All Hair Types (75g)</v>
+      </c>
+      <c r="M290" t="str">
+        <v>Amla Shampoo Bar, Shikakai Shampoo, Organic Hair Care, Vegan Shampoo, Cruelty Free Beauty, Plastic Free Shampoo, Hair Fall Control, Shiny Hair, Natural Ingredients, Methi for Hair, Ginger Hair Care, Mango Butter, Aloe Vera Shampoo, Vitamin E Hair, Eco Friendly Shampoo, Solid Shampoo Bar, Sustainable Beauty, Rustic Art, Herbal Shampoo, Ayurvedic Hair Care, All Hair Types, Chemical Free Shampoo, Zero Waste Beauty, Indian Hair Care, Handmade Shampoo, Scalp Health, Hair Strengthening, Non Toxic Hair Care, Natural Shine, Traditional Herbs</v>
+      </c>
+      <c r="N290" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P290" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q290" t="b">
+        <v>0</v>
+      </c>
+      <c r="R290" t="b">
+        <v>0</v>
+      </c>
+      <c r="S290" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>pc45</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C291" t="str">
+        <v>Amla Methi Hair Conditioning Bar</v>
+      </c>
+      <c r="D291" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Amla_Methi_Hair_Conditioning_Bar_Rustic_Art_aa0c73267eb815cd_1024x.png?v=1768722429</v>
+      </c>
+      <c r="E291" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F291" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G291">
+        <v>429</v>
+      </c>
+      <c r="H291" t="str">
+        <v>75g</v>
+      </c>
+      <c r="I291" t="str">
+        <v>Rustic Art Amla Methi Hair Conditioning Bar is a 100% natural and silicone-free solid conditioner designed to transform frizzy, dry, and damaged hair into smooth, manageable tresses. Formulated with potent traditional ingredients like Indian Gooseberry (Amla) and Fenugreek (Methi), this eco-friendly bar provides deep conditioning without the use of harsh chemicals or plastic packaging. Amla is rich in Vitamin C, which helps in strengthening hair follicles and adding a natural shine, while Methi acts as a powerful emollient to detangle and soften the hair. This concentrated formula is highly efficient, lasting for over 80 washes, making it a sustainable alternative to multiple plastic bottles of liquid conditioner. The texture is smooth and easy to apply, gliding through wet hair to deposit essential nutrients. Certified natural and vegan, this bar is perfect for those seeking a zero-waste lifestyle without compromising on hair health. It is free from sulfates, parabens, and synthetic fragrances, ensuring a pure and gentle experience for all hair types.</v>
+      </c>
+      <c r="J291" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-bar/products/amla-methi-hair-conditioning-bar</v>
+      </c>
+      <c r="K291" t="str">
+        <v>rustic-art-shampoo-butter1</v>
+      </c>
+      <c r="L291" t="str">
+        <v>Amla Methi Hair Conditioning Bar</v>
+      </c>
+      <c r="M291" t="str">
+        <v>Hair Care, Shampoo Bar, Conditioner Bar, Rustic Art, Natural Conditioner, Silicone Free, Amla, Methi, Fenugreek, Indian Gooseberry, Frizzy Hair, Dry Hair, Damaged Hair, Sustainable Beauty, Zero Waste, Eco Friendly, Vegan, Cruelty Free, Herbal Hair Care, Plastic Free, Solid Conditioner, Hair Detangler, Vitamin C, Hair Strengthening, Ayurvedic, Indian Beauty, Sustainable Living, Natural Ingredients, Chemical Free, Sulfate Free, Paraben Free, Hair Health, Smooth Hair, Shiny Hair, Manageable Hair, Long Lasting, Travel Friendly, Artisan Made, Handmade, Small Batch, Non-Toxic, Clean Beauty</v>
+      </c>
+      <c r="N291" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P291" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q291" t="b">
+        <v>0</v>
+      </c>
+      <c r="R291" t="b">
+        <v>0</v>
+      </c>
+      <c r="S291" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>pc46</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Rose Sandal Shampoo Bar | Dry Damaged Hair, Frizzy Hair (75g)</v>
+      </c>
+      <c r="D292" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/rose_sandal_shampoo_bar_1024x.png?v=1758112689</v>
+      </c>
+      <c r="E292" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F292" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G292">
+        <v>445</v>
+      </c>
+      <c r="H292" t="str">
+        <v>75g</v>
+      </c>
+      <c r="I292" t="str">
+        <v>Rustic Art Rose Sandal Hair Cleansing Bar is a flagship eco-friendly solution designed specifically for dry, damaged, and frizzy hair. This luxurious solid shampoo bar simplifies your hair care routine while delivering professional results. Formulated with a potent blend of organic ingredients, it features Rose extract to efficiently remove sebum build-up and stabilize the hair's natural pH balance. The addition of Sandalwood helps strengthen and activate hair follicles, promoting better hair health and growth. This cold-processed bar offers a creamy, rich lather that deeply cleanses without stripping away essential moisture. It is a completely biodegradable, vegan, and sulfate-free alternative to traditional bottled shampoos, making it perfect for sustainable living and travel. The texture is solid yet smooth, ensuring easy application directly to wet hair. Regular use leaves hair feeling soft, hydrated, and manageable. Certified organic and cruelty-free, this bar provides a restorative experience for the scalp and strands alike, ensuring a clean, healthy shine with every wash.</v>
+      </c>
+      <c r="J292" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-bar/products/rustic-art-rose-sandal-hair-cleansing-bar-shampoo-bar</v>
+      </c>
+      <c r="K292" t="str">
+        <v>rustic-art-shampoo-butter1</v>
+      </c>
+      <c r="L292" t="str">
+        <v>Rose Sandal Shampoo Bar | Dry Damaged Hair, Frizzy Hair (75g)</v>
+      </c>
+      <c r="M292" t="str">
+        <v>Shampoo Bar, Organic Shampoo, Rose Shampoo, Sandalwood Hair Care, Dry Hair Treatment, Damaged Hair Care, Frizzy Hair Solution, Hair Cleansing Bar, Rustic Art, Vegan Shampoo, Zero Waste Hair Care, Sulfate Free, Paraben Free, Natural Hair Care, Eco Friendly Beauty, Sustainable Living, Solid Shampoo, Hair Growth, Scalp Health, PH Balanced, Essential Oils, Cold Processed Soap, Ayurvedic Hair Care, Indian Beauty Brand, Plastic Free, Travel Friendly, Cruelty Free, Bio Degradable, Moisture Restoration, Healthy Hair</v>
+      </c>
+      <c r="N292" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P292" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q292" t="b">
+        <v>0</v>
+      </c>
+      <c r="R292" t="b">
+        <v>0</v>
+      </c>
+      <c r="S292" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>pc47</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C293" t="str">
+        <v>Hibiscus Hemp Oil Shampoo Bar | Combination Hair, Itchy Scalp (75g)</v>
+      </c>
+      <c r="D293" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Hibiscus_Hemp_Oil_Shampoo_Bar_Combination_Hair_Itchy_Scalp_Rustic_Art_fa5e9c2f67e85b62_1024x.png?v=1771740569</v>
+      </c>
+      <c r="E293" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F293" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G293">
+        <v>400</v>
+      </c>
+      <c r="H293" t="str">
+        <v>75g</v>
+      </c>
+      <c r="I293" t="str">
+        <v>The Rustic Art Hibiscus Hemp Oil Shampoo Bar is a premium hair cleansing solution specifically formulated for combination hair and those suffering from an itchy scalp. This organic shampoo bar features a powerful blend of hibiscus and hemp oil, working together to control dry dandruff while making hair visibly healthier. It effectively addresses the needs of dry and damaged hair by providing deep hydration without weighing it down. The bar's natural conditioning properties ensure a smooth texture and manageable finish after every wash. Crafted with organic ingredients, it offers an eco-friendly alternative to liquid shampoos, reducing plastic waste. To use, simply rub the bar directly onto wet hair to create a rich lather, massage into the scalp, and rinse thoroughly. This cleansing bar is free from harsh chemicals, ensuring a gentle yet effective cleaning process that maintains the scalp's natural balance. Its compact size makes it perfect for travel while delivering long-lasting results for shiny, strong, and revitalized hair.</v>
+      </c>
+      <c r="J293" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-bar/products/rustic-art-hibiscus-hemp-oil-hair-cleansing-bar-shampoo-bar</v>
+      </c>
+      <c r="K293" t="str">
+        <v>rustic-art-shampoo-butter1</v>
+      </c>
+      <c r="L293" t="str">
+        <v>Hibiscus Hemp Oil Shampoo Bar | Combination Hair, Itchy Scalp (75g)</v>
+      </c>
+      <c r="M293" t="str">
+        <v>Organic shampoo bar, Hibiscus shampoo, Hemp oil hair care, Dandruff control, Combination hair care, Itchy scalp treatment, Natural hair cleanser, Eco-friendly shampoo, Plastic-free hair care, Rustic Art shampoo, Sustainable beauty, Vegan shampoo bar, Chemical-free hair care, Hibiscus for hair, Hemp oil benefits, Healthy hair, Hair strengthening, Scalp health, Dry dandruff remedy, Damaged hair repair, Solid shampoo, Travel-friendly hair care, Ayurvedic hair care, Indian beauty brand, Organic hair products, Sulfate-free shampoo, Paraben-free, Cruelty-free hair care, Natural ingredients, Hibiscus hemp oil bar, Hair growth support, Scalp soothing, Deep cleansing, Hair hydration, Non-toxic beauty, Zero waste, Handcrafted shampoo, Essential oil hair care, Refreshing scalp, Shiny hair, Smooth hair, Natural hair wash, Traditional hair care, Artisanal shampoo</v>
+      </c>
+      <c r="N293" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P293" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q293" t="b">
+        <v>0</v>
+      </c>
+      <c r="R293" t="b">
+        <v>0</v>
+      </c>
+      <c r="S293" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>pc48</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C294" t="str">
+        <v>Neem Tulsi Shampoo Bar | Oily to Normal Hair, Dandruff Prone Scalp (75g)</v>
+      </c>
+      <c r="D294" t="str">
+        <v>https://www.rusticart.in/cdn/shop/files/Neem_Tulsi_Shampoo_Bar_Oily_to_Normal_Hair_Dandruff_Prone_Scalp_Rustic_Art_e75c9e075aea7c4e_1024x.png?v=1768722469</v>
+      </c>
+      <c r="E294" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F294" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G294">
+        <v>338</v>
+      </c>
+      <c r="H294" t="str">
+        <v>75g</v>
+      </c>
+      <c r="I294" t="str">
+        <v>The Rustic Art Neem Tulsi Hair Cleansing Bar is an exceptional organic shampoo solution designed specifically for individuals with oily to normal hair and dandruff-prone scalps. Formulated with potent natural ingredients like Neem, Tulsi, and Charcoal, this anti-dandruff shampoo bar effectively cleanses the scalp by removing excess oil and impurities while controlling persistent itching and reducing hair fall. The inclusion of charcoal ensures deep detoxification of the hair follicles. This eco-friendly, long-lasting organic formula not only addresses scalp issues but also leaves the hair feeling remarkably soft and shiny without the use of harsh chemicals or plastic packaging. To use, simply wet your hair and the bar, lather between hands or apply directly to the scalp, massage thoroughly, and rinse well. The firm texture of the bar provides a rich, creamy lather that efficiently covers the hair. It is a sustainable choice for those seeking a natural hair care routine that balances oil production and maintains a healthy, flake-free scalp. This product is a testament to traditional herbal wisdom combined with modern sustainable practices.</v>
+      </c>
+      <c r="J294" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-bar/products/rustic-art-neem-tulsi-hair-cleansing-bar-shampoo-bar</v>
+      </c>
+      <c r="K294" t="str">
+        <v>rustic-art-shampoo-butter1</v>
+      </c>
+      <c r="L294" t="str">
+        <v>Neem Tulsi Shampoo Bar | Oily to Normal Hair, Dandruff Prone Scalp (75g)</v>
+      </c>
+      <c r="M294" t="str">
+        <v>Neem Tulsi Shampoo Bar, Anti Dandruff Shampoo, Organic Hair Care, Rustic Art, Shampoo Bar for Oily Scalp, Charcoal Shampoo Bar, Natural Hair Cleanser, Hair Fall Control, Itchy Scalp Relief, Sustainable Beauty, Plastic Free Shampoo, Vegan Hair Care, Cruelty Free, Handmade Shampoo Bar, Ayurvedic Hair Care, Normal Hair Shampoo, Deep Cleansing Shampoo, Detox Shampoo Bar, Herbal Hair Care, Solid Shampoo, Eco Friendly Grooming, Indian Beauty Brand, Chemical Free Shampoo, No Sulfates, No Parabens, Shiny Hair, Soft Hair, Scalp Health, Traditional Hair Care, Neem Benefits, Tulsi for Hair, Charcoal Benefits, Zero Waste Hair Care, Travel Friendly Shampoo, Long Lasting Shampoo, Hair Detox, Natural Ingredients, Bio Degradable, Artisan Shampoo, Non Toxic Hair Care, Scalp Treatment, Dandruff Solutions, Oily Hair Remedies, Healthy Hair Routine, Green Beauty India, Minimalist Skin Care, Holistic Hair Care</v>
+      </c>
+      <c r="N294" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P294" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q294" t="b">
+        <v>0</v>
+      </c>
+      <c r="R294" t="b">
+        <v>0</v>
+      </c>
+      <c r="S294" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>pc49</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C295" t="str">
+        <v>Papaya Lime Shampoo Bar | All Hair Types (75g)</v>
+      </c>
+      <c r="D295" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Papaya_Lime_Shampoo_Bar_All_Hair_Types_Rustic_Art_1ac9a048fb79085c_1024x.png?v=1768723581</v>
+      </c>
+      <c r="E295" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F295" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G295">
+        <v>338</v>
+      </c>
+      <c r="H295" t="str">
+        <v>75g</v>
+      </c>
+      <c r="I295" t="str">
+        <v>The Rustic Art Organic Papaya Lime Hair Cleansing Bar is a high-performance, eco-friendly alternative to liquid shampoos, specifically formulated to provide intense frizz control and superior softness for all hair types. This artisanal bar is made using a traditional cold-processed method that preserves the integrity of its potent organic ingredients, including saponified oils of coconut, mahua, and castor. Enriched with natural papaya extract and refreshing lime essential oil, it works as a natural exfoliant for the scalp, removing product buildup while balancing natural oils without the use of harsh sulphates or parabens. This vegan and cruelty-free cleansing bar creates a dense, creamy lather that deeply nourishes the hair shaft, improving texture and promoting a healthy shine. The travel-friendly design makes it a convenient choice for on-the-go lifestyles while significantly reducing plastic pollution. For optimal results, wet the hair thoroughly and rub the bar between your palms or directly onto the scalp to create a rich lather; massage gently and rinse well. This product is biodegradable and safe for the environment, ensuring a sustainable grooming routine that delivers professional results without synthetic chemicals.</v>
+      </c>
+      <c r="J295" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-bar/products/rustic-art-papaya-lime-hair-cleansing-bar-shampoo-bar</v>
+      </c>
+      <c r="K295" t="str">
+        <v>rustic-art-shampoo-butter1</v>
+      </c>
+      <c r="L295" t="str">
+        <v>Papaya Lime Shampoo Bar | All Hair Types (75g)</v>
+      </c>
+      <c r="M295" t="str">
+        <v>Shampoo Bar, Hair Care, Organic Shampoo, Sulphate Free, Paraben Free, Eco-Friendly, Sustainable Beauty, Zero Waste, Papaya Hair Care, Lime Essential Oil, Frizz Control, Soft Hair, All Hair Types, Natural Hair Cleanser, Vegan Beauty, Cruelty Free, Cold Processed Soap, Indian Brand, Rustic Art, Hair Strengthening, Scalp Health, Natural Ingredients, Chemical Free, Travel Friendly, Plastic Free Packaging, Hair Cleansing Bar, Deep Conditioning, Shine Boost, Detox Shampoo, Artisan Shampoo, Non Toxic Hair Care, Sustainable Haircare, Herbal Shampoo Bar</v>
+      </c>
+      <c r="N295" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P295" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q295" t="b">
+        <v>0</v>
+      </c>
+      <c r="R295" t="b">
+        <v>0</v>
+      </c>
+      <c r="S295" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>b1</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C296" t="str">
+        <v>Neem Leaf Shampoo Bar for Babies &amp; Kids (75g)</v>
+      </c>
+      <c r="D296" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/neem_leaf_shmapoo_bar_1024x.png?v=1771740500</v>
+      </c>
+      <c r="E296" t="str">
+        <v>Baby Care</v>
+      </c>
+      <c r="F296" t="str">
+        <v>Baby Personal Care</v>
+      </c>
+      <c r="G296">
+        <v>400</v>
+      </c>
+      <c r="H296" t="str">
+        <v>75g</v>
+      </c>
+      <c r="I296" t="str">
+        <v>Rustic Art Neem Leaf Hair Cleansing Bar for Babies &amp; Kids is a gentle, soap-free shampoo specifically designed for the sensitive scalps of toddlers and children. Formulated with organic neem leaf extracts, this hair cleansing bar provides natural antibacterial protection while effectively controlling dandruff and preventing scalp irritation. The bar is enriched with nourishing oils that make hair exceptionally soft, manageable, and add a healthy natural shine without stripping away essential moisture. Unlike liquid shampoos, this solid bar is concentrated and easy to use, ensuring a tear-free experience for little ones. It is strictly free from sulphates, parabens, and harsh chemicals, making it a safe choice for daily use. This vegan and eco-friendly product is travel-friendly and long-lasting. The texture is firm yet lathers into a creamy, mild foam with a refreshing natural scent. Ideal for maintaining healthy hair growth and a clean scalp, this shampoo bar is certified organic and handcrafted to provide the ultimate hair nutrition for your child’s developing locks.</v>
+      </c>
+      <c r="J296" t="str">
+        <v>https://www.rusticart.in/collections/shampoo-bar/products/rustic-art-neem-leaf-hair-cleansing-bar-for-babies-kids-shampoo-bar</v>
+      </c>
+      <c r="K296" t="str">
+        <v>-</v>
+      </c>
+      <c r="L296" t="str">
+        <v>Neem Leaf Shampoo Bar for Babies &amp; Kids (75g)</v>
+      </c>
+      <c r="M296" t="str">
+        <v>organic shampoo bar, neem shampoo, baby hair care, kids shampoo, sulfate free, paraben free, rustic art, hair cleansing bar, natural baby products, eco friendly hair care, vegan shampoo, dandruff control, shiny hair, soft hair, soap free shampoo, toddler hair care, neem leaf benefits, herbal shampoo, sustainable beauty, zero waste, handcrafted soap, organic hair care, gentle cleanser, hair nutrition, baby bath essentials, kids grooming, chemical free, non toxic, made in india, ayurvedic hair care, sensitive scalp, hair growth, organic certification, travel friendly shampoo, solid shampoo bar, neem leaf extract</v>
+      </c>
+      <c r="N296" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P296" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q296" t="b">
+        <v>0</v>
+      </c>
+      <c r="R296" t="b">
+        <v>0</v>
+      </c>
+      <c r="S296" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>pc50</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C297" t="str">
+        <v>Coconut Coriander Hair Cream with Vitamin C &amp; E (50ml)</v>
+      </c>
+      <c r="D297" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Coconut_Coriander_Hair_Cream_with_Vitamin_C_E_50ml_Rustic_Art_d772b780864f83eb_1024x.jpg?v=1768722478</v>
+      </c>
+      <c r="E297" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F297" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G297">
+        <v>250</v>
+      </c>
+      <c r="H297" t="str">
+        <v>50ml</v>
+      </c>
+      <c r="I297" t="str">
+        <v>Rustic Art Coconut Coriander Hair Cream with Vitamin C &amp; E is a meticulously crafted natural formula designed for intensive hair nourishment and protection. Enriched with the goodness of organic coconut oil and coriander, it provides a deep hydration boost to both the scalp and hair strands. This hair cream is fortified with Vitamin C and E, which act as powerful antioxidants to shield your hair from the damaging effects of heat styling, UV rays, and urban pollution. The texture is lightweight and non-greasy, making it perfect for daily use as a leave-in conditioner or post-wash styling cream. It effectively tames frizz, improves manageability, and adds a healthy, natural shine to the hair. Free from sulfates, parabens, and synthetic fragrances, this product is certified organic and vegan, ensuring a safe and eco-friendly grooming experience. Simply apply a small amount to damp or dry hair to lock in moisture and strengthen hair fibers. Experience the benefits of traditional botanical wisdom combined with modern nutritional science for vibrant, resilient hair.</v>
+      </c>
+      <c r="J297" t="str">
+        <v>https://www.rusticart.in/collections/hair-care-conditioner/products/rustic-art-coconut-coriander-hair-cream-vitamin-c</v>
+      </c>
+      <c r="K297" t="str">
+        <v>1</v>
+      </c>
+      <c r="L297" t="str">
+        <v>50ml</v>
+      </c>
+      <c r="M297" t="str">
+        <v>Hair Care, Hair Cream, Natural Hair Care, Organic Hair Cream, Coconut Hair Cream, Coriander Hair Cream, Vitamin C, Vitamin E, UV Protection, Heat Protection, Anti-Pollution, Deep Hydration, Healthy Hair, Manageable Hair, Frizz Control, Shiny Hair, Rustic Art, Vegan Hair Care, Cruelty Free, Paraben Free, Sulfate Free, Natural Ingredients, Hair Nourishment, Daily Hair Care, Post Wash Treatment, Scalp Health, Moisturizing Hair Cream, Indian Beauty Brand, Eco Friendly, Sustainable Beauty, Chemical Free, Leave-in Conditioner, Hair Protection, Scalp Care, Non Greasy, Botanical Hair Care, Vitamin Enriched, Styling Cream, Hair Repair, Soft Hair</v>
+      </c>
+      <c r="N297" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P297" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q297" t="b">
+        <v>0</v>
+      </c>
+      <c r="R297" t="b">
+        <v>0</v>
+      </c>
+      <c r="S297" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>pc51</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C298" t="str">
+        <v>Organic Orange Almond Hair Conditioner</v>
+      </c>
+      <c r="D298" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Orange_Almond_Hair_Conditioner_Rustic_Art_b021b49e77c7260f_1024x.jpg?v=1768722440</v>
+      </c>
+      <c r="E298" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F298" t="str">
+        <v>Hair Care</v>
+      </c>
+      <c r="G298">
+        <v>475</v>
+      </c>
+      <c r="H298" t="str">
+        <v>200 g</v>
+      </c>
+      <c r="I298" t="str">
+        <v>Rustic Art Organic Orange Almond Hair Conditioner is a uniquely formulated hair care essential designed to transform your post-wash routine. Enriched with the goodness of Vitamin F, Glycerin, and Coconut Milk, this conditioner provides a natural gloss to the length of your hair while ensuring it remains deeply conditioned and manageable. No more struggling with entangled hair; this natural blend works effectively to smoothen cuticles and restore vitality. The inclusion of Orange and Almond oils provides a refreshing citrus scent and deep nourishment to every strand. The texture is lightweight yet creamy, allowing for easy application and absorption without weighing hair down. This product is ideal for those seeking a sustainable and chemical-free way to maintain hair health. It is free from harsh surfactants and synthetic fragrances, making it suitable for all hair types. Use after shampooing to achieve soft, shiny, and frizz-free hair naturally. This conditioner is an excellent choice for conscious consumers looking for organic and effective hair care solutions, certified for purity and environmental safety.</v>
+      </c>
+      <c r="J298" t="str">
+        <v>https://www.rusticart.in/collections/hair-care-conditioner/products/organic-orange-almond-hair-conditioner</v>
+      </c>
+      <c r="K298" t="str">
+        <v>1</v>
+      </c>
+      <c r="L298" t="str">
+        <v>200 g</v>
+      </c>
+      <c r="M298" t="str">
+        <v>organic hair conditioner, orange almond conditioner, rustic art hair care, natural hair conditioner, vegan hair care, sulfate free conditioner, paraben free, vitamin f for hair, coconut milk conditioner, hair detangler, glossy hair, hair nourishment, cruelty free, sustainable beauty, plastic free hair care, eco friendly conditioner, herbal hair care, ayurvedic hair care, hair moisturizing, deep conditioning, frizz control, soft hair, shiny hair, indian beauty brand, organic ingredients, almond oil for hair, orange oil for hair, chemical free hair care, hair health, salon finish at home, eco conscious products, natural shine, healthy hair routine, clean beauty, ethical consumer, hair softening, moisture locking, plant based hair care, toxin free, rustic art products</v>
+      </c>
+      <c r="N298" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P298" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q298" t="b">
+        <v>0</v>
+      </c>
+      <c r="R298" t="b">
+        <v>0</v>
+      </c>
+      <c r="S298" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>m3</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C299" t="str">
+        <v>Coconut Coriander Hair Cream with Vitamin C &amp; E (50ml)</v>
+      </c>
+      <c r="D299" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Coconut_Coriander_Hair_Cream_with_Vitamin_C_E_50ml_Rustic_Art_d772b780864f83eb_1024x.jpg?v=1768722478</v>
+      </c>
+      <c r="E299" t="str">
+        <v>Men</v>
+      </c>
+      <c r="F299" t="str">
+        <v>Kurtas</v>
+      </c>
+      <c r="G299">
+        <v>250</v>
+      </c>
+      <c r="H299" t="str">
+        <v>50ml</v>
+      </c>
+      <c r="I299" t="str">
+        <v>Rustic Art Coconut Coriander Hair Cream with Vitamin C &amp; E is a meticulously crafted natural formula designed for intensive hair nourishment and protection. Enriched with the goodness of organic coconut oil and coriander, it provides a deep hydration boost to both the scalp and hair strands. This hair cream is fortified with Vitamin C and E, which act as powerful antioxidants to shield your hair from the damaging effects of heat styling, UV rays, and urban pollution. The texture is lightweight and non-greasy, making it perfect for daily use as a leave-in conditioner or post-wash styling cream. It effectively tames frizz, improves manageability, and adds a healthy, natural shine to the hair. Free from sulfates, parabens, and synthetic fragrances, this product is certified organic and vegan, ensuring a safe and eco-friendly grooming experience. Simply apply a small amount to damp or dry hair to lock in moisture and strengthen hair fibers. Experience the benefits of traditional botanical wisdom combined with modern nutritional science for vibrant, resilient hair.</v>
+      </c>
+      <c r="J299" t="str">
+        <v>https://www.rusticart.in/collections/hair-care-conditioner/products/rustic-art-coconut-coriander-hair-cream-vitamin-c</v>
+      </c>
+      <c r="K299" t="str">
+        <v>1</v>
+      </c>
+      <c r="L299" t="str">
+        <v>50ml</v>
+      </c>
+      <c r="M299" t="str">
+        <v>Hair Care, Hair Cream, Natural Hair Care, Organic Hair Cream, Coconut Hair Cream, Coriander Hair Cream, Vitamin C, Vitamin E, UV Protection, Heat Protection, Anti-Pollution, Deep Hydration, Healthy Hair, Manageable Hair, Frizz Control, Shiny Hair, Rustic Art, Vegan Hair Care, Cruelty Free, Paraben Free, Sulfate Free, Natural Ingredients, Hair Nourishment, Daily Hair Care, Post Wash Treatment, Scalp Health, Moisturizing Hair Cream, Indian Beauty Brand, Eco Friendly, Sustainable Beauty, Chemical Free, Leave-in Conditioner, Hair Protection, Scalp Care, Non Greasy, Botanical Hair Care, Vitamin Enriched, Styling Cream, Hair Repair, Soft Hair</v>
+      </c>
+      <c r="N299" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P299" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q299" t="b">
+        <v>0</v>
+      </c>
+      <c r="R299" t="b">
+        <v>0</v>
+      </c>
+      <c r="S299" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>m4</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C300" t="str">
+        <v>Organic Orange Almond Hair Conditioner</v>
+      </c>
+      <c r="D300" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Orange_Almond_Hair_Conditioner_Rustic_Art_b021b49e77c7260f_1024x.jpg?v=1768722440</v>
+      </c>
+      <c r="E300" t="str">
+        <v>Men</v>
+      </c>
+      <c r="F300" t="str">
+        <v>Kurtas</v>
+      </c>
+      <c r="G300">
+        <v>475</v>
+      </c>
+      <c r="H300" t="str">
+        <v>200 g</v>
+      </c>
+      <c r="I300" t="str">
+        <v>Rustic Art Organic Orange Almond Hair Conditioner is a uniquely formulated hair care essential designed to transform your post-wash routine. Enriched with the goodness of Vitamin F, Glycerin, and Coconut Milk, this conditioner provides a natural gloss to the length of your hair while ensuring it remains deeply conditioned and manageable. No more struggling with entangled hair; this natural blend works effectively to smoothen cuticles and restore vitality. The inclusion of Orange and Almond oils provides a refreshing citrus scent and deep nourishment to every strand. The texture is lightweight yet creamy, allowing for easy application and absorption without weighing hair down. This product is ideal for those seeking a sustainable and chemical-free way to maintain hair health. It is free from harsh surfactants and synthetic fragrances, making it suitable for all hair types. Use after shampooing to achieve soft, shiny, and frizz-free hair naturally. This conditioner is an excellent choice for conscious consumers looking for organic and effective hair care solutions, certified for purity and environmental safety.</v>
+      </c>
+      <c r="J300" t="str">
+        <v>https://www.rusticart.in/collections/hair-care-conditioner/products/organic-orange-almond-hair-conditioner</v>
+      </c>
+      <c r="K300" t="str">
+        <v>1</v>
+      </c>
+      <c r="L300" t="str">
+        <v>200 g</v>
+      </c>
+      <c r="M300" t="str">
+        <v>organic hair conditioner, orange almond conditioner, rustic art hair care, natural hair conditioner, vegan hair care, sulfate free conditioner, paraben free, vitamin f for hair, coconut milk conditioner, hair detangler, glossy hair, hair nourishment, cruelty free, sustainable beauty, plastic free hair care, eco friendly conditioner, herbal hair care, ayurvedic hair care, hair moisturizing, deep conditioning, frizz control, soft hair, shiny hair, indian beauty brand, organic ingredients, almond oil for hair, orange oil for hair, chemical free hair care, hair health, salon finish at home, eco conscious products, natural shine, healthy hair routine, clean beauty, ethical consumer, hair softening, moisture locking, plant based hair care, toxin free, rustic art products</v>
+      </c>
+      <c r="N300" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P300" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q300" t="b">
+        <v>0</v>
+      </c>
+      <c r="R300" t="b">
+        <v>0</v>
+      </c>
+      <c r="S300" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>pet1</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C301" t="str">
+        <v>Coconut Coriander Hair Cream with Vitamin C &amp; E (50ml)</v>
+      </c>
+      <c r="D301" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Coconut_Coriander_Hair_Cream_with_Vitamin_C_E_50ml_Rustic_Art_d772b780864f83eb_1024x.jpg?v=1768722478</v>
+      </c>
+      <c r="E301" t="str">
+        <v>Pets</v>
+      </c>
+      <c r="F301" t="str">
+        <v>Pet Care</v>
+      </c>
+      <c r="G301">
+        <v>250</v>
+      </c>
+      <c r="H301" t="str">
+        <v>50ml</v>
+      </c>
+      <c r="I301" t="str">
+        <v>Rustic Art Coconut Coriander Hair Cream with Vitamin C &amp; E is a meticulously crafted natural formula designed for intensive hair nourishment and protection. Enriched with the goodness of organic coconut oil and coriander, it provides a deep hydration boost to both the scalp and hair strands. This hair cream is fortified with Vitamin C and E, which act as powerful antioxidants to shield your hair from the damaging effects of heat styling, UV rays, and urban pollution. The texture is lightweight and non-greasy, making it perfect for daily use as a leave-in conditioner or post-wash styling cream. It effectively tames frizz, improves manageability, and adds a healthy, natural shine to the hair. Free from sulfates, parabens, and synthetic fragrances, this product is certified organic and vegan, ensuring a safe and eco-friendly grooming experience. Simply apply a small amount to damp or dry hair to lock in moisture and strengthen hair fibers. Experience the benefits of traditional botanical wisdom combined with modern nutritional science for vibrant, resilient hair.</v>
+      </c>
+      <c r="J301" t="str">
+        <v>https://www.rusticart.in/collections/hair-care-conditioner/products/rustic-art-coconut-coriander-hair-cream-vitamin-c</v>
+      </c>
+      <c r="K301" t="str">
+        <v>1</v>
+      </c>
+      <c r="L301" t="str">
+        <v>50ml</v>
+      </c>
+      <c r="M301" t="str">
+        <v>Hair Care, Hair Cream, Natural Hair Care, Organic Hair Cream, Coconut Hair Cream, Coriander Hair Cream, Vitamin C, Vitamin E, UV Protection, Heat Protection, Anti-Pollution, Deep Hydration, Healthy Hair, Manageable Hair, Frizz Control, Shiny Hair, Rustic Art, Vegan Hair Care, Cruelty Free, Paraben Free, Sulfate Free, Natural Ingredients, Hair Nourishment, Daily Hair Care, Post Wash Treatment, Scalp Health, Moisturizing Hair Cream, Indian Beauty Brand, Eco Friendly, Sustainable Beauty, Chemical Free, Leave-in Conditioner, Hair Protection, Scalp Care, Non Greasy, Botanical Hair Care, Vitamin Enriched, Styling Cream, Hair Repair, Soft Hair</v>
+      </c>
+      <c r="N301" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P301" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q301" t="b">
+        <v>0</v>
+      </c>
+      <c r="R301" t="b">
+        <v>0</v>
+      </c>
+      <c r="S301" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>pet2</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C302" t="str">
+        <v>Organic Orange Almond Hair Conditioner</v>
+      </c>
+      <c r="D302" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Orange_Almond_Hair_Conditioner_Rustic_Art_b021b49e77c7260f_1024x.jpg?v=1768722440</v>
+      </c>
+      <c r="E302" t="str">
+        <v>Pets</v>
+      </c>
+      <c r="F302" t="str">
+        <v>Pet Care</v>
+      </c>
+      <c r="G302">
+        <v>475</v>
+      </c>
+      <c r="H302" t="str">
+        <v>200 g</v>
+      </c>
+      <c r="I302" t="str">
+        <v>Rustic Art Organic Orange Almond Hair Conditioner is a uniquely formulated hair care essential designed to transform your post-wash routine. Enriched with the goodness of Vitamin F, Glycerin, and Coconut Milk, this conditioner provides a natural gloss to the length of your hair while ensuring it remains deeply conditioned and manageable. No more struggling with entangled hair; this natural blend works effectively to smoothen cuticles and restore vitality. The inclusion of Orange and Almond oils provides a refreshing citrus scent and deep nourishment to every strand. The texture is lightweight yet creamy, allowing for easy application and absorption without weighing hair down. This product is ideal for those seeking a sustainable and chemical-free way to maintain hair health. It is free from harsh surfactants and synthetic fragrances, making it suitable for all hair types. Use after shampooing to achieve soft, shiny, and frizz-free hair naturally. This conditioner is an excellent choice for conscious consumers looking for organic and effective hair care solutions, certified for purity and environmental safety.</v>
+      </c>
+      <c r="J302" t="str">
+        <v>https://www.rusticart.in/collections/hair-care-conditioner/products/organic-orange-almond-hair-conditioner</v>
+      </c>
+      <c r="K302" t="str">
+        <v>1</v>
+      </c>
+      <c r="L302" t="str">
+        <v>200 g</v>
+      </c>
+      <c r="M302" t="str">
+        <v>organic hair conditioner, orange almond conditioner, rustic art hair care, natural hair conditioner, vegan hair care, sulfate free conditioner, paraben free, vitamin f for hair, coconut milk conditioner, hair detangler, glossy hair, hair nourishment, cruelty free, sustainable beauty, plastic free hair care, eco friendly conditioner, herbal hair care, ayurvedic hair care, hair moisturizing, deep conditioning, frizz control, soft hair, shiny hair, indian beauty brand, organic ingredients, almond oil for hair, orange oil for hair, chemical free hair care, hair health, salon finish at home, eco conscious products, natural shine, healthy hair routine, clean beauty, ethical consumer, hair softening, moisture locking, plant based hair care, toxin free, rustic art products</v>
+      </c>
+      <c r="N302" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P302" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q302" t="b">
+        <v>0</v>
+      </c>
+      <c r="R302" t="b">
+        <v>0</v>
+      </c>
+      <c r="S302" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>b2</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C303" t="str">
+        <v>Coconut Coriander Hair Cream with Vitamin C &amp; E (50ml)</v>
+      </c>
+      <c r="D303" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Coconut_Coriander_Hair_Cream_with_Vitamin_C_E_50ml_Rustic_Art_d772b780864f83eb_1024x.jpg?v=1768722478</v>
+      </c>
+      <c r="E303" t="str">
+        <v>Baby Care</v>
+      </c>
+      <c r="F303" t="str">
+        <v>Baby Food</v>
+      </c>
+      <c r="G303">
+        <v>250</v>
+      </c>
+      <c r="H303" t="str">
+        <v>50ml</v>
+      </c>
+      <c r="I303" t="str">
+        <v>Rustic Art Coconut Coriander Hair Cream with Vitamin C &amp; E is a meticulously crafted natural formula designed for intensive hair nourishment and protection. Enriched with the goodness of organic coconut oil and coriander, it provides a deep hydration boost to both the scalp and hair strands. This hair cream is fortified with Vitamin C and E, which act as powerful antioxidants to shield your hair from the damaging effects of heat styling, UV rays, and urban pollution. The texture is lightweight and non-greasy, making it perfect for daily use as a leave-in conditioner or post-wash styling cream. It effectively tames frizz, improves manageability, and adds a healthy, natural shine to the hair. Free from sulfates, parabens, and synthetic fragrances, this product is certified organic and vegan, ensuring a safe and eco-friendly grooming experience. Simply apply a small amount to damp or dry hair to lock in moisture and strengthen hair fibers. Experience the benefits of traditional botanical wisdom combined with modern nutritional science for vibrant, resilient hair.</v>
+      </c>
+      <c r="J303" t="str">
+        <v>https://www.rusticart.in/collections/hair-care-conditioner/products/rustic-art-coconut-coriander-hair-cream-vitamin-c</v>
+      </c>
+      <c r="K303" t="str">
+        <v>1</v>
+      </c>
+      <c r="L303" t="str">
+        <v>50ml</v>
+      </c>
+      <c r="M303" t="str">
+        <v>Hair Care, Hair Cream, Natural Hair Care, Organic Hair Cream, Coconut Hair Cream, Coriander Hair Cream, Vitamin C, Vitamin E, UV Protection, Heat Protection, Anti-Pollution, Deep Hydration, Healthy Hair, Manageable Hair, Frizz Control, Shiny Hair, Rustic Art, Vegan Hair Care, Cruelty Free, Paraben Free, Sulfate Free, Natural Ingredients, Hair Nourishment, Daily Hair Care, Post Wash Treatment, Scalp Health, Moisturizing Hair Cream, Indian Beauty Brand, Eco Friendly, Sustainable Beauty, Chemical Free, Leave-in Conditioner, Hair Protection, Scalp Care, Non Greasy, Botanical Hair Care, Vitamin Enriched, Styling Cream, Hair Repair, Soft Hair</v>
+      </c>
+      <c r="N303" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P303" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q303" t="b">
+        <v>0</v>
+      </c>
+      <c r="R303" t="b">
+        <v>0</v>
+      </c>
+      <c r="S303" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>b3</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Rustic Art</v>
+      </c>
+      <c r="C304" t="str">
+        <v>Organic Orange Almond Hair Conditioner</v>
+      </c>
+      <c r="D304" t="str">
+        <v>http://www.rusticart.in/cdn/shop/files/Orange_Almond_Hair_Conditioner_Rustic_Art_b021b49e77c7260f_1024x.jpg?v=1768722440</v>
+      </c>
+      <c r="E304" t="str">
+        <v>Baby Care</v>
+      </c>
+      <c r="F304" t="str">
+        <v>Baby Food</v>
+      </c>
+      <c r="G304">
+        <v>475</v>
+      </c>
+      <c r="H304" t="str">
+        <v>200 g</v>
+      </c>
+      <c r="I304" t="str">
+        <v>Rustic Art Organic Orange Almond Hair Conditioner is a uniquely formulated hair care essential designed to transform your post-wash routine. Enriched with the goodness of Vitamin F, Glycerin, and Coconut Milk, this conditioner provides a natural gloss to the length of your hair while ensuring it remains deeply conditioned and manageable. No more struggling with entangled hair; this natural blend works effectively to smoothen cuticles and restore vitality. The inclusion of Orange and Almond oils provides a refreshing citrus scent and deep nourishment to every strand. The texture is lightweight yet creamy, allowing for easy application and absorption without weighing hair down. This product is ideal for those seeking a sustainable and chemical-free way to maintain hair health. It is free from harsh surfactants and synthetic fragrances, making it suitable for all hair types. Use after shampooing to achieve soft, shiny, and frizz-free hair naturally. This conditioner is an excellent choice for conscious consumers looking for organic and effective hair care solutions, certified for purity and environmental safety.</v>
+      </c>
+      <c r="J304" t="str">
+        <v>https://www.rusticart.in/collections/hair-care-conditioner/products/organic-orange-almond-hair-conditioner</v>
+      </c>
+      <c r="K304" t="str">
+        <v>1</v>
+      </c>
+      <c r="L304" t="str">
+        <v>200 g</v>
+      </c>
+      <c r="M304" t="str">
+        <v>organic hair conditioner, orange almond conditioner, rustic art hair care, natural hair conditioner, vegan hair care, sulfate free conditioner, paraben free, vitamin f for hair, coconut milk conditioner, hair detangler, glossy hair, hair nourishment, cruelty free, sustainable beauty, plastic free hair care, eco friendly conditioner, herbal hair care, ayurvedic hair care, hair moisturizing, deep conditioning, frizz control, soft hair, shiny hair, indian beauty brand, organic ingredients, almond oil for hair, orange oil for hair, chemical free hair care, hair health, salon finish at home, eco conscious products, natural shine, healthy hair routine, clean beauty, ethical consumer, hair softening, moisture locking, plant based hair care, toxin free, rustic art products</v>
+      </c>
+      <c r="N304" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P304" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q304" t="b">
+        <v>0</v>
+      </c>
+      <c r="R304" t="b">
+        <v>0</v>
+      </c>
+      <c r="S304" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S304"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nigooda-web/nigooda-backend/products.xlsx
+++ b/nigooda-web/nigooda-backend/products.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S304"/>
+  <dimension ref="A1:T305"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,6 +457,9 @@
       <c r="S1" t="str">
         <v>isUnderrated</v>
       </c>
+      <c r="T1" t="str">
+        <v>Subcategory Sample Rank</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -2081,6 +2084,9 @@
       <c r="S30" t="b">
         <v>0</v>
       </c>
+      <c r="T30">
+        <v>6</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -2137,6 +2143,9 @@
       <c r="S31" t="b">
         <v>0</v>
       </c>
+      <c r="T31">
+        <v>4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -2193,6 +2202,9 @@
       <c r="S32" t="b">
         <v>0</v>
       </c>
+      <c r="T32">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -2249,6 +2261,9 @@
       <c r="S33" t="b">
         <v>0</v>
       </c>
+      <c r="T33">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -2305,6 +2320,9 @@
       <c r="S34" t="b">
         <v>0</v>
       </c>
+      <c r="T34">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -2361,6 +2379,9 @@
       <c r="S35" t="b">
         <v>0</v>
       </c>
+      <c r="T35">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -2417,6 +2438,9 @@
       <c r="S36" t="b">
         <v>0</v>
       </c>
+      <c r="T36">
+        <v>7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -2473,6 +2497,9 @@
       <c r="S37" t="b">
         <v>0</v>
       </c>
+      <c r="T37">
+        <v>9</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -2529,6 +2556,9 @@
       <c r="S38" t="b">
         <v>0</v>
       </c>
+      <c r="T38">
+        <v>8</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2585,6 +2615,9 @@
       <c r="S39" t="b">
         <v>0</v>
       </c>
+      <c r="T39">
+        <v>10</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -11186,7 +11219,7 @@
         <v>https://honeyveda.in/products/himalayan-forest-raw-honey</v>
       </c>
       <c r="K193" t="str">
-        <v>HONEYVEDA-002</v>
+        <v>HONEYVEDA-001</v>
       </c>
       <c r="L193" t="str">
         <v>Himalayan Forest Raw Honey - 250 g</v>
@@ -11242,7 +11275,7 @@
         <v>https://honeyveda.in/products/eucalyptus-honey</v>
       </c>
       <c r="K194" t="str">
-        <v>HONEYVEDA-003</v>
+        <v>HONEYVEDA-001</v>
       </c>
       <c r="L194" t="str">
         <v>Eucalyptus Honey - 250 g</v>
@@ -11298,7 +11331,7 @@
         <v>https://honeyveda.in/products/lychee-honey</v>
       </c>
       <c r="K195" t="str">
-        <v>HONEYVEDA-004</v>
+        <v>HONEYVEDA-001</v>
       </c>
       <c r="L195" t="str">
         <v>Lychee Honey - 250 g</v>
@@ -11354,7 +11387,7 @@
         <v>https://honeyveda.in/products/jamun-raw-honey</v>
       </c>
       <c r="K196" t="str">
-        <v>HONEYVEDA-005</v>
+        <v>HONEYVEDA-001</v>
       </c>
       <c r="L196" t="str">
         <v>Jamun Raw Honey - 250 g</v>
@@ -11410,7 +11443,7 @@
         <v>https://honeyveda.in/products/mustard-honey</v>
       </c>
       <c r="K197" t="str">
-        <v>HONEYVEDA-006</v>
+        <v>HONEYVEDA-001</v>
       </c>
       <c r="L197" t="str">
         <v>Mustard Honey - 250 g</v>
@@ -11466,7 +11499,7 @@
         <v>https://honeyveda.in/products/ajwain-raw-honey</v>
       </c>
       <c r="K198" t="str">
-        <v>HONEYVEDA-007</v>
+        <v>HONEYVEDA-001</v>
       </c>
       <c r="L198" t="str">
         <v>Ajwain Raw Honey - 250 g</v>
@@ -17426,9 +17459,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>f244</v>
+      </c>
+      <c r="B305" t="str">
+        <v>ritu</v>
+      </c>
+      <c r="C305" t="str">
+        <v>ritesh</v>
+      </c>
+      <c r="D305" t="str">
+        <v>https://www.eggoz.com/cdn/shop/files/pack_of_6_2_fa4439c2-b1ba-4355-a24f-56235891b00a.jpg?v=1764934437&amp;width=713</v>
+      </c>
+      <c r="E305" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F305" t="str">
+        <v>Whole Foods</v>
+      </c>
+      <c r="G305">
+        <v>69</v>
+      </c>
+      <c r="H305" t="str">
+        <v>6 Eggs</v>
+      </c>
+      <c r="I305" t="str">
+        <v>Eggoz White Eggs are farm-fresh, high-quality eggs sourced from healthy hens. These eggs are UV sanitized to ensure they are free from bacteria and pathogens. They are rich in high-quality protein and essential vitamins, making them a perfect choice for a healthy breakfast or baking needs. Eggoz ensures no antibiotics or hormones are used in the process. These eggs are quality-checked through an 11-step process to ensure safety and freshness. Available in various pack sizes including 6, 10, and 30 eggs.</v>
+      </c>
+      <c r="J305" t="str">
+        <v>eggoz.com</v>
+      </c>
+      <c r="K305" t="str">
+        <v>EGG-01</v>
+      </c>
+      <c r="L305" t="str">
+        <v>Eggoz White Eggs</v>
+      </c>
+      <c r="M305" t="str">
+        <v>Eggoz, White Eggs, Eggs, Fresh Eggs, High Protein, Breakfast, Healthy, UV Sanitized, Hormone Free, Antibiotic Free, Farm Fresh, Dairy, Poultry, Nutritious, Cooking, Baking, Eggoz Nutrition, Natural, Quality Checked, Kitchen Staples, Protein Rich, Freshness, Daily Essentials</v>
+      </c>
+      <c r="N305" t="str">
+        <v>Live</v>
+      </c>
+      <c r="P305" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q305" t="b">
+        <v>0</v>
+      </c>
+      <c r="R305" t="b">
+        <v>0</v>
+      </c>
+      <c r="S305" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S304"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T305"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nigooda-web/nigooda-backend/products.xlsx
+++ b/nigooda-web/nigooda-backend/products.xlsx
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         <v>Live</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -673,7 +673,7 @@
         <v>Live</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
